--- a/interview/Interview_Inventory.xlsx
+++ b/interview/Interview_Inventory.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Interview Inventory'!$A$2:$AQ$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Interview Inventory'!$A$2:$AQ$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Round 1 Question Bank'!$A$4:$G$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -915,7 +915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ25"/>
+  <dimension ref="A1:AQ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1319,7 +1319,7 @@
         <v>46310</v>
       </c>
       <c r="S3" s="18" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T3" s="19" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>46269</v>
       </c>
       <c r="S4" s="18" t="n">
-        <v>-34</v>
+        <v>-40</v>
       </c>
       <c r="T4" s="25" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>46265</v>
       </c>
       <c r="S5" s="18" t="n">
-        <v>-38</v>
+        <v>-44</v>
       </c>
       <c r="T5" s="25" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>46240</v>
       </c>
       <c r="S6" s="18" t="n">
-        <v>-63</v>
+        <v>-69</v>
       </c>
       <c r="T6" s="25" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>46300</v>
       </c>
       <c r="S7" s="18" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="T7" s="25" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>46295</v>
       </c>
       <c r="S8" s="18" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="T8" s="25" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>46325</v>
       </c>
       <c r="S9" s="18" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="T9" s="19" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>46184</v>
       </c>
       <c r="S10" s="18" t="n">
-        <v>-119</v>
+        <v>-125</v>
       </c>
       <c r="T10" s="25" t="inlineStr">
         <is>
@@ -2303,11 +2303,11 @@
         <v>46304</v>
       </c>
       <c r="S11" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" s="19" t="inlineStr">
-        <is>
-          <t>Within 30 days</t>
+        <v>-5</v>
+      </c>
+      <c r="T11" s="25" t="inlineStr">
+        <is>
+          <t>Available now</t>
         </is>
       </c>
       <c r="U11" s="19" t="inlineStr">
@@ -2426,7 +2426,7 @@
         <v>46265</v>
       </c>
       <c r="S12" s="18" t="n">
-        <v>-38</v>
+        <v>-44</v>
       </c>
       <c r="T12" s="25" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>46263</v>
       </c>
       <c r="S13" s="18" t="n">
-        <v>-40</v>
+        <v>-46</v>
       </c>
       <c r="T13" s="25" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>46300</v>
       </c>
       <c r="S14" s="18" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="T14" s="25" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>46289</v>
       </c>
       <c r="S15" s="18" t="n">
-        <v>-14</v>
+        <v>-20</v>
       </c>
       <c r="T15" s="25" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46274</v>
       </c>
       <c r="S16" s="18" t="n">
-        <v>-29</v>
+        <v>-35</v>
       </c>
       <c r="T16" s="25" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>46248</v>
       </c>
       <c r="S17" s="18" t="n">
-        <v>-55</v>
+        <v>-61</v>
       </c>
       <c r="T17" s="25" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>46293</v>
       </c>
       <c r="S18" s="18" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="T18" s="25" t="inlineStr">
         <is>
@@ -3287,11 +3287,11 @@
         <v>46305</v>
       </c>
       <c r="S19" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" s="19" t="inlineStr">
-        <is>
-          <t>Within 30 days</t>
+        <v>-4</v>
+      </c>
+      <c r="T19" s="25" t="inlineStr">
+        <is>
+          <t>Available now</t>
         </is>
       </c>
       <c r="U19" s="19" t="inlineStr">
@@ -3410,7 +3410,7 @@
         <v>46241</v>
       </c>
       <c r="S20" s="18" t="n">
-        <v>-62</v>
+        <v>-68</v>
       </c>
       <c r="T20" s="25" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>46280</v>
       </c>
       <c r="S21" s="18" t="n">
-        <v>-23</v>
+        <v>-29</v>
       </c>
       <c r="T21" s="25" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>46240</v>
       </c>
       <c r="S22" s="18" t="n">
-        <v>-63</v>
+        <v>-69</v>
       </c>
       <c r="T22" s="25" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>46178</v>
       </c>
       <c r="S24" s="18" t="n">
-        <v>-125</v>
+        <v>-131</v>
       </c>
       <c r="T24" s="25" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>46295</v>
       </c>
       <c r="S25" s="18" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="T25" s="25" t="inlineStr">
         <is>
@@ -4062,24 +4062,270 @@
       <c r="AP25" s="22" t="n"/>
       <c r="AQ25" s="20" t="n"/>
     </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>IKrux Engineering</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>8-Oct-2026</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Saravana Kumar B</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>9043215204</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>hashvana@gmail.com</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>InFynd</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>16 Years</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Technical Project Manager: 6 Years | Backend Node.js: 5 Years</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="L26" s="14" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>LWD : 15-Jun-26</t>
+        </is>
+      </c>
+      <c r="N26" s="15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="O26" s="15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="P26" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q26" s="16" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="R26" s="17" t="n">
+        <v>46188</v>
+      </c>
+      <c r="S26" s="18" t="n">
+        <v>-121</v>
+      </c>
+      <c r="T26" s="25" t="inlineStr">
+        <is>
+          <t>Available now</t>
+        </is>
+      </c>
+      <c r="U26" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="V26" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="W26" s="20" t="n"/>
+      <c r="X26" s="21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y26" s="20" t="n"/>
+      <c r="Z26" s="22" t="n"/>
+      <c r="AA26" s="20" t="n"/>
+      <c r="AB26" s="20" t="n"/>
+      <c r="AC26" s="22" t="n"/>
+      <c r="AD26" s="20" t="n"/>
+      <c r="AE26" s="20" t="n"/>
+      <c r="AF26" s="22" t="n"/>
+      <c r="AG26" s="20" t="n"/>
+      <c r="AH26" s="20" t="n"/>
+      <c r="AI26" s="22" t="n"/>
+      <c r="AJ26" s="20" t="n"/>
+      <c r="AK26" s="20" t="n"/>
+      <c r="AL26" s="23" t="n"/>
+      <c r="AM26" s="20" t="n"/>
+      <c r="AN26" s="20" t="n"/>
+      <c r="AO26" s="24" t="n"/>
+      <c r="AP26" s="22" t="n"/>
+      <c r="AQ26" s="20" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>IKrux Engineering</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>8-Oct-2026</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Veena Kuppusamy</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>9894188254</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>veenakcbe@gmail.com</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>G2 TechSoft</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>18 Years</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Technical Project Manager: 10 Years | Backend .Net: 10 Years</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="L27" s="14" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>LWD : 30-Mar-26</t>
+        </is>
+      </c>
+      <c r="N27" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="O27" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q27" s="16" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="R27" s="17" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S27" s="18" t="n">
+        <v>-198</v>
+      </c>
+      <c r="T27" s="25" t="inlineStr">
+        <is>
+          <t>Available now</t>
+        </is>
+      </c>
+      <c r="U27" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="V27" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W27" s="20" t="n"/>
+      <c r="X27" s="21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y27" s="20" t="n"/>
+      <c r="Z27" s="22" t="n"/>
+      <c r="AA27" s="20" t="n"/>
+      <c r="AB27" s="20" t="n"/>
+      <c r="AC27" s="22" t="n"/>
+      <c r="AD27" s="20" t="n"/>
+      <c r="AE27" s="20" t="n"/>
+      <c r="AF27" s="22" t="n"/>
+      <c r="AG27" s="20" t="n"/>
+      <c r="AH27" s="20" t="n"/>
+      <c r="AI27" s="22" t="n"/>
+      <c r="AJ27" s="20" t="n"/>
+      <c r="AK27" s="20" t="n"/>
+      <c r="AL27" s="23" t="n"/>
+      <c r="AM27" s="20" t="n"/>
+      <c r="AN27" s="20" t="n"/>
+      <c r="AO27" s="24" t="n"/>
+      <c r="AP27" s="22" t="n"/>
+      <c r="AQ27" s="20" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AQ25"/>
+  <autoFilter ref="A2:AQ27"/>
   <mergeCells count="3">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="Q1:V1"/>
     <mergeCell ref="W1:AQ1"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="Y3:Y25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Y3:Y27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Shortlisted,On Hold,Rejected"</formula1>
     </dataValidation>
-    <dataValidation sqref="AB3:AB25 AE3:AE25 AH3:AH25 AK3:AK25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AB3:AB27 AE3:AE27 AH3:AH27 AK3:AK27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Scheduled,Selected,Rejected,On Hold,No Show,Rescheduled"</formula1>
     </dataValidation>
-    <dataValidation sqref="AM3:AM25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AM3:AM27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"In Process,Selected,Rejected,On Hold,Offer Declined,Joined,Dropped Out"</formula1>
     </dataValidation>
-    <dataValidation sqref="X3:X25 AN3:AN25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="X3:X27 AN3:AN27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4094,7 +4340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5080,6 +5326,86 @@
       <c r="H27" s="19" t="inlineStr">
         <is>
           <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="104" customHeight="1">
+      <c r="A28" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Saravana Kumar B</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>IKrux Engineering</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Saravana_Kumar_B.pdf</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Technical Project Manager | IT Delivery Leader | PMP | 16+ years IT | AI/ML | Cloud</t>
+        </is>
+      </c>
+      <c r="F28" s="28" t="inlineStr">
+        <is>
+          <t>Real delivery record, but four employers in under three years</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Genuine technical project management: 20+ member cross-functional teams, ₹5M+ budgets, 95% on-time milestones, stakeholders across three continents, and current AI/LLM delivery work evaluating OpenAI, Gemini and GPT-OSS against cost and latency. PMP and a GCP certification. The concern is tenure, not capability: since Dec 2022 he has had four employers — InFynd 11 months, Bluekode 7, Mobitech 7 on contract, CG-VAK 15 — with two of those explicitly consultant or contract engagements, against a 9-year run at Ugam before that. He also left InFynd in June 2026. Separately, the row credits Backend Node.js at 5 years; his CV lists Node only in a skills line, and his hands-on development was Python, Java and Selenium at Ugam up to 2020.</t>
+        </is>
+      </c>
+      <c r="H28" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="104" customHeight="1">
+      <c r="A29" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Veena Kuppusamy</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>IKrux Engineering</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Veena.pdf</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Project Manager | Agile delivery | .NET background</t>
+        </is>
+      </c>
+      <c r="F29" s="30" t="inlineStr">
+        <is>
+          <t>Long experience, but a dated stack and a 15-month gap</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Eighteen-plus years, 15–20 member teams, full RFP-to-sign-off ownership and a Microsoft Partnership Award on a food-bank project. Three things weigh against her. Her stack is C#, VB.NET, ASP.NET MVC, jQuery and MS SQL Server — no .NET Core or .NET 5+, no cloud of any kind, no containers or microservices, which is unusual against the rest of this pipeline and makes ‘Backend .Net 10 Years’ mean something different from what it suggests. There is an unexplained 15-month gap between Alligatortek ending Dec 2020 and Inno Valley starting Mar 2022. And the row credits 10 years as Technical Project Manager, but her PM and TPM titles run from Mar 2022, about four years; the preceding eight were as a Technical Lead. She left G2 TechSoft in March 2026, so she has been out roughly six months.</t>
+        </is>
+      </c>
+      <c r="H29" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5459,29 +5785,27 @@
       <c r="A15" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="11" t="n">
+        <v>24</v>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Pipeline-wide</t>
-        </is>
-      </c>
-      <c r="D15" s="32" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Saravana Kumar B</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Offers field blank for SL 8, 10, 13, 14 and 15.</t>
+          <t>Four employers since Dec 2022 — InFynd 11 months, Bluekode 7, Mobitech 7 on contract, CG-VAK 15 — two of them explicitly consultant or contract engagements.</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Collect a yes-with-value or a no before any offer discussion.</t>
+          <t>Probe the reason for each move and what would make him stay; a permanent delivery role needs that answered.</t>
         </is>
       </c>
       <c r="G15" s="20" t="n"/>
@@ -5490,29 +5814,27 @@
       <c r="A16" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="11" t="n">
+        <v>25</v>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Pipeline-wide</t>
-        </is>
-      </c>
-      <c r="D16" s="32" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Veena Kuppusamy</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Hikes of 100%, 97%, 65% and 64% at Senior Software Engineer level.</t>
+          <t>Unexplained 15-month gap between Alligatortek ending Dec 2020 and Inno Valley starting Mar 2022.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Check each against the approved band before the profiles reach a panel.</t>
+          <t>Ask her to account for it.</t>
         </is>
       </c>
       <c r="G16" s="20" t="n"/>
@@ -5522,26 +5844,26 @@
         <v>13</v>
       </c>
       <c r="B17" s="11" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Jeganagan Murugesan</t>
-        </is>
-      </c>
-      <c r="D17" s="32" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Veena Kuppusamy</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>CV lists employment from Jul 2007 (about 18 years of history) but states 14+ years; a gap sits between Cognizant (to Oct 2013) and TCS (from Dec 2014).</t>
+          <t>Out of employment around six months — G2 TechSoft ended 30 Mar 2026.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Ask him to account for the gap and confirm the true total.</t>
+          <t>Confirm current status and what she has been doing since.</t>
         </is>
       </c>
       <c r="G17" s="20" t="n"/>
@@ -5551,26 +5873,26 @@
         <v>14</v>
       </c>
       <c r="B18" s="11" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Dayakar G</t>
-        </is>
-      </c>
-      <c r="D18" s="32" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Veena Kuppusamy</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>CV shows IBM as current with no notice; the row records LWD 4 Sep 2026.</t>
+          <t>Stack is C#, VB.NET, ASP.NET MVC, jQuery and MS SQL Server, with no .NET Core, no cloud, no containers and no microservices anywhere on the CV.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Establish which is current and record the real notice position.</t>
+          <t>Decide whether a PM who has not worked on a modern stack can lead this team, and test it directly if she proceeds.</t>
         </is>
       </c>
       <c r="G18" s="20" t="n"/>
@@ -5579,12 +5901,14 @@
       <c r="A19" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="11" t="n">
-        <v>2</v>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Dayakar G</t>
+          <t>Pipeline-wide</t>
         </is>
       </c>
       <c r="D19" s="32" t="inlineStr">
@@ -5594,12 +5918,12 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>10.7 of 15 years were in-house manufacturing IT at Pricol.</t>
+          <t>The Round 1 theory set was written for engineers and leads. The two Technical Project Manager candidates will be scored against architecture depth they are not hired for.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Probe depth of enterprise .NET delivery in the technical round.</t>
+          <t>Either calibrate the expected bar for SL 24 and 25, or ask for a delivery-management question set for that role.</t>
         </is>
       </c>
       <c r="G19" s="20" t="n"/>
@@ -5608,12 +5932,14 @@
       <c r="A20" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="11" t="n">
-        <v>3</v>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Amre Binnaz. M</t>
+          <t>Pipeline-wide</t>
         </is>
       </c>
       <c r="D20" s="32" t="inlineStr">
@@ -5623,12 +5949,12 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Employment gap of roughly Jun–Oct 2020 between LAKEBA and OMS.</t>
+          <t>Offers field blank for SL 8, 10, 13, 14 and 15.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Ask the candidate to account for the gap.</t>
+          <t>Collect a yes-with-value or a no before any offer discussion.</t>
         </is>
       </c>
       <c r="G20" s="20" t="n"/>
@@ -5637,12 +5963,14 @@
       <c r="A21" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="11" t="n">
-        <v>4</v>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Adarsh Swaminathan</t>
+          <t>Pipeline-wide</t>
         </is>
       </c>
       <c r="D21" s="32" t="inlineStr">
@@ -5652,12 +5980,12 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Credited with 10.3 years of .Net, but his first Infosys projects (CAO, MCP for NatWest) were Java and Struts. CV states 9.5 years total against 10.3 recorded.</t>
+          <t>Hikes of 100%, 97%, 65% and 64% at Senior Software Engineer level.</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Restate .Net at roughly 7 to 8 years and correct the total.</t>
+          <t>Check each against the approved band before the profiles reach a panel.</t>
         </is>
       </c>
       <c r="G21" s="20" t="n"/>
@@ -5667,11 +5995,11 @@
         <v>18</v>
       </c>
       <c r="B22" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Adarsh Swaminathan</t>
+          <t>Jeganagan Murugesan</t>
         </is>
       </c>
       <c r="D22" s="32" t="inlineStr">
@@ -5681,12 +6009,12 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Based in Chamrajnagar, and already holds a 28 L offer against a 30 L expectation.</t>
+          <t>CV lists employment from Jul 2007 (about 18 years of history) but states 14+ years; a gap sits between Cognizant (to Oct 2013) and TCS (from Dec 2014).</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Confirm relocation and the closing timeline against the competing offer.</t>
+          <t>Ask him to account for the gap and confirm the true total.</t>
         </is>
       </c>
       <c r="G22" s="20" t="n"/>
@@ -5696,11 +6024,11 @@
         <v>19</v>
       </c>
       <c r="B23" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Sivakumar Varatharaj</t>
+          <t>Dayakar G</t>
         </is>
       </c>
       <c r="D23" s="32" t="inlineStr">
@@ -5710,12 +6038,12 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>CV states ‘Open to international opportunities (H1B Visa Holder)’ — a flight risk against a Coimbatore posting at 36 L.</t>
+          <t>CV shows IBM as current with no notice; the row records LWD 4 Sep 2026.</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Ask directly about his US plans before an offer is built.</t>
+          <t>Establish which is current and record the real notice position.</t>
         </is>
       </c>
       <c r="G23" s="20" t="n"/>
@@ -5725,11 +6053,11 @@
         <v>20</v>
       </c>
       <c r="B24" s="11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Sathya K S</t>
+          <t>Dayakar G</t>
         </is>
       </c>
       <c r="D24" s="32" t="inlineStr">
@@ -5739,12 +6067,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Of the 12 years recorded, 4+ were as an Assistant Professor of Computer Science, not industry software engineering.</t>
+          <t>10.7 of 15 years were in-house manufacturing IT at Pricol.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Record industry experience as roughly 8 years and confirm the panel is comfortable with the academic period.</t>
+          <t>Probe depth of enterprise .NET delivery in the technical round.</t>
         </is>
       </c>
       <c r="G24" s="20" t="n"/>
@@ -5754,11 +6082,11 @@
         <v>21</v>
       </c>
       <c r="B25" s="11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Navin Kumar</t>
+          <t>Amre Binnaz. M</t>
         </is>
       </c>
       <c r="D25" s="32" t="inlineStr">
@@ -5768,12 +6096,12 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Credited with 6 years of .Net; the CV shows C# only 2017–2020 and again from Jul 2025 — roughly 3 to 4 years.</t>
+          <t>Employment gap of roughly Jun–Oct 2020 between LAKEBA and OMS.</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Restate the .Net span and decide whether a React/Node lead fits the role.</t>
+          <t>Ask the candidate to account for the gap.</t>
         </is>
       </c>
       <c r="G25" s="20" t="n"/>
@@ -5783,11 +6111,11 @@
         <v>22</v>
       </c>
       <c r="B26" s="11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Navin Kumar</t>
+          <t>Adarsh Swaminathan</t>
         </is>
       </c>
       <c r="D26" s="32" t="inlineStr">
@@ -5797,12 +6125,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>33 L expected against 32.8 L current — a 0.6% hike, out of line with the rest.</t>
+          <t>Credited with 10.3 years of .Net, but his first Infosys projects (CAO, MCP for NatWest) were Java and Struts. CV states 9.5 years total against 10.3 recorded.</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Verify both figures; one is likely mis-keyed.</t>
+          <t>Restate .Net at roughly 7 to 8 years and correct the total.</t>
         </is>
       </c>
       <c r="G26" s="20" t="n"/>
@@ -5812,11 +6140,11 @@
         <v>23</v>
       </c>
       <c r="B27" s="11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Boopathi Molakgounder</t>
+          <t>Adarsh Swaminathan</t>
         </is>
       </c>
       <c r="D27" s="32" t="inlineStr">
@@ -5826,12 +6154,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Location recorded as Erode; the CV says Bangalore.</t>
+          <t>Based in Chamrajnagar, and already holds a 28 L offer against a 30 L expectation.</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Confirm with the candidate.</t>
+          <t>Confirm relocation and the closing timeline against the competing offer.</t>
         </is>
       </c>
       <c r="G27" s="20" t="n"/>
@@ -5841,11 +6169,11 @@
         <v>24</v>
       </c>
       <c r="B28" s="11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Ravikumar Gopal</t>
+          <t>Sivakumar Varatharaj</t>
         </is>
       </c>
       <c r="D28" s="32" t="inlineStr">
@@ -5855,12 +6183,12 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Credited with 10 years of Java; Java and Spring Boot start Jun 2018 — about 8 years. The 2016–2018 role was Android and IoT.</t>
+          <t>CV states ‘Open to international opportunities (H1B Visa Holder)’ — a flight risk against a Coimbatore posting at 36 L.</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Restate the Java span, and record the GenAI depth the row currently omits.</t>
+          <t>Ask directly about his US plans before an offer is built.</t>
         </is>
       </c>
       <c r="G28" s="20" t="n"/>
@@ -5870,11 +6198,11 @@
         <v>25</v>
       </c>
       <c r="B29" s="11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Vaisakh P</t>
+          <t>Sathya K S</t>
         </is>
       </c>
       <c r="D29" s="32" t="inlineStr">
@@ -5884,12 +6212,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Angular at 4 years appears only on a personal side project, and Lead at 6 years against a title held since Aug 2022.</t>
+          <t>Of the 12 years recorded, 4+ were as an Assistant Professor of Computer Science, not industry software engineering.</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Verify both figures with the candidate.</t>
+          <t>Record industry experience as roughly 8 years and confirm the panel is comfortable with the academic period.</t>
         </is>
       </c>
       <c r="G29" s="20" t="n"/>
@@ -5899,11 +6227,11 @@
         <v>26</v>
       </c>
       <c r="B30" s="11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Sandhosh Kumar</t>
+          <t>Navin Kumar</t>
         </is>
       </c>
       <c r="D30" s="32" t="inlineStr">
@@ -5913,12 +6241,12 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Credited with 5 years as Lead; Tech Lead title held only since Apr 2024, about 2.4 years. Four employers between Apr 2021 and Apr 2024, one a six-month stint.</t>
+          <t>Credited with 6 years of .Net; the CV shows C# only 2017–2020 and again from Jul 2025 — roughly 3 to 4 years.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Restate the lead span and probe the tenure pattern for retention risk.</t>
+          <t>Restate the .Net span and decide whether a React/Node lead fits the role.</t>
         </is>
       </c>
       <c r="G30" s="20" t="n"/>
@@ -5928,11 +6256,11 @@
         <v>27</v>
       </c>
       <c r="B31" s="11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Karthy</t>
+          <t>Navin Kumar</t>
         </is>
       </c>
       <c r="D31" s="32" t="inlineStr">
@@ -5942,12 +6270,12 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Cloud recorded generically at 4 years; the CV shows AWS, not Azure.</t>
+          <t>33 L expected against 32.8 L current — a 0.6% hike, out of line with the rest.</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Restate as AWS and confirm whether the role needs Azure.</t>
+          <t>Verify both figures; one is likely mis-keyed.</t>
         </is>
       </c>
       <c r="G31" s="20" t="n"/>
@@ -5957,11 +6285,11 @@
         <v>28</v>
       </c>
       <c r="B32" s="11" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Sankar Ponnusamy</t>
+          <t>Boopathi Molakgounder</t>
         </is>
       </c>
       <c r="D32" s="32" t="inlineStr">
@@ -5986,11 +6314,11 @@
         <v>29</v>
       </c>
       <c r="B33" s="11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Shanmuga raja</t>
+          <t>Ravikumar Gopal</t>
         </is>
       </c>
       <c r="D33" s="32" t="inlineStr">
@@ -6000,12 +6328,12 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>His CV and Adhithyan C’s (SL 13) share an employer and a near-identical structure, wording and skills taxonomy, differing mainly in the client name.</t>
+          <t>Credited with 10 years of Java; Java and Spring Boot start Jun 2018 — about 8 years. The 2016–2018 role was Android and IoT.</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Assess the two independently; do not let one interview colour the other.</t>
+          <t>Restate the Java span, and record the GenAI depth the row currently omits.</t>
         </is>
       </c>
       <c r="G33" s="20" t="n"/>
@@ -6015,11 +6343,11 @@
         <v>30</v>
       </c>
       <c r="B34" s="11" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Srinidhi Ravi</t>
+          <t>Vaisakh P</t>
         </is>
       </c>
       <c r="D34" s="32" t="inlineStr">
@@ -6029,12 +6357,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Entire tech skills list is Java 8, Unix shell, SQL, HTML/CSS, Actimize and AIS — no framework, no cloud, no modern front end, against an 18 L expectation.</t>
+          <t>Angular at 4 years appears only on a personal side project, and Lead at 6 years against a title held since Aug 2022.</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Probe what he has actually built, as distinct from supported.</t>
+          <t>Verify both figures with the candidate.</t>
         </is>
       </c>
       <c r="G34" s="20" t="n"/>
@@ -6044,11 +6372,11 @@
         <v>31</v>
       </c>
       <c r="B35" s="11" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Prince Kumar P</t>
+          <t>Sandhosh Kumar</t>
         </is>
       </c>
       <c r="D35" s="32" t="inlineStr">
@@ -6058,12 +6386,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Sixteen years total, but his own CV puts Java at about 5 years against Node at 7 and Angular at 9.</t>
+          <t>Credited with 5 years as Lead; Tech Lead title held only since Apr 2024, about 2.4 years. Four employers between Apr 2021 and Apr 2024, one a six-month stint.</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Decide whether the opening needs Java depth or accepts a polyglot lead, and brief the panel accordingly.</t>
+          <t>Restate the lead span and probe the tenure pattern for retention risk.</t>
         </is>
       </c>
       <c r="G35" s="20" t="n"/>
@@ -6073,11 +6401,11 @@
         <v>32</v>
       </c>
       <c r="B36" s="11" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Prince Kumar P</t>
+          <t>Karthy</t>
         </is>
       </c>
       <c r="D36" s="32" t="inlineStr">
@@ -6087,12 +6415,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>The row claims AWS and Microservices at 12 years each; his AWS work starts at Virtusa in Jan 2020, about six years.</t>
+          <t>Cloud recorded generically at 4 years; the CV shows AWS, not Azure.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Restate both spans and brief the panel on the real depth.</t>
+          <t>Restate as AWS and confirm whether the role needs Azure.</t>
         </is>
       </c>
       <c r="G36" s="20" t="n"/>
@@ -6102,11 +6430,11 @@
         <v>33</v>
       </c>
       <c r="B37" s="11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Prince Kumar P</t>
+          <t>Sankar Ponnusamy</t>
         </is>
       </c>
       <c r="D37" s="32" t="inlineStr">
@@ -6116,12 +6444,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>The row says Coimbatore and an LWD of 7 Aug 2026; the CV header says Chennai and still shows Virtusa as current.</t>
+          <t>Location recorded as Erode; the CV says Bangalore.</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Confirm both his location and whether he has actually left.</t>
+          <t>Confirm with the candidate.</t>
         </is>
       </c>
       <c r="G37" s="20" t="n"/>
@@ -6131,11 +6459,11 @@
         <v>34</v>
       </c>
       <c r="B38" s="11" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Gangasri Paramasivam</t>
+          <t>Shanmuga raja</t>
         </is>
       </c>
       <c r="D38" s="32" t="inlineStr">
@@ -6145,12 +6473,12 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>E-mail differs between sources: the row gives gangasri.p@gmail.com, the CV says p.gangasri@gmail.com.</t>
+          <t>His CV and Adhithyan C’s (SL 13) share an employer and a near-identical structure, wording and skills taxonomy, differing mainly in the client name.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Confirm which address reaches her before sending anything.</t>
+          <t>Assess the two independently; do not let one interview colour the other.</t>
         </is>
       </c>
       <c r="G38" s="20" t="n"/>
@@ -6160,11 +6488,11 @@
         <v>35</v>
       </c>
       <c r="B39" s="11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Gunavadhi A S</t>
+          <t>Srinidhi Ravi</t>
         </is>
       </c>
       <c r="D39" s="32" t="inlineStr">
@@ -6174,12 +6502,12 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Tech Mahindra engagement is listed as ending August 2026, so she has been out around two months.</t>
+          <t>Entire tech skills list is Java 8, Unix shell, SQL, HTML/CSS, Actimize and AIS — no framework, no cloud, no modern front end, against an 18 L expectation.</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Confirm current status and availability.</t>
+          <t>Probe what he has actually built, as distinct from supported.</t>
         </is>
       </c>
       <c r="G39" s="20" t="n"/>
@@ -6189,11 +6517,11 @@
         <v>36</v>
       </c>
       <c r="B40" s="11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Dhachanamoorthy N</t>
+          <t>Prince Kumar P</t>
         </is>
       </c>
       <c r="D40" s="32" t="inlineStr">
@@ -6203,12 +6531,12 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Five years total experience against an architecture-heavy Round 1 — a strong engineer, but the theory set will stretch him.</t>
+          <t>Sixteen years total, but his own CV puts Java at about 5 years against Node at 7 and Angular at 9.</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Decide whether to score him against the mid-level bar or treat the gaps as expected.</t>
+          <t>Decide whether the opening needs Java depth or accepts a polyglot lead, and brief the panel accordingly.</t>
         </is>
       </c>
       <c r="G40" s="20" t="n"/>
@@ -6218,11 +6546,11 @@
         <v>37</v>
       </c>
       <c r="B41" s="11" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Krishnan K</t>
+          <t>Prince Kumar P</t>
         </is>
       </c>
       <c r="D41" s="32" t="inlineStr">
@@ -6232,12 +6560,12 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Out of employment around four months, and the dates disagree: the vendor row says LWD 5 June 2026, the CV says the Wipro engagement ran to 25 June 2026.</t>
+          <t>The row claims AWS and Microservices at 12 years each; his AWS work starts at Virtusa in Jan 2020, about six years.</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Pin down the actual exit date and the reason for the break.</t>
+          <t>Restate both spans and brief the panel on the real depth.</t>
         </is>
       </c>
       <c r="G41" s="20" t="n"/>
@@ -6247,11 +6575,11 @@
         <v>38</v>
       </c>
       <c r="B42" s="11" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Krishnan K</t>
+          <t>Prince Kumar P</t>
         </is>
       </c>
       <c r="D42" s="32" t="inlineStr">
@@ -6261,12 +6589,12 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>The vendor row says Coimbatore; his CV address is Madurai.</t>
+          <t>The row says Coimbatore and an LWD of 7 Aug 2026; the CV header says Chennai and still shows Virtusa as current.</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Confirm where he is actually based and his willingness to be in Coimbatore.</t>
+          <t>Confirm both his location and whether he has actually left.</t>
         </is>
       </c>
       <c r="G42" s="20" t="n"/>
@@ -6276,11 +6604,11 @@
         <v>39</v>
       </c>
       <c r="B43" s="11" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Monish Kanna Bommuraj</t>
+          <t>Gangasri Paramasivam</t>
         </is>
       </c>
       <c r="D43" s="32" t="inlineStr">
@@ -6290,12 +6618,12 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>LWD of 30 Sep 2026 has passed, so he is already out.</t>
+          <t>E-mail differs between sources: the row gives gangasri.p@gmail.com, the CV says p.gangasri@gmail.com.</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Confirm current status and availability.</t>
+          <t>Confirm which address reaches her before sending anything.</t>
         </is>
       </c>
       <c r="G43" s="20" t="n"/>
@@ -6304,29 +6632,27 @@
       <c r="A44" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="11" t="n">
+        <v>20</v>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Pipeline-wide</t>
-        </is>
-      </c>
-      <c r="D44" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Gunavadhi A S</t>
+        </is>
+      </c>
+      <c r="D44" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>The commercials missing for SL 18–22 have now arrived with the IKrux row of 5 Sep 2026, which also added Monish Kanna Bommuraj.</t>
+          <t>Tech Mahindra engagement is listed as ending August 2026, so she has been out around two months.</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Closed. Note the 5 Sep batch predates the 21 Sep one, so those six were submitted first.</t>
+          <t>Confirm current status and availability.</t>
         </is>
       </c>
       <c r="G44" s="20" t="n"/>
@@ -6335,29 +6661,27 @@
       <c r="A45" s="11" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="11" t="n">
+        <v>21</v>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Pipeline-wide</t>
-        </is>
-      </c>
-      <c r="D45" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Dhachanamoorthy N</t>
+        </is>
+      </c>
+      <c r="D45" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>All 22 resumes are on file and checked — 17 against their submitted row, and 5 that arrived as resumes only.</t>
+          <t>Five years total experience against an architecture-heavy Round 1 — a strong engineer, but the theory set will stretch him.</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Closed. Seventeen of the 22 carry a correction or an open question — see the items below.</t>
+          <t>Decide whether to score him against the mid-level bar or treat the gaps as expected.</t>
         </is>
       </c>
       <c r="G45" s="20" t="n"/>
@@ -6367,26 +6691,26 @@
         <v>42</v>
       </c>
       <c r="B46" s="11" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Amre Binnaz. M</t>
-        </is>
-      </c>
-      <c r="D46" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Krishnan K</t>
+        </is>
+      </c>
+      <c r="D46" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>‘AI : 0.6 Months’ is ambiguous and describes AI-assisted coding, not AI engineering.</t>
+          <t>Out of employment around four months, and the dates disagree: the vendor row says LWD 5 June 2026, the CV says the Wipro engagement ran to 25 June 2026.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Restate the AI entry in the units the rest of the sheet uses.</t>
+          <t>Pin down the actual exit date and the reason for the break.</t>
         </is>
       </c>
       <c r="G46" s="20" t="n"/>
@@ -6396,26 +6720,26 @@
         <v>43</v>
       </c>
       <c r="B47" s="11" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Amre Binnaz. M</t>
-        </is>
-      </c>
-      <c r="D47" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Krishnan K</t>
+        </is>
+      </c>
+      <c r="D47" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>The CV carries no education section.</t>
+          <t>The vendor row says Coimbatore; his CV address is Madurai.</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Collect the qualification.</t>
+          <t>Confirm where he is actually based and his willingness to be in Coimbatore.</t>
         </is>
       </c>
       <c r="G47" s="20" t="n"/>
@@ -6425,26 +6749,26 @@
         <v>44</v>
       </c>
       <c r="B48" s="11" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Navin Kumar</t>
-        </is>
-      </c>
-      <c r="D48" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Monish Kanna Bommuraj</t>
+        </is>
+      </c>
+      <c r="D48" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Address reads Tamil Nadu 638701, which is Erode, not Coimbatore; the Nagarro role is remote.</t>
+          <t>LWD of 30 Sep 2026 has passed, so he is already out.</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Confirm his base and his willingness to work onsite.</t>
+          <t>Confirm current status and availability.</t>
         </is>
       </c>
       <c r="G48" s="20" t="n"/>
@@ -6454,26 +6778,26 @@
         <v>45</v>
       </c>
       <c r="B49" s="11" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Vaisakh P</t>
-        </is>
-      </c>
-      <c r="D49" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Saravana Kumar B</t>
+        </is>
+      </c>
+      <c r="D49" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Two employment gaps: Mar to Aug 2017, and Dec 2019 to Jul 2020.</t>
+          <t>Out of employment around four months — InFynd ended June 2026.</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Ask him to account for both.</t>
+          <t>Confirm current status and the reason for the break.</t>
         </is>
       </c>
       <c r="G49" s="20" t="n"/>
@@ -6483,26 +6807,26 @@
         <v>46</v>
       </c>
       <c r="B50" s="11" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>Sandhosh Kumar</t>
-        </is>
-      </c>
-      <c r="D50" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Saravana Kumar B</t>
+        </is>
+      </c>
+      <c r="D50" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Early career was PHP and LAMP, which the recorded skill split does not mention.</t>
+          <t>The row credits Backend Node.js at 5 years; the CV lists Node only in a skills line, and his hands-on work was Python, Java and Selenium up to 2020.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Add it for completeness.</t>
+          <t>Restate the Node claim, and decide whether this role needs hands-on backend depth at all.</t>
         </is>
       </c>
       <c r="G50" s="20" t="n"/>
@@ -6512,26 +6836,26 @@
         <v>47</v>
       </c>
       <c r="B51" s="11" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Manoj</t>
-        </is>
-      </c>
-      <c r="D51" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Veena Kuppusamy</t>
+        </is>
+      </c>
+      <c r="D51" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Location recorded as ‘Bangalore / Coimbatore’.</t>
+          <t>The row credits 10 years as Technical Project Manager; her PM and TPM titles start Mar 2022, about four years, with the preceding eight as Technical Lead.</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Record a single current location.</t>
+          <t>Restate the management span.</t>
         </is>
       </c>
       <c r="G51" s="20" t="n"/>
@@ -6540,12 +6864,14 @@
       <c r="A52" s="11" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="11" t="n">
-        <v>16</v>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Shanmuga raja</t>
+          <t>Pipeline-wide</t>
         </is>
       </c>
       <c r="D52" s="33" t="inlineStr">
@@ -6555,12 +6881,12 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>E-mail address was supplied with a leading space.</t>
+          <t>The commercials missing for SL 18–22 have now arrived with the IKrux row of 5 Sep 2026, which also added Monish Kanna Bommuraj.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Corrected here; fix at source so mail merges do not fail.</t>
+          <t>Closed. Note the 5 Sep batch predates the 21 Sep one, so those six were submitted first.</t>
         </is>
       </c>
       <c r="G52" s="20" t="n"/>
@@ -6569,12 +6895,14 @@
       <c r="A53" s="11" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="11" t="n">
-        <v>18</v>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Prince Kumar P</t>
+          <t>Pipeline-wide</t>
         </is>
       </c>
       <c r="D53" s="33" t="inlineStr">
@@ -6584,12 +6912,12 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Project dates overlap: Discern runs Jan 2016 to Dec 2020 while Treselle ends Jan 2020 and Virtusa starts the same month.</t>
+          <t>All 22 resumes are on file and checked — 17 against their submitted row, and 5 that arrived as resumes only.</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Ask him to clarify the overlap.</t>
+          <t>Closed. Seventeen of the 22 carry a correction or an open question — see the items below.</t>
         </is>
       </c>
       <c r="G53" s="20" t="n"/>
@@ -6599,11 +6927,11 @@
         <v>50</v>
       </c>
       <c r="B54" s="11" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Gunavadhi A S</t>
+          <t>Amre Binnaz. M</t>
         </is>
       </c>
       <c r="D54" s="33" t="inlineStr">
@@ -6613,12 +6941,12 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>MCA is recorded as coursework completed rather than awarded; the completed degree is a B.Sc.</t>
+          <t>‘AI : 0.6 Months’ is ambiguous and describes AI-assisted coding, not AI engineering.</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Confirm the highest qualification actually held.</t>
+          <t>Restate the AI entry in the units the rest of the sheet uses.</t>
         </is>
       </c>
       <c r="G54" s="20" t="n"/>
@@ -6628,11 +6956,11 @@
         <v>51</v>
       </c>
       <c r="B55" s="11" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Dhachanamoorthy N</t>
+          <t>Amre Binnaz. M</t>
         </is>
       </c>
       <c r="D55" s="33" t="inlineStr">
@@ -6642,12 +6970,12 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>The CV states no location; the vendor row gives Coimbatore.</t>
+          <t>The CV carries no education section.</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Closed by the 5 Sep row — confirm verbally at screening.</t>
+          <t>Collect the qualification.</t>
         </is>
       </c>
       <c r="G55" s="20" t="n"/>
@@ -6657,11 +6985,11 @@
         <v>52</v>
       </c>
       <c r="B56" s="11" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>Krishnan K</t>
+          <t>Navin Kumar</t>
         </is>
       </c>
       <c r="D56" s="33" t="inlineStr">
@@ -6671,12 +6999,12 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Degree is BE Electrical and Electronics rather than computer science, and the CV is list-heavy with thin description of personal contribution.</t>
+          <t>Address reads Tamil Nadu 638701, which is Erode, not Coimbatore; the Nagarro role is remote.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Probe for what he personally designed and built in the technical round.</t>
+          <t>Confirm his base and his willingness to work onsite.</t>
         </is>
       </c>
       <c r="G56" s="20" t="n"/>
@@ -6686,11 +7014,11 @@
         <v>53</v>
       </c>
       <c r="B57" s="11" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Monish Kanna Bommuraj</t>
+          <t>Vaisakh P</t>
         </is>
       </c>
       <c r="D57" s="33" t="inlineStr">
@@ -6700,12 +7028,12 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>The row credits React: 2+ Years; the CV mentions React once, on a single pharmacy application.</t>
+          <t>Two employment gaps: Mar to Aug 2017, and Dec 2019 to Jul 2020.</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Verify the React depth if the role needs front-end work.</t>
+          <t>Ask him to account for both.</t>
         </is>
       </c>
       <c r="G57" s="20" t="n"/>
@@ -6715,29 +7043,290 @@
         <v>54</v>
       </c>
       <c r="B58" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>Sandhosh Kumar</t>
+        </is>
+      </c>
+      <c r="D58" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Early career was PHP and LAMP, which the recorded skill split does not mention.</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Add it for completeness.</t>
+        </is>
+      </c>
+      <c r="G58" s="20" t="n"/>
+    </row>
+    <row r="59" ht="44" customHeight="1">
+      <c r="A59" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>Manoj</t>
+        </is>
+      </c>
+      <c r="D59" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Location recorded as ‘Bangalore / Coimbatore’.</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Record a single current location.</t>
+        </is>
+      </c>
+      <c r="G59" s="20" t="n"/>
+    </row>
+    <row r="60" ht="44" customHeight="1">
+      <c r="A60" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>Shanmuga raja</t>
+        </is>
+      </c>
+      <c r="D60" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>E-mail address was supplied with a leading space.</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Corrected here; fix at source so mail merges do not fail.</t>
+        </is>
+      </c>
+      <c r="G60" s="20" t="n"/>
+    </row>
+    <row r="61" ht="44" customHeight="1">
+      <c r="A61" s="11" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>Prince Kumar P</t>
+        </is>
+      </c>
+      <c r="D61" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Project dates overlap: Discern runs Jan 2016 to Dec 2020 while Treselle ends Jan 2020 and Virtusa starts the same month.</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Ask him to clarify the overlap.</t>
+        </is>
+      </c>
+      <c r="G61" s="20" t="n"/>
+    </row>
+    <row r="62" ht="44" customHeight="1">
+      <c r="A62" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>Gunavadhi A S</t>
+        </is>
+      </c>
+      <c r="D62" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>MCA is recorded as coursework completed rather than awarded; the completed degree is a B.Sc.</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>Confirm the highest qualification actually held.</t>
+        </is>
+      </c>
+      <c r="G62" s="20" t="n"/>
+    </row>
+    <row r="63" ht="44" customHeight="1">
+      <c r="A63" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>Dhachanamoorthy N</t>
+        </is>
+      </c>
+      <c r="D63" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>The CV states no location; the vendor row gives Coimbatore.</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>Closed by the 5 Sep row — confirm verbally at screening.</t>
+        </is>
+      </c>
+      <c r="G63" s="20" t="n"/>
+    </row>
+    <row r="64" ht="44" customHeight="1">
+      <c r="A64" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>Krishnan K</t>
+        </is>
+      </c>
+      <c r="D64" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Degree is BE Electrical and Electronics rather than computer science, and the CV is list-heavy with thin description of personal contribution.</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>Probe for what he personally designed and built in the technical round.</t>
+        </is>
+      </c>
+      <c r="G64" s="20" t="n"/>
+    </row>
+    <row r="65" ht="44" customHeight="1">
+      <c r="A65" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="C58" s="12" t="inlineStr">
+      <c r="C65" s="12" t="inlineStr">
         <is>
           <t>Monish Kanna Bommuraj</t>
         </is>
       </c>
-      <c r="D58" s="33" t="inlineStr">
+      <c r="D65" s="33" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>The row credits React: 2+ Years; the CV mentions React once, on a single pharmacy application.</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Verify the React depth if the role needs front-end work.</t>
+        </is>
+      </c>
+      <c r="G65" s="20" t="n"/>
+    </row>
+    <row r="66" ht="44" customHeight="1">
+      <c r="A66" s="11" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>Monish Kanna Bommuraj</t>
+        </is>
+      </c>
+      <c r="D66" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>Accenture is his only employer across all five years, and the degree is B.E. Mechatronics rather than computer science.</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t>Probe adaptability outside a single engineering culture; the CGPA of 8.97 and the Azure certification offset the degree.</t>
         </is>
       </c>
-      <c r="G58" s="20" t="n"/>
+      <c r="G66" s="20" t="n"/>
+    </row>
+    <row r="67" ht="44" customHeight="1">
+      <c r="A67" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>Veena Kuppusamy</t>
+        </is>
+      </c>
+      <c r="D67" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Her CV opens with personal details including religion and marital status.</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>Brief the panel to disregard protected characteristics; assess on the professional record only.</t>
+        </is>
+      </c>
+      <c r="G67" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6745,7 +7334,7 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In Progress,Closed,Not Applicable"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9008,7 +9597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -12941,8 +13530,344 @@
       </c>
       <c r="H165" s="39" t="n"/>
     </row>
+    <row r="166" ht="108" customHeight="1">
+      <c r="A166" s="36" t="n">
+        <v>24</v>
+      </c>
+      <c r="B166" s="37" t="inlineStr">
+        <is>
+          <t>Saravana Kumar B</t>
+        </is>
+      </c>
+      <c r="C166" s="38" t="inlineStr">
+        <is>
+          <t>Node / JS</t>
+        </is>
+      </c>
+      <c r="D166" s="36" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>System design patterns</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>Explain CQRS. What problem does it solve, and what does it cost you?</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>Command Query Responsibility Segregation splits the write model from the read model so each can be shaped for its own job — writes enforce invariants and stay normalised, reads are denormalised and shaped for the screen that needs them. It pays off when read and write loads differ sharply, when reads need many different projections, or when write-side validation is complex. The cost is two models to keep in step: if the read side is updated asynchronously you inherit eventual consistency, so the UI must tolerate reading its own write late, and you need a rebuild path for projections.</t>
+        </is>
+      </c>
+      <c r="H166" s="39" t="n"/>
+    </row>
+    <row r="167" ht="108" customHeight="1">
+      <c r="A167" s="40" t="n"/>
+      <c r="B167" s="40" t="n"/>
+      <c r="C167" s="40" t="n"/>
+      <c r="D167" s="40" t="n"/>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>Integration patterns</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>Two services must stay in step. Walk me through choosing between a synchronous API call, a message queue, and a shared database.</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>A synchronous call is simplest and gives an immediate answer, but couples availability — if the callee is down the caller fails — so it suits a read the caller cannot proceed without. A queue decouples availability and smooths spikes, at the cost of eventual consistency and at-least-once delivery the consumer must handle idempotently; it suits work that can complete later. A shared database is the one to avoid: it couples the two through a schema nobody owns, so neither can change independently and a bad query in one takes down the other.</t>
+        </is>
+      </c>
+      <c r="H167" s="39" t="n"/>
+    </row>
+    <row r="168" ht="108" customHeight="1">
+      <c r="A168" s="40" t="n"/>
+      <c r="B168" s="40" t="n"/>
+      <c r="C168" s="40" t="n"/>
+      <c r="D168" s="40" t="n"/>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>Security considerations</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>Explain the difference between authentication and authorisation, and where each belongs in a microservices setup.</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>Authentication establishes who the caller is; authorisation decides what that identity may do. Authentication is best done once at the edge — the gateway or an identity provider — issuing a signed token the services can validate without a round trip. Authorisation cannot live only at the edge, because only the service owning a resource knows whether this user may touch this record; the gateway can do coarse checks, the service must do the fine-grained one. Services validate the token's signature, issuer, audience and expiry locally rather than calling the identity provider per request.</t>
+        </is>
+      </c>
+      <c r="H168" s="39" t="n"/>
+    </row>
+    <row r="169" ht="108" customHeight="1">
+      <c r="A169" s="40" t="n"/>
+      <c r="B169" s="40" t="n"/>
+      <c r="C169" s="40" t="n"/>
+      <c r="D169" s="40" t="n"/>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>Scalability</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>Vertical versus horizontal scaling — and what has to be true of your application before horizontal works?</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>Vertical means a bigger machine: simple, no code change, but bounded by the largest instance and a single point of failure. Horizontal means more instances behind a load balancer: effectively unbounded and more resilient, but it demands the application be stateless — no in-memory session, no local file writes, no in-process cache assumed to be shared, no singleton scheduler that must run once. State moves to a distributed cache, a database or object storage; scheduled work needs a leader election or a distributed lock so it runs once across the fleet.</t>
+        </is>
+      </c>
+      <c r="H169" s="39" t="n"/>
+    </row>
+    <row r="170" ht="108" customHeight="1">
+      <c r="A170" s="40" t="n"/>
+      <c r="B170" s="40" t="n"/>
+      <c r="C170" s="40" t="n"/>
+      <c r="D170" s="40" t="n"/>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>Multi-tenancy</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>Describe the models for multi-tenant data isolation and the trade-offs between them.</t>
+        </is>
+      </c>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>Three broadly. Database per tenant gives the strongest isolation, simple per-tenant backup and restore, and easy noisy-neighbour control, but cost and operational effort grow with tenant count and schema migrations must run everywhere. Schema per tenant within one database is a middle ground with moderate isolation and fewer instances. Shared schema with a tenant ID column on every row is cheapest and scales to many small tenants, but isolation is entirely enforced by code, so one missing WHERE clause is a cross-tenant data leak. Many products mix them — shared for small tenants, dedicated for large or regulated ones.</t>
+        </is>
+      </c>
+      <c r="H170" s="39" t="n"/>
+    </row>
+    <row r="171" ht="108" customHeight="1">
+      <c r="A171" s="40" t="n"/>
+      <c r="B171" s="40" t="n"/>
+      <c r="C171" s="40" t="n"/>
+      <c r="D171" s="40" t="n"/>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>What does a good CI/CD pipeline do, and what belongs in CI as opposed to CD?</t>
+        </is>
+      </c>
+      <c r="G171" s="4" t="inlineStr">
+        <is>
+          <t>CI runs on every commit and protects the main branch: build, unit and integration tests, static analysis, dependency and secret scanning, and producing one immutable versioned artifact. CD takes that same artifact and promotes it through environments with configuration injected per environment — never rebuilding per environment, because then you deployed something you did not test. Deployment should be repeatable and reversible: automated, with a health check gate, and a rollback that is a tested path rather than a hope. Anything slow or flaky belongs outside the commit gate, or it trains people to ignore red builds.</t>
+        </is>
+      </c>
+      <c r="H171" s="39" t="n"/>
+    </row>
+    <row r="172" ht="108" customHeight="1">
+      <c r="A172" s="41" t="n"/>
+      <c r="B172" s="41" t="n"/>
+      <c r="C172" s="41" t="n"/>
+      <c r="D172" s="41" t="n"/>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>Monolith or microservices — how do you decide, and what does microservices cost?</t>
+        </is>
+      </c>
+      <c r="G172" s="4" t="inlineStr">
+        <is>
+          <t>A well-structured monolith is the right default: one deployment, in-process calls, easy transactions and refactoring. Microservices buy independent deployment, independent scaling and team autonomy, and they are worth it when teams are blocked on each other's release cycles or when parts of the system have genuinely different scaling or availability needs. The cost is real: network calls that fail, distributed transactions replaced by sagas and eventual consistency, distributed tracing to debug anything, versioned contracts, and much heavier operations. Splitting a domain you do not yet understand produces a distributed monolith — all the cost, none of the independence.</t>
+        </is>
+      </c>
+      <c r="H172" s="39" t="n"/>
+    </row>
+    <row r="173" ht="108" customHeight="1">
+      <c r="A173" s="36" t="n">
+        <v>25</v>
+      </c>
+      <c r="B173" s="37" t="inlineStr">
+        <is>
+          <t>Veena Kuppusamy</t>
+        </is>
+      </c>
+      <c r="C173" s="38" t="inlineStr">
+        <is>
+          <t>.NET</t>
+        </is>
+      </c>
+      <c r="D173" s="36" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>System design patterns</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>Explain CQRS. What problem does it solve, and what does it cost you?</t>
+        </is>
+      </c>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t>Command Query Responsibility Segregation splits the write model from the read model so each can be shaped for its own job — writes enforce invariants and stay normalised, reads are denormalised and shaped for the screen that needs them. It pays off when read and write loads differ sharply, when reads need many different projections, or when write-side validation is complex. The cost is two models to keep in step: if the read side is updated asynchronously you inherit eventual consistency, so the UI must tolerate reading its own write late, and you need a rebuild path for projections.</t>
+        </is>
+      </c>
+      <c r="H173" s="39" t="n"/>
+    </row>
+    <row r="174" ht="108" customHeight="1">
+      <c r="A174" s="40" t="n"/>
+      <c r="B174" s="40" t="n"/>
+      <c r="C174" s="40" t="n"/>
+      <c r="D174" s="40" t="n"/>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>Integration patterns</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>Two services must stay in step. Walk me through choosing between a synchronous API call, a message queue, and a shared database.</t>
+        </is>
+      </c>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t>A synchronous call is simplest and gives an immediate answer, but couples availability — if the callee is down the caller fails — so it suits a read the caller cannot proceed without. A queue decouples availability and smooths spikes, at the cost of eventual consistency and at-least-once delivery the consumer must handle idempotently; it suits work that can complete later. A shared database is the one to avoid: it couples the two through a schema nobody owns, so neither can change independently and a bad query in one takes down the other.</t>
+        </is>
+      </c>
+      <c r="H174" s="39" t="n"/>
+    </row>
+    <row r="175" ht="108" customHeight="1">
+      <c r="A175" s="40" t="n"/>
+      <c r="B175" s="40" t="n"/>
+      <c r="C175" s="40" t="n"/>
+      <c r="D175" s="40" t="n"/>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>Security considerations</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>Explain the difference between authentication and authorisation, and where each belongs in a microservices setup.</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>Authentication establishes who the caller is; authorisation decides what that identity may do. Authentication is best done once at the edge — the gateway or an identity provider — issuing a signed token the services can validate without a round trip. Authorisation cannot live only at the edge, because only the service owning a resource knows whether this user may touch this record; the gateway can do coarse checks, the service must do the fine-grained one. Services validate the token's signature, issuer, audience and expiry locally rather than calling the identity provider per request.</t>
+        </is>
+      </c>
+      <c r="H175" s="39" t="n"/>
+    </row>
+    <row r="176" ht="108" customHeight="1">
+      <c r="A176" s="40" t="n"/>
+      <c r="B176" s="40" t="n"/>
+      <c r="C176" s="40" t="n"/>
+      <c r="D176" s="40" t="n"/>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>Scalability</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>Vertical versus horizontal scaling — and what has to be true of your application before horizontal works?</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>Vertical means a bigger machine: simple, no code change, but bounded by the largest instance and a single point of failure. Horizontal means more instances behind a load balancer: effectively unbounded and more resilient, but it demands the application be stateless — no in-memory session, no local file writes, no in-process cache assumed to be shared, no singleton scheduler that must run once. State moves to a distributed cache, a database or object storage; scheduled work needs a leader election or a distributed lock so it runs once across the fleet.</t>
+        </is>
+      </c>
+      <c r="H176" s="39" t="n"/>
+    </row>
+    <row r="177" ht="108" customHeight="1">
+      <c r="A177" s="40" t="n"/>
+      <c r="B177" s="40" t="n"/>
+      <c r="C177" s="40" t="n"/>
+      <c r="D177" s="40" t="n"/>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>Multi-tenancy</t>
+        </is>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>Describe the models for multi-tenant data isolation and the trade-offs between them.</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>Three broadly. Database per tenant gives the strongest isolation, simple per-tenant backup and restore, and easy noisy-neighbour control, but cost and operational effort grow with tenant count and schema migrations must run everywhere. Schema per tenant within one database is a middle ground with moderate isolation and fewer instances. Shared schema with a tenant ID column on every row is cheapest and scales to many small tenants, but isolation is entirely enforced by code, so one missing WHERE clause is a cross-tenant data leak. Many products mix them — shared for small tenants, dedicated for large or regulated ones.</t>
+        </is>
+      </c>
+      <c r="H177" s="39" t="n"/>
+    </row>
+    <row r="178" ht="108" customHeight="1">
+      <c r="A178" s="40" t="n"/>
+      <c r="B178" s="40" t="n"/>
+      <c r="C178" s="40" t="n"/>
+      <c r="D178" s="40" t="n"/>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>What does a good CI/CD pipeline do, and what belongs in CI as opposed to CD?</t>
+        </is>
+      </c>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>CI runs on every commit and protects the main branch: build, unit and integration tests, static analysis, dependency and secret scanning, and producing one immutable versioned artifact. CD takes that same artifact and promotes it through environments with configuration injected per environment — never rebuilding per environment, because then you deployed something you did not test. Deployment should be repeatable and reversible: automated, with a health check gate, and a rollback that is a tested path rather than a hope. Anything slow or flaky belongs outside the commit gate, or it trains people to ignore red builds.</t>
+        </is>
+      </c>
+      <c r="H178" s="39" t="n"/>
+    </row>
+    <row r="179" ht="108" customHeight="1">
+      <c r="A179" s="41" t="n"/>
+      <c r="B179" s="41" t="n"/>
+      <c r="C179" s="41" t="n"/>
+      <c r="D179" s="41" t="n"/>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>Monolith or microservices — how do you decide, and what does microservices cost?</t>
+        </is>
+      </c>
+      <c r="G179" s="4" t="inlineStr">
+        <is>
+          <t>A well-structured monolith is the right default: one deployment, in-process calls, easy transactions and refactoring. Microservices buy independent deployment, independent scaling and team autonomy, and they are worth it when teams are blocked on each other's release cycles or when parts of the system have genuinely different scaling or availability needs. The cost is real: network calls that fail, distributed transactions replaced by sagas and eventual consistency, distributed tracing to debug anything, versioned contracts, and much heavier operations. Splitting a domain you do not yet understand produces a distributed monolith — all the cost, none of the independence.</t>
+        </is>
+      </c>
+      <c r="H179" s="39" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="94">
+  <mergeCells count="102">
     <mergeCell ref="A12:A18"/>
     <mergeCell ref="C12:C18"/>
     <mergeCell ref="C61:C67"/>
@@ -12951,7 +13876,9 @@
     <mergeCell ref="B33:B39"/>
     <mergeCell ref="D33:D39"/>
     <mergeCell ref="A159:A165"/>
+    <mergeCell ref="B173:B179"/>
     <mergeCell ref="C159:C165"/>
+    <mergeCell ref="D173:D179"/>
     <mergeCell ref="A96:A102"/>
     <mergeCell ref="B75:B81"/>
     <mergeCell ref="D19:D25"/>
@@ -12965,6 +13892,8 @@
     <mergeCell ref="C26:C32"/>
     <mergeCell ref="A124:A130"/>
     <mergeCell ref="C124:C130"/>
+    <mergeCell ref="B166:B172"/>
+    <mergeCell ref="D166:D172"/>
     <mergeCell ref="C117:C123"/>
     <mergeCell ref="B103:B109"/>
     <mergeCell ref="D103:D109"/>
@@ -12993,6 +13922,7 @@
     <mergeCell ref="D61:D67"/>
     <mergeCell ref="C40:C46"/>
     <mergeCell ref="D47:D53"/>
+    <mergeCell ref="C173:C179"/>
     <mergeCell ref="A33:A39"/>
     <mergeCell ref="B54:B60"/>
     <mergeCell ref="D54:D60"/>
@@ -13003,7 +13933,9 @@
     <mergeCell ref="D159:D165"/>
     <mergeCell ref="D40:D46"/>
     <mergeCell ref="A110:A116"/>
+    <mergeCell ref="A166:A172"/>
     <mergeCell ref="A61:A67"/>
+    <mergeCell ref="C166:C172"/>
     <mergeCell ref="B96:B102"/>
     <mergeCell ref="C75:C81"/>
     <mergeCell ref="A103:A109"/>
@@ -13032,6 +13964,7 @@
     <mergeCell ref="B110:B116"/>
     <mergeCell ref="D110:D116"/>
     <mergeCell ref="B47:B53"/>
+    <mergeCell ref="A173:A179"/>
     <mergeCell ref="D96:D102"/>
     <mergeCell ref="C89:C95"/>
     <mergeCell ref="C5:C11"/>
@@ -13039,7 +13972,7 @@
     <mergeCell ref="B152:B158"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H165" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="H5:H179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
@@ -13054,7 +13987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -13086,7 +14019,7 @@
         </is>
       </c>
       <c r="B4" s="43" t="n">
-        <v>46303</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="5">
@@ -13096,8 +14029,8 @@
         </is>
       </c>
       <c r="B5" s="11">
-        <f>COUNTA('Interview Inventory'!$A$3:$A$25)</f>
-        <v>23</v>
+        <f>COUNTA('Interview Inventory'!$A$3:$A$27)</f>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -13146,23 +14079,23 @@
         </is>
       </c>
       <c r="B9" s="11">
-        <f>COUNTIF('Interview Inventory'!$D$3:$D$25,A9)</f>
+        <f>COUNTIF('Interview Inventory'!$D$3:$D$27,A9)</f>
         <v>7</v>
       </c>
       <c r="C9" s="15">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$25,A9,'Interview Inventory'!$N$3:$N$25),"")</f>
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A9,'Interview Inventory'!$N$3:$N$27),"")</f>
         <v>9.8885714286</v>
       </c>
       <c r="D9" s="15">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$25,A9,'Interview Inventory'!$O$3:$O$25),"")</f>
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A9,'Interview Inventory'!$O$3:$O$27),"")</f>
         <v>15.8571428571</v>
       </c>
       <c r="E9" s="16">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$25,A9,'Interview Inventory'!$Q$3:$Q$25),"")</f>
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A9,'Interview Inventory'!$Q$3:$Q$27),"")</f>
         <v>0.6679520583</v>
       </c>
       <c r="F9" s="15">
-        <f>_xlfn.MAXIFS('Interview Inventory'!$O$3:$O$25,'Interview Inventory'!$D$3:$D$25,A9)</f>
+        <f>_xlfn.MAXIFS('Interview Inventory'!$O$3:$O$27,'Interview Inventory'!$D$3:$D$27,A9)</f>
         <v>25</v>
       </c>
     </row>
@@ -13173,401 +14106,439 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>COUNTIF('Interview Inventory'!$D$3:$D$25,A10)</f>
+        <f>COUNTIF('Interview Inventory'!$D$3:$D$27,A10)</f>
         <v>9</v>
       </c>
       <c r="C10" s="15">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$25,A10,'Interview Inventory'!$N$3:$N$25),"")</f>
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A10,'Interview Inventory'!$N$3:$N$27),"")</f>
         <v>22.8555555556</v>
       </c>
       <c r="D10" s="15">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$25,A10,'Interview Inventory'!$O$3:$O$25),"")</f>
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A10,'Interview Inventory'!$O$3:$O$27),"")</f>
         <v>29.4444444444</v>
       </c>
       <c r="E10" s="16">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$25,A10,'Interview Inventory'!$Q$3:$Q$25),"")</f>
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A10,'Interview Inventory'!$Q$3:$Q$27),"")</f>
         <v>0.3315765374</v>
       </c>
       <c r="F10" s="15">
-        <f>_xlfn.MAXIFS('Interview Inventory'!$O$3:$O$25,'Interview Inventory'!$D$3:$D$25,A10)</f>
+        <f>_xlfn.MAXIFS('Interview Inventory'!$O$3:$O$27,'Interview Inventory'!$D$3:$D$27,A10)</f>
         <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
+          <t>Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="B11" s="11">
+        <f>COUNTIF('Interview Inventory'!$D$3:$D$27,A11)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="15">
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A11,'Interview Inventory'!$N$3:$N$27),"")</f>
+        <v>14.25</v>
+      </c>
+      <c r="D11" s="15">
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A11,'Interview Inventory'!$O$3:$O$27),"")</f>
+        <v>20.25</v>
+      </c>
+      <c r="E11" s="16">
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A11,'Interview Inventory'!$Q$3:$Q$27),"")</f>
+        <v>0.4275</v>
+      </c>
+      <c r="F11" s="15">
+        <f>_xlfn.MAXIFS('Interview Inventory'!$O$3:$O$27,'Interview Inventory'!$D$3:$D$27,A11)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
           <t>Technology Lead</t>
         </is>
       </c>
-      <c r="B11" s="11">
-        <f>COUNTIF('Interview Inventory'!$D$3:$D$25,A11)</f>
+      <c r="B12" s="11">
+        <f>COUNTIF('Interview Inventory'!$D$3:$D$27,A12)</f>
         <v>7</v>
       </c>
-      <c r="C11" s="15">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$25,A11,'Interview Inventory'!$N$3:$N$25),"")</f>
+      <c r="C12" s="15">
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A12,'Interview Inventory'!$N$3:$N$27),"")</f>
         <v>22.8428571429</v>
       </c>
-      <c r="D11" s="15">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$25,A11,'Interview Inventory'!$O$3:$O$25),"")</f>
+      <c r="D12" s="15">
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A12,'Interview Inventory'!$O$3:$O$27),"")</f>
         <v>31.4285714286</v>
       </c>
-      <c r="E11" s="16">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$25,A11,'Interview Inventory'!$Q$3:$Q$25),"")</f>
+      <c r="E12" s="16">
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A12,'Interview Inventory'!$Q$3:$Q$27),"")</f>
         <v>0.3802691395</v>
       </c>
-      <c r="F11" s="15">
-        <f>_xlfn.MAXIFS('Interview Inventory'!$O$3:$O$25,'Interview Inventory'!$D$3:$D$25,A11)</f>
+      <c r="F12" s="15">
+        <f>_xlfn.MAXIFS('Interview Inventory'!$O$3:$O$27,'Interview Inventory'!$D$3:$D$27,A12)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="42" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="42" t="inlineStr">
         <is>
           <t>All roles</t>
         </is>
       </c>
-      <c r="B12" s="33">
-        <f>COUNTA('Interview Inventory'!$A$3:$A$25)</f>
-        <v>23</v>
-      </c>
-      <c r="C12" s="46">
-        <f>AVERAGE('Interview Inventory'!$N$3:$N$25)</f>
-        <v>18.9052173913</v>
-      </c>
-      <c r="D12" s="46">
-        <f>AVERAGE('Interview Inventory'!$O$3:$O$25)</f>
-        <v>25.9130434783</v>
-      </c>
-      <c r="E12" s="47">
-        <f>AVERAGE('Interview Inventory'!$Q$3:$Q$25)</f>
-        <v>0.4487711835</v>
-      </c>
-      <c r="F12" s="46">
-        <f>MAX('Interview Inventory'!$O$3:$O$25)</f>
+      <c r="B13" s="33">
+        <f>COUNTA('Interview Inventory'!$A$3:$A$27)</f>
+        <v>25</v>
+      </c>
+      <c r="C13" s="46">
+        <f>AVERAGE('Interview Inventory'!$N$3:$N$27)</f>
+        <v>18.5328</v>
+      </c>
+      <c r="D13" s="46">
+        <f>AVERAGE('Interview Inventory'!$O$3:$O$27)</f>
+        <v>25.46</v>
+      </c>
+      <c r="E13" s="47">
+        <f>AVERAGE('Interview Inventory'!$Q$3:$Q$27)</f>
+        <v>0.4470694889</v>
+      </c>
+      <c r="F13" s="46">
+        <f>MAX('Interview Inventory'!$O$3:$O$27)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="45" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="45" t="inlineStr">
         <is>
           <t>Availability against the as-on date</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Candidates</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>% of pipeline</t>
         </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>Last working day already passed</t>
-        </is>
-      </c>
-      <c r="B16" s="11">
-        <f>COUNTIF('Interview Inventory'!$T$3:$T$25,"Available now")</f>
-        <v>18</v>
-      </c>
-      <c r="C16" s="16">
-        <f>IFERROR(B16/$B$5,"")</f>
-        <v>0.7826086957</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>Within 30 days</t>
+          <t>Last working day already passed</t>
         </is>
       </c>
       <c r="B17" s="11">
-        <f>COUNTIF('Interview Inventory'!$T$3:$T$25,"Within 30 days")</f>
-        <v>4</v>
+        <f>COUNTIF('Interview Inventory'!$T$3:$T$27,"Available now")</f>
+        <v>22</v>
       </c>
       <c r="C17" s="16">
         <f>IFERROR(B17/$B$5,"")</f>
-        <v>0.1739130435</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>Beyond 30 days</t>
+          <t>Within 30 days</t>
         </is>
       </c>
       <c r="B18" s="11">
-        <f>COUNTIF('Interview Inventory'!$T$3:$T$25,"Beyond 30 days")</f>
-        <v>0</v>
+        <f>COUNTIF('Interview Inventory'!$T$3:$T$27,"Within 30 days")</f>
+        <v>2</v>
       </c>
       <c r="C18" s="16">
         <f>IFERROR(B18/$B$5,"")</f>
-        <v>0.0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>Notice period stated, no exit date</t>
+          <t>Beyond 30 days</t>
         </is>
       </c>
       <c r="B19" s="11">
-        <f>COUNTIF('Interview Inventory'!$T$3:$T$25,"Notice period only")</f>
-        <v>1</v>
+        <f>COUNTIF('Interview Inventory'!$T$3:$T$27,"Beyond 30 days")</f>
+        <v>0</v>
       </c>
       <c r="C19" s="16">
         <f>IFERROR(B19/$B$5,"")</f>
-        <v>0.0434782609</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Notice not captured</t>
+          <t>Notice period stated, no exit date</t>
         </is>
       </c>
       <c r="B20" s="11">
-        <f>COUNTIF('Interview Inventory'!$T$3:$T$25,"Not captured")</f>
-        <v>0</v>
+        <f>COUNTIF('Interview Inventory'!$T$3:$T$27,"Notice period only")</f>
+        <v>1</v>
       </c>
       <c r="C20" s="16">
         <f>IFERROR(B20/$B$5,"")</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Notice not captured</t>
+        </is>
+      </c>
+      <c r="B21" s="11">
+        <f>COUNTIF('Interview Inventory'!$T$3:$T$27,"Not captured")</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="16">
+        <f>IFERROR(B21/$B$5,"")</f>
         <v>0.0</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="45" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="45" t="inlineStr">
         <is>
           <t>Batch, commercials, offers and flags</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Measure</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>Submitted 5 Sep 2026</t>
-        </is>
-      </c>
-      <c r="B24" s="11">
-        <f>COUNTIF('Interview Inventory'!$C$3:$C$25,"5-Sep-2026")</f>
-        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>Submitted 21 Sep 2026</t>
+          <t>Submitted 5 Sep 2026</t>
         </is>
       </c>
       <c r="B25" s="11">
-        <f>COUNTIF('Interview Inventory'!$C$3:$C$25,"21-Sep-2026")</f>
-        <v>17</v>
+        <f>COUNTIF('Interview Inventory'!$C$3:$C$27,"5-Sep-2026")</f>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>CTC and ECTC captured</t>
+          <t>Submitted 21 Sep 2026</t>
         </is>
       </c>
       <c r="B26" s="11">
-        <f>COUNT('Interview Inventory'!$N$3:$N$25)</f>
-        <v>23</v>
+        <f>COUNTIF('Interview Inventory'!$C$3:$C$27,"21-Sep-2026")</f>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>Commercials not yet captured</t>
+          <t>Submitted 8 Oct 2026</t>
         </is>
       </c>
       <c r="B27" s="11">
-        <f>$B$5-COUNT('Interview Inventory'!$N$3:$N$25)</f>
-        <v>0</v>
+        <f>COUNTIF('Interview Inventory'!$C$3:$C$27,"8-Oct-2026")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>Holding a competing offer</t>
+          <t>CTC and ECTC captured</t>
         </is>
       </c>
       <c r="B28" s="11">
-        <f>$B$5-COUNTIF('Interview Inventory'!$P$3:$P$25,"No")-COUNTIF('Interview Inventory'!$P$3:$P$25,"Not captured")</f>
-        <v>4</v>
+        <f>COUNT('Interview Inventory'!$N$3:$N$27)</f>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>Already in Coimbatore</t>
+          <t>Commercials not yet captured</t>
         </is>
       </c>
       <c r="B29" s="11">
-        <f>COUNTIF('Interview Inventory'!$K$3:$K$25,"Coimbatore")</f>
-        <v>15</v>
+        <f>$B$5-COUNT('Interview Inventory'!$N$3:$N$27)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Carrying a High flag</t>
+          <t>Holding a competing offer</t>
         </is>
       </c>
       <c r="B30" s="11">
-        <f>COUNTIF('Interview Inventory'!$U$3:$U$25,"High")</f>
-        <v>7</v>
+        <f>$B$5-COUNTIF('Interview Inventory'!$P$3:$P$27,"No")-COUNTIF('Interview Inventory'!$P$3:$P$27,"Not captured")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Carrying a Medium flag</t>
+          <t>Already in Coimbatore</t>
         </is>
       </c>
       <c r="B31" s="11">
-        <f>COUNTIF('Interview Inventory'!$U$3:$U$25,"Medium")</f>
-        <v>15</v>
+        <f>COUNTIF('Interview Inventory'!$K$3:$K$27,"Coimbatore")</f>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
+          <t>Carrying a High flag</t>
+        </is>
+      </c>
+      <c r="B32" s="11">
+        <f>COUNTIF('Interview Inventory'!$U$3:$U$27,"High")</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>Carrying a Medium flag</t>
+        </is>
+      </c>
+      <c r="B33" s="11">
+        <f>COUNTIF('Interview Inventory'!$U$3:$U$27,"Medium")</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
           <t>No flags raised</t>
         </is>
       </c>
-      <c r="B32" s="11">
-        <f>COUNTIF('Interview Inventory'!$U$3:$U$25,"None")</f>
+      <c r="B34" s="11">
+        <f>COUNTIF('Interview Inventory'!$U$3:$U$27,"None")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="45" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="45" t="inlineStr">
         <is>
           <t>Interview funnel (fills as the tracking columns are used)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>Shortlisted at screening</t>
-        </is>
-      </c>
-      <c r="B36" s="11">
-        <f>COUNTIF('Interview Inventory'!$Y$3:$Y$25,"Shortlisted")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>Round 1 selected</t>
-        </is>
-      </c>
-      <c r="B37" s="11">
-        <f>COUNTIF('Interview Inventory'!$AB$3:$AB$25,"Selected")</f>
-        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Round 2 selected</t>
+          <t>Shortlisted at screening</t>
         </is>
       </c>
       <c r="B38" s="11">
-        <f>COUNTIF('Interview Inventory'!$AE$3:$AE$25,"Selected")</f>
+        <f>COUNTIF('Interview Inventory'!$Y$3:$Y$27,"Shortlisted")</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>Round 3 selected</t>
+          <t>Round 1 selected</t>
         </is>
       </c>
       <c r="B39" s="11">
-        <f>COUNTIF('Interview Inventory'!$AH$3:$AH$25,"Selected")</f>
+        <f>COUNTIF('Interview Inventory'!$AB$3:$AB$27,"Selected")</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Final round selected</t>
+          <t>Round 2 selected</t>
         </is>
       </c>
       <c r="B40" s="11">
-        <f>COUNTIF('Interview Inventory'!$AK$3:$AK$25,"Selected")</f>
+        <f>COUNTIF('Interview Inventory'!$AE$3:$AE$27,"Selected")</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Offer released</t>
+          <t>Round 3 selected</t>
         </is>
       </c>
       <c r="B41" s="11">
-        <f>COUNTIF('Interview Inventory'!$AN$3:$AN$25,"Yes")</f>
+        <f>COUNTIF('Interview Inventory'!$AH$3:$AH$27,"Selected")</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>Joined</t>
+          <t>Final round selected</t>
         </is>
       </c>
       <c r="B42" s="11">
-        <f>COUNTIF('Interview Inventory'!$AM$3:$AM$25,"Joined")</f>
+        <f>COUNTIF('Interview Inventory'!$AK$3:$AK$27,"Selected")</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
+          <t>Offer released</t>
+        </is>
+      </c>
+      <c r="B43" s="11">
+        <f>COUNTIF('Interview Inventory'!$AN$3:$AN$27,"Yes")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>Joined</t>
+        </is>
+      </c>
+      <c r="B44" s="11">
+        <f>COUNTIF('Interview Inventory'!$AM$3:$AM$27,"Joined")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
           <t>Rejected at any round</t>
         </is>
       </c>
-      <c r="B43" s="11">
-        <f>COUNTIF('Interview Inventory'!$Y$3:$Y$25,"Rejected")+COUNTIF('Interview Inventory'!$AB$3:$AB$25,"Rejected")+COUNTIF('Interview Inventory'!$AE$3:$AE$25,"Rejected")+COUNTIF('Interview Inventory'!$AH$3:$AH$25,"Rejected")+COUNTIF('Interview Inventory'!$AK$3:$AK$25,"Rejected")</f>
+      <c r="B45" s="11">
+        <f>COUNTIF('Interview Inventory'!$Y$3:$Y$27,"Rejected")+COUNTIF('Interview Inventory'!$AB$3:$AB$27,"Rejected")+COUNTIF('Interview Inventory'!$AE$3:$AE$27,"Rejected")+COUNTIF('Interview Inventory'!$AH$3:$AH$27,"Rejected")+COUNTIF('Interview Inventory'!$AK$3:$AK$27,"Rejected")</f>
         <v>0</v>
       </c>
     </row>

--- a/interview/Interview_Inventory.xlsx
+++ b/interview/Interview_Inventory.xlsx
@@ -16,8 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Interview Inventory'!$A$2:$AQ$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Round 1 Question Bank'!$A$4:$G$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Interview Inventory'!$A$2:$AQ$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Round 1 Question Bank'!$A$4:$G$94</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -134,17 +134,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -280,22 +280,22 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -303,10 +303,10 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -315,7 +315,7 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -336,7 +336,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -769,14 +769,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Interview inventory - Certainti hiring, 22 candidates</t>
+          <t>Interview inventory - Certainti hiring, 27 candidates</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rebuilt on 8 Oct 2026 from the same data the Certainti Hiring Portal runs on, so the two cannot drift apart.</t>
+          <t>Rebuilt on 23 Oct 2026 from the same data the Certainti Hiring Portal runs on, so the two cannot drift apart.</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>All 22 candidates: 17 submitted by IKrux Engineering on 21-Sep-2026 and 5 that arrived as resumes on 6-Oct-2026. Every one has a CV on file and a verdict against it.</t>
+          <t>All 27 candidates, every one submitted by IKrux Engineering: 6 on 5-Sep-2026, 17 on 21-Sep-2026, 2 on 8-Oct-2026, 2 on 22-Oct-2026. Each has a CV on file and a verdict against it.</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>46 open items ranked High, Medium then Low, each with the action it needs and a column for owner and status.</t>
+          <t>75 open items ranked High, Medium then Low, each with the action it needs and a column for owner and status.</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>All 62 theory questions with the expected answer and a follow-up to push with. Filter by topic, stream or level.</t>
+          <t>All 90 questions with the expected answer and a follow-up to push with - the engineering theory set and the delivery and process management set. Filter by topic, stream or level.</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>The question each candidate starts on for each of the seven topics, with its expected answer and a score column.</t>
+          <t>The question each candidate starts on for each of their seven topics, with its expected answer and a score column.</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ27"/>
+  <dimension ref="A1:AQ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1319,14 +1319,14 @@
         <v>46310</v>
       </c>
       <c r="S3" s="18" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="T3" s="19" t="inlineStr">
         <is>
-          <t>Within 30 days</t>
-        </is>
-      </c>
-      <c r="U3" s="19" t="inlineStr">
+          <t>Available now</t>
+        </is>
+      </c>
+      <c r="U3" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1334,31 +1334,31 @@
       <c r="V3" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="W3" s="20" t="n"/>
-      <c r="X3" s="21" t="inlineStr">
+      <c r="W3" s="21" t="n"/>
+      <c r="X3" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y3" s="20" t="n"/>
-      <c r="Z3" s="22" t="n"/>
-      <c r="AA3" s="20" t="n"/>
-      <c r="AB3" s="20" t="n"/>
-      <c r="AC3" s="22" t="n"/>
-      <c r="AD3" s="20" t="n"/>
-      <c r="AE3" s="20" t="n"/>
-      <c r="AF3" s="22" t="n"/>
-      <c r="AG3" s="20" t="n"/>
-      <c r="AH3" s="20" t="n"/>
-      <c r="AI3" s="22" t="n"/>
-      <c r="AJ3" s="20" t="n"/>
-      <c r="AK3" s="20" t="n"/>
-      <c r="AL3" s="23" t="n"/>
-      <c r="AM3" s="20" t="n"/>
-      <c r="AN3" s="20" t="n"/>
-      <c r="AO3" s="24" t="n"/>
-      <c r="AP3" s="22" t="n"/>
-      <c r="AQ3" s="20" t="n"/>
+      <c r="Y3" s="21" t="n"/>
+      <c r="Z3" s="23" t="n"/>
+      <c r="AA3" s="21" t="n"/>
+      <c r="AB3" s="21" t="n"/>
+      <c r="AC3" s="23" t="n"/>
+      <c r="AD3" s="21" t="n"/>
+      <c r="AE3" s="21" t="n"/>
+      <c r="AF3" s="23" t="n"/>
+      <c r="AG3" s="21" t="n"/>
+      <c r="AH3" s="21" t="n"/>
+      <c r="AI3" s="23" t="n"/>
+      <c r="AJ3" s="21" t="n"/>
+      <c r="AK3" s="21" t="n"/>
+      <c r="AL3" s="24" t="n"/>
+      <c r="AM3" s="21" t="n"/>
+      <c r="AN3" s="21" t="n"/>
+      <c r="AO3" s="25" t="n"/>
+      <c r="AP3" s="23" t="n"/>
+      <c r="AQ3" s="21" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="11" t="n">
@@ -1442,14 +1442,14 @@
         <v>46269</v>
       </c>
       <c r="S4" s="18" t="n">
-        <v>-40</v>
-      </c>
-      <c r="T4" s="25" t="inlineStr">
+        <v>-49</v>
+      </c>
+      <c r="T4" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
       </c>
-      <c r="U4" s="19" t="inlineStr">
+      <c r="U4" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1457,31 +1457,31 @@
       <c r="V4" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="W4" s="20" t="n"/>
-      <c r="X4" s="21" t="inlineStr">
+      <c r="W4" s="21" t="n"/>
+      <c r="X4" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y4" s="20" t="n"/>
-      <c r="Z4" s="22" t="n"/>
-      <c r="AA4" s="20" t="n"/>
-      <c r="AB4" s="20" t="n"/>
-      <c r="AC4" s="22" t="n"/>
-      <c r="AD4" s="20" t="n"/>
-      <c r="AE4" s="20" t="n"/>
-      <c r="AF4" s="22" t="n"/>
-      <c r="AG4" s="20" t="n"/>
-      <c r="AH4" s="20" t="n"/>
-      <c r="AI4" s="22" t="n"/>
-      <c r="AJ4" s="20" t="n"/>
-      <c r="AK4" s="20" t="n"/>
-      <c r="AL4" s="23" t="n"/>
-      <c r="AM4" s="20" t="n"/>
-      <c r="AN4" s="20" t="n"/>
-      <c r="AO4" s="24" t="n"/>
-      <c r="AP4" s="22" t="n"/>
-      <c r="AQ4" s="20" t="n"/>
+      <c r="Y4" s="21" t="n"/>
+      <c r="Z4" s="23" t="n"/>
+      <c r="AA4" s="21" t="n"/>
+      <c r="AB4" s="21" t="n"/>
+      <c r="AC4" s="23" t="n"/>
+      <c r="AD4" s="21" t="n"/>
+      <c r="AE4" s="21" t="n"/>
+      <c r="AF4" s="23" t="n"/>
+      <c r="AG4" s="21" t="n"/>
+      <c r="AH4" s="21" t="n"/>
+      <c r="AI4" s="23" t="n"/>
+      <c r="AJ4" s="21" t="n"/>
+      <c r="AK4" s="21" t="n"/>
+      <c r="AL4" s="24" t="n"/>
+      <c r="AM4" s="21" t="n"/>
+      <c r="AN4" s="21" t="n"/>
+      <c r="AO4" s="25" t="n"/>
+      <c r="AP4" s="23" t="n"/>
+      <c r="AQ4" s="21" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="11" t="n">
@@ -1565,14 +1565,14 @@
         <v>46265</v>
       </c>
       <c r="S5" s="18" t="n">
-        <v>-44</v>
-      </c>
-      <c r="T5" s="25" t="inlineStr">
+        <v>-53</v>
+      </c>
+      <c r="T5" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
       </c>
-      <c r="U5" s="19" t="inlineStr">
+      <c r="U5" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1580,31 +1580,31 @@
       <c r="V5" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="W5" s="20" t="n"/>
-      <c r="X5" s="21" t="inlineStr">
+      <c r="W5" s="21" t="n"/>
+      <c r="X5" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y5" s="20" t="n"/>
-      <c r="Z5" s="22" t="n"/>
-      <c r="AA5" s="20" t="n"/>
-      <c r="AB5" s="20" t="n"/>
-      <c r="AC5" s="22" t="n"/>
-      <c r="AD5" s="20" t="n"/>
-      <c r="AE5" s="20" t="n"/>
-      <c r="AF5" s="22" t="n"/>
-      <c r="AG5" s="20" t="n"/>
-      <c r="AH5" s="20" t="n"/>
-      <c r="AI5" s="22" t="n"/>
-      <c r="AJ5" s="20" t="n"/>
-      <c r="AK5" s="20" t="n"/>
-      <c r="AL5" s="23" t="n"/>
-      <c r="AM5" s="20" t="n"/>
-      <c r="AN5" s="20" t="n"/>
-      <c r="AO5" s="24" t="n"/>
-      <c r="AP5" s="22" t="n"/>
-      <c r="AQ5" s="20" t="n"/>
+      <c r="Y5" s="21" t="n"/>
+      <c r="Z5" s="23" t="n"/>
+      <c r="AA5" s="21" t="n"/>
+      <c r="AB5" s="21" t="n"/>
+      <c r="AC5" s="23" t="n"/>
+      <c r="AD5" s="21" t="n"/>
+      <c r="AE5" s="21" t="n"/>
+      <c r="AF5" s="23" t="n"/>
+      <c r="AG5" s="21" t="n"/>
+      <c r="AH5" s="21" t="n"/>
+      <c r="AI5" s="23" t="n"/>
+      <c r="AJ5" s="21" t="n"/>
+      <c r="AK5" s="21" t="n"/>
+      <c r="AL5" s="24" t="n"/>
+      <c r="AM5" s="21" t="n"/>
+      <c r="AN5" s="21" t="n"/>
+      <c r="AO5" s="25" t="n"/>
+      <c r="AP5" s="23" t="n"/>
+      <c r="AQ5" s="21" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="11" t="n">
@@ -1688,14 +1688,14 @@
         <v>46240</v>
       </c>
       <c r="S6" s="18" t="n">
-        <v>-69</v>
-      </c>
-      <c r="T6" s="25" t="inlineStr">
+        <v>-78</v>
+      </c>
+      <c r="T6" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
       </c>
-      <c r="U6" s="19" t="inlineStr">
+      <c r="U6" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1703,31 +1703,31 @@
       <c r="V6" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="W6" s="20" t="n"/>
-      <c r="X6" s="21" t="inlineStr">
+      <c r="W6" s="21" t="n"/>
+      <c r="X6" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y6" s="20" t="n"/>
-      <c r="Z6" s="22" t="n"/>
-      <c r="AA6" s="20" t="n"/>
-      <c r="AB6" s="20" t="n"/>
-      <c r="AC6" s="22" t="n"/>
-      <c r="AD6" s="20" t="n"/>
-      <c r="AE6" s="20" t="n"/>
-      <c r="AF6" s="22" t="n"/>
-      <c r="AG6" s="20" t="n"/>
-      <c r="AH6" s="20" t="n"/>
-      <c r="AI6" s="22" t="n"/>
-      <c r="AJ6" s="20" t="n"/>
-      <c r="AK6" s="20" t="n"/>
-      <c r="AL6" s="23" t="n"/>
-      <c r="AM6" s="20" t="n"/>
-      <c r="AN6" s="20" t="n"/>
-      <c r="AO6" s="24" t="n"/>
-      <c r="AP6" s="22" t="n"/>
-      <c r="AQ6" s="20" t="n"/>
+      <c r="Y6" s="21" t="n"/>
+      <c r="Z6" s="23" t="n"/>
+      <c r="AA6" s="21" t="n"/>
+      <c r="AB6" s="21" t="n"/>
+      <c r="AC6" s="23" t="n"/>
+      <c r="AD6" s="21" t="n"/>
+      <c r="AE6" s="21" t="n"/>
+      <c r="AF6" s="23" t="n"/>
+      <c r="AG6" s="21" t="n"/>
+      <c r="AH6" s="21" t="n"/>
+      <c r="AI6" s="23" t="n"/>
+      <c r="AJ6" s="21" t="n"/>
+      <c r="AK6" s="21" t="n"/>
+      <c r="AL6" s="24" t="n"/>
+      <c r="AM6" s="21" t="n"/>
+      <c r="AN6" s="21" t="n"/>
+      <c r="AO6" s="25" t="n"/>
+      <c r="AP6" s="23" t="n"/>
+      <c r="AQ6" s="21" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="11" t="n">
@@ -1811,14 +1811,14 @@
         <v>46300</v>
       </c>
       <c r="S7" s="18" t="n">
-        <v>-9</v>
-      </c>
-      <c r="T7" s="25" t="inlineStr">
+        <v>-18</v>
+      </c>
+      <c r="T7" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
       </c>
-      <c r="U7" s="19" t="inlineStr">
+      <c r="U7" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1826,31 +1826,31 @@
       <c r="V7" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="W7" s="20" t="n"/>
-      <c r="X7" s="21" t="inlineStr">
+      <c r="W7" s="21" t="n"/>
+      <c r="X7" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y7" s="20" t="n"/>
-      <c r="Z7" s="22" t="n"/>
-      <c r="AA7" s="20" t="n"/>
-      <c r="AB7" s="20" t="n"/>
-      <c r="AC7" s="22" t="n"/>
-      <c r="AD7" s="20" t="n"/>
-      <c r="AE7" s="20" t="n"/>
-      <c r="AF7" s="22" t="n"/>
-      <c r="AG7" s="20" t="n"/>
-      <c r="AH7" s="20" t="n"/>
-      <c r="AI7" s="22" t="n"/>
-      <c r="AJ7" s="20" t="n"/>
-      <c r="AK7" s="20" t="n"/>
-      <c r="AL7" s="23" t="n"/>
-      <c r="AM7" s="20" t="n"/>
-      <c r="AN7" s="20" t="n"/>
-      <c r="AO7" s="24" t="n"/>
-      <c r="AP7" s="22" t="n"/>
-      <c r="AQ7" s="20" t="n"/>
+      <c r="Y7" s="21" t="n"/>
+      <c r="Z7" s="23" t="n"/>
+      <c r="AA7" s="21" t="n"/>
+      <c r="AB7" s="21" t="n"/>
+      <c r="AC7" s="23" t="n"/>
+      <c r="AD7" s="21" t="n"/>
+      <c r="AE7" s="21" t="n"/>
+      <c r="AF7" s="23" t="n"/>
+      <c r="AG7" s="21" t="n"/>
+      <c r="AH7" s="21" t="n"/>
+      <c r="AI7" s="23" t="n"/>
+      <c r="AJ7" s="21" t="n"/>
+      <c r="AK7" s="21" t="n"/>
+      <c r="AL7" s="24" t="n"/>
+      <c r="AM7" s="21" t="n"/>
+      <c r="AN7" s="21" t="n"/>
+      <c r="AO7" s="25" t="n"/>
+      <c r="AP7" s="23" t="n"/>
+      <c r="AQ7" s="21" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="11" t="n">
@@ -1934,14 +1934,14 @@
         <v>46295</v>
       </c>
       <c r="S8" s="18" t="n">
-        <v>-14</v>
-      </c>
-      <c r="T8" s="25" t="inlineStr">
+        <v>-23</v>
+      </c>
+      <c r="T8" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
       </c>
-      <c r="U8" s="19" t="inlineStr">
+      <c r="U8" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1949,31 +1949,31 @@
       <c r="V8" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="W8" s="20" t="n"/>
-      <c r="X8" s="21" t="inlineStr">
+      <c r="W8" s="21" t="n"/>
+      <c r="X8" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y8" s="20" t="n"/>
-      <c r="Z8" s="22" t="n"/>
-      <c r="AA8" s="20" t="n"/>
-      <c r="AB8" s="20" t="n"/>
-      <c r="AC8" s="22" t="n"/>
-      <c r="AD8" s="20" t="n"/>
-      <c r="AE8" s="20" t="n"/>
-      <c r="AF8" s="22" t="n"/>
-      <c r="AG8" s="20" t="n"/>
-      <c r="AH8" s="20" t="n"/>
-      <c r="AI8" s="22" t="n"/>
-      <c r="AJ8" s="20" t="n"/>
-      <c r="AK8" s="20" t="n"/>
-      <c r="AL8" s="23" t="n"/>
-      <c r="AM8" s="20" t="n"/>
-      <c r="AN8" s="20" t="n"/>
-      <c r="AO8" s="24" t="n"/>
-      <c r="AP8" s="22" t="n"/>
-      <c r="AQ8" s="20" t="n"/>
+      <c r="Y8" s="21" t="n"/>
+      <c r="Z8" s="23" t="n"/>
+      <c r="AA8" s="21" t="n"/>
+      <c r="AB8" s="21" t="n"/>
+      <c r="AC8" s="23" t="n"/>
+      <c r="AD8" s="21" t="n"/>
+      <c r="AE8" s="21" t="n"/>
+      <c r="AF8" s="23" t="n"/>
+      <c r="AG8" s="21" t="n"/>
+      <c r="AH8" s="21" t="n"/>
+      <c r="AI8" s="23" t="n"/>
+      <c r="AJ8" s="21" t="n"/>
+      <c r="AK8" s="21" t="n"/>
+      <c r="AL8" s="24" t="n"/>
+      <c r="AM8" s="21" t="n"/>
+      <c r="AN8" s="21" t="n"/>
+      <c r="AO8" s="25" t="n"/>
+      <c r="AP8" s="23" t="n"/>
+      <c r="AQ8" s="21" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="11" t="n">
@@ -2057,14 +2057,14 @@
         <v>46325</v>
       </c>
       <c r="S9" s="18" t="n">
-        <v>16</v>
-      </c>
-      <c r="T9" s="19" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="T9" s="20" t="inlineStr">
         <is>
           <t>Within 30 days</t>
         </is>
       </c>
-      <c r="U9" s="19" t="inlineStr">
+      <c r="U9" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2072,31 +2072,31 @@
       <c r="V9" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="W9" s="20" t="n"/>
-      <c r="X9" s="21" t="inlineStr">
+      <c r="W9" s="21" t="n"/>
+      <c r="X9" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y9" s="20" t="n"/>
-      <c r="Z9" s="22" t="n"/>
-      <c r="AA9" s="20" t="n"/>
-      <c r="AB9" s="20" t="n"/>
-      <c r="AC9" s="22" t="n"/>
-      <c r="AD9" s="20" t="n"/>
-      <c r="AE9" s="20" t="n"/>
-      <c r="AF9" s="22" t="n"/>
-      <c r="AG9" s="20" t="n"/>
-      <c r="AH9" s="20" t="n"/>
-      <c r="AI9" s="22" t="n"/>
-      <c r="AJ9" s="20" t="n"/>
-      <c r="AK9" s="20" t="n"/>
-      <c r="AL9" s="23" t="n"/>
-      <c r="AM9" s="20" t="n"/>
-      <c r="AN9" s="20" t="n"/>
-      <c r="AO9" s="24" t="n"/>
-      <c r="AP9" s="22" t="n"/>
-      <c r="AQ9" s="20" t="n"/>
+      <c r="Y9" s="21" t="n"/>
+      <c r="Z9" s="23" t="n"/>
+      <c r="AA9" s="21" t="n"/>
+      <c r="AB9" s="21" t="n"/>
+      <c r="AC9" s="23" t="n"/>
+      <c r="AD9" s="21" t="n"/>
+      <c r="AE9" s="21" t="n"/>
+      <c r="AF9" s="23" t="n"/>
+      <c r="AG9" s="21" t="n"/>
+      <c r="AH9" s="21" t="n"/>
+      <c r="AI9" s="23" t="n"/>
+      <c r="AJ9" s="21" t="n"/>
+      <c r="AK9" s="21" t="n"/>
+      <c r="AL9" s="24" t="n"/>
+      <c r="AM9" s="21" t="n"/>
+      <c r="AN9" s="21" t="n"/>
+      <c r="AO9" s="25" t="n"/>
+      <c r="AP9" s="23" t="n"/>
+      <c r="AQ9" s="21" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="11" t="n">
@@ -2180,9 +2180,9 @@
         <v>46184</v>
       </c>
       <c r="S10" s="18" t="n">
-        <v>-125</v>
-      </c>
-      <c r="T10" s="25" t="inlineStr">
+        <v>-134</v>
+      </c>
+      <c r="T10" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
@@ -2195,31 +2195,31 @@
       <c r="V10" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="W10" s="20" t="n"/>
-      <c r="X10" s="21" t="inlineStr">
+      <c r="W10" s="21" t="n"/>
+      <c r="X10" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y10" s="20" t="n"/>
-      <c r="Z10" s="22" t="n"/>
-      <c r="AA10" s="20" t="n"/>
-      <c r="AB10" s="20" t="n"/>
-      <c r="AC10" s="22" t="n"/>
-      <c r="AD10" s="20" t="n"/>
-      <c r="AE10" s="20" t="n"/>
-      <c r="AF10" s="22" t="n"/>
-      <c r="AG10" s="20" t="n"/>
-      <c r="AH10" s="20" t="n"/>
-      <c r="AI10" s="22" t="n"/>
-      <c r="AJ10" s="20" t="n"/>
-      <c r="AK10" s="20" t="n"/>
-      <c r="AL10" s="23" t="n"/>
-      <c r="AM10" s="20" t="n"/>
-      <c r="AN10" s="20" t="n"/>
-      <c r="AO10" s="24" t="n"/>
-      <c r="AP10" s="22" t="n"/>
-      <c r="AQ10" s="20" t="n"/>
+      <c r="Y10" s="21" t="n"/>
+      <c r="Z10" s="23" t="n"/>
+      <c r="AA10" s="21" t="n"/>
+      <c r="AB10" s="21" t="n"/>
+      <c r="AC10" s="23" t="n"/>
+      <c r="AD10" s="21" t="n"/>
+      <c r="AE10" s="21" t="n"/>
+      <c r="AF10" s="23" t="n"/>
+      <c r="AG10" s="21" t="n"/>
+      <c r="AH10" s="21" t="n"/>
+      <c r="AI10" s="23" t="n"/>
+      <c r="AJ10" s="21" t="n"/>
+      <c r="AK10" s="21" t="n"/>
+      <c r="AL10" s="24" t="n"/>
+      <c r="AM10" s="21" t="n"/>
+      <c r="AN10" s="21" t="n"/>
+      <c r="AO10" s="25" t="n"/>
+      <c r="AP10" s="23" t="n"/>
+      <c r="AQ10" s="21" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="11" t="n">
@@ -2303,14 +2303,14 @@
         <v>46304</v>
       </c>
       <c r="S11" s="18" t="n">
-        <v>-5</v>
-      </c>
-      <c r="T11" s="25" t="inlineStr">
+        <v>-14</v>
+      </c>
+      <c r="T11" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
       </c>
-      <c r="U11" s="19" t="inlineStr">
+      <c r="U11" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2318,31 +2318,31 @@
       <c r="V11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="W11" s="20" t="n"/>
-      <c r="X11" s="21" t="inlineStr">
+      <c r="W11" s="21" t="n"/>
+      <c r="X11" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y11" s="20" t="n"/>
-      <c r="Z11" s="22" t="n"/>
-      <c r="AA11" s="20" t="n"/>
-      <c r="AB11" s="20" t="n"/>
-      <c r="AC11" s="22" t="n"/>
-      <c r="AD11" s="20" t="n"/>
-      <c r="AE11" s="20" t="n"/>
-      <c r="AF11" s="22" t="n"/>
-      <c r="AG11" s="20" t="n"/>
-      <c r="AH11" s="20" t="n"/>
-      <c r="AI11" s="22" t="n"/>
-      <c r="AJ11" s="20" t="n"/>
-      <c r="AK11" s="20" t="n"/>
-      <c r="AL11" s="23" t="n"/>
-      <c r="AM11" s="20" t="n"/>
-      <c r="AN11" s="20" t="n"/>
-      <c r="AO11" s="24" t="n"/>
-      <c r="AP11" s="22" t="n"/>
-      <c r="AQ11" s="20" t="n"/>
+      <c r="Y11" s="21" t="n"/>
+      <c r="Z11" s="23" t="n"/>
+      <c r="AA11" s="21" t="n"/>
+      <c r="AB11" s="21" t="n"/>
+      <c r="AC11" s="23" t="n"/>
+      <c r="AD11" s="21" t="n"/>
+      <c r="AE11" s="21" t="n"/>
+      <c r="AF11" s="23" t="n"/>
+      <c r="AG11" s="21" t="n"/>
+      <c r="AH11" s="21" t="n"/>
+      <c r="AI11" s="23" t="n"/>
+      <c r="AJ11" s="21" t="n"/>
+      <c r="AK11" s="21" t="n"/>
+      <c r="AL11" s="24" t="n"/>
+      <c r="AM11" s="21" t="n"/>
+      <c r="AN11" s="21" t="n"/>
+      <c r="AO11" s="25" t="n"/>
+      <c r="AP11" s="23" t="n"/>
+      <c r="AQ11" s="21" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="11" t="n">
@@ -2426,9 +2426,9 @@
         <v>46265</v>
       </c>
       <c r="S12" s="18" t="n">
-        <v>-44</v>
-      </c>
-      <c r="T12" s="25" t="inlineStr">
+        <v>-53</v>
+      </c>
+      <c r="T12" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
@@ -2441,31 +2441,31 @@
       <c r="V12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="W12" s="20" t="n"/>
-      <c r="X12" s="21" t="inlineStr">
+      <c r="W12" s="21" t="n"/>
+      <c r="X12" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y12" s="20" t="n"/>
-      <c r="Z12" s="22" t="n"/>
-      <c r="AA12" s="20" t="n"/>
-      <c r="AB12" s="20" t="n"/>
-      <c r="AC12" s="22" t="n"/>
-      <c r="AD12" s="20" t="n"/>
-      <c r="AE12" s="20" t="n"/>
-      <c r="AF12" s="22" t="n"/>
-      <c r="AG12" s="20" t="n"/>
-      <c r="AH12" s="20" t="n"/>
-      <c r="AI12" s="22" t="n"/>
-      <c r="AJ12" s="20" t="n"/>
-      <c r="AK12" s="20" t="n"/>
-      <c r="AL12" s="23" t="n"/>
-      <c r="AM12" s="20" t="n"/>
-      <c r="AN12" s="20" t="n"/>
-      <c r="AO12" s="24" t="n"/>
-      <c r="AP12" s="22" t="n"/>
-      <c r="AQ12" s="20" t="n"/>
+      <c r="Y12" s="21" t="n"/>
+      <c r="Z12" s="23" t="n"/>
+      <c r="AA12" s="21" t="n"/>
+      <c r="AB12" s="21" t="n"/>
+      <c r="AC12" s="23" t="n"/>
+      <c r="AD12" s="21" t="n"/>
+      <c r="AE12" s="21" t="n"/>
+      <c r="AF12" s="23" t="n"/>
+      <c r="AG12" s="21" t="n"/>
+      <c r="AH12" s="21" t="n"/>
+      <c r="AI12" s="23" t="n"/>
+      <c r="AJ12" s="21" t="n"/>
+      <c r="AK12" s="21" t="n"/>
+      <c r="AL12" s="24" t="n"/>
+      <c r="AM12" s="21" t="n"/>
+      <c r="AN12" s="21" t="n"/>
+      <c r="AO12" s="25" t="n"/>
+      <c r="AP12" s="23" t="n"/>
+      <c r="AQ12" s="21" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="11" t="n">
@@ -2549,14 +2549,14 @@
         <v>46263</v>
       </c>
       <c r="S13" s="18" t="n">
-        <v>-46</v>
-      </c>
-      <c r="T13" s="25" t="inlineStr">
+        <v>-55</v>
+      </c>
+      <c r="T13" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
       </c>
-      <c r="U13" s="19" t="inlineStr">
+      <c r="U13" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2564,31 +2564,31 @@
       <c r="V13" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="W13" s="20" t="n"/>
-      <c r="X13" s="21" t="inlineStr">
+      <c r="W13" s="21" t="n"/>
+      <c r="X13" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y13" s="20" t="n"/>
-      <c r="Z13" s="22" t="n"/>
-      <c r="AA13" s="20" t="n"/>
-      <c r="AB13" s="20" t="n"/>
-      <c r="AC13" s="22" t="n"/>
-      <c r="AD13" s="20" t="n"/>
-      <c r="AE13" s="20" t="n"/>
-      <c r="AF13" s="22" t="n"/>
-      <c r="AG13" s="20" t="n"/>
-      <c r="AH13" s="20" t="n"/>
-      <c r="AI13" s="22" t="n"/>
-      <c r="AJ13" s="20" t="n"/>
-      <c r="AK13" s="20" t="n"/>
-      <c r="AL13" s="23" t="n"/>
-      <c r="AM13" s="20" t="n"/>
-      <c r="AN13" s="20" t="n"/>
-      <c r="AO13" s="24" t="n"/>
-      <c r="AP13" s="22" t="n"/>
-      <c r="AQ13" s="20" t="n"/>
+      <c r="Y13" s="21" t="n"/>
+      <c r="Z13" s="23" t="n"/>
+      <c r="AA13" s="21" t="n"/>
+      <c r="AB13" s="21" t="n"/>
+      <c r="AC13" s="23" t="n"/>
+      <c r="AD13" s="21" t="n"/>
+      <c r="AE13" s="21" t="n"/>
+      <c r="AF13" s="23" t="n"/>
+      <c r="AG13" s="21" t="n"/>
+      <c r="AH13" s="21" t="n"/>
+      <c r="AI13" s="23" t="n"/>
+      <c r="AJ13" s="21" t="n"/>
+      <c r="AK13" s="21" t="n"/>
+      <c r="AL13" s="24" t="n"/>
+      <c r="AM13" s="21" t="n"/>
+      <c r="AN13" s="21" t="n"/>
+      <c r="AO13" s="25" t="n"/>
+      <c r="AP13" s="23" t="n"/>
+      <c r="AQ13" s="21" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="11" t="n">
@@ -2672,9 +2672,9 @@
         <v>46300</v>
       </c>
       <c r="S14" s="18" t="n">
-        <v>-9</v>
-      </c>
-      <c r="T14" s="25" t="inlineStr">
+        <v>-18</v>
+      </c>
+      <c r="T14" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
@@ -2687,31 +2687,31 @@
       <c r="V14" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="W14" s="20" t="n"/>
-      <c r="X14" s="21" t="inlineStr">
+      <c r="W14" s="21" t="n"/>
+      <c r="X14" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y14" s="20" t="n"/>
-      <c r="Z14" s="22" t="n"/>
-      <c r="AA14" s="20" t="n"/>
-      <c r="AB14" s="20" t="n"/>
-      <c r="AC14" s="22" t="n"/>
-      <c r="AD14" s="20" t="n"/>
-      <c r="AE14" s="20" t="n"/>
-      <c r="AF14" s="22" t="n"/>
-      <c r="AG14" s="20" t="n"/>
-      <c r="AH14" s="20" t="n"/>
-      <c r="AI14" s="22" t="n"/>
-      <c r="AJ14" s="20" t="n"/>
-      <c r="AK14" s="20" t="n"/>
-      <c r="AL14" s="23" t="n"/>
-      <c r="AM14" s="20" t="n"/>
-      <c r="AN14" s="20" t="n"/>
-      <c r="AO14" s="24" t="n"/>
-      <c r="AP14" s="22" t="n"/>
-      <c r="AQ14" s="20" t="n"/>
+      <c r="Y14" s="21" t="n"/>
+      <c r="Z14" s="23" t="n"/>
+      <c r="AA14" s="21" t="n"/>
+      <c r="AB14" s="21" t="n"/>
+      <c r="AC14" s="23" t="n"/>
+      <c r="AD14" s="21" t="n"/>
+      <c r="AE14" s="21" t="n"/>
+      <c r="AF14" s="23" t="n"/>
+      <c r="AG14" s="21" t="n"/>
+      <c r="AH14" s="21" t="n"/>
+      <c r="AI14" s="23" t="n"/>
+      <c r="AJ14" s="21" t="n"/>
+      <c r="AK14" s="21" t="n"/>
+      <c r="AL14" s="24" t="n"/>
+      <c r="AM14" s="21" t="n"/>
+      <c r="AN14" s="21" t="n"/>
+      <c r="AO14" s="25" t="n"/>
+      <c r="AP14" s="23" t="n"/>
+      <c r="AQ14" s="21" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="11" t="n">
@@ -2795,9 +2795,9 @@
         <v>46289</v>
       </c>
       <c r="S15" s="18" t="n">
-        <v>-20</v>
-      </c>
-      <c r="T15" s="25" t="inlineStr">
+        <v>-29</v>
+      </c>
+      <c r="T15" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
@@ -2810,31 +2810,31 @@
       <c r="V15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="W15" s="20" t="n"/>
-      <c r="X15" s="21" t="inlineStr">
+      <c r="W15" s="21" t="n"/>
+      <c r="X15" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y15" s="20" t="n"/>
-      <c r="Z15" s="22" t="n"/>
-      <c r="AA15" s="20" t="n"/>
-      <c r="AB15" s="20" t="n"/>
-      <c r="AC15" s="22" t="n"/>
-      <c r="AD15" s="20" t="n"/>
-      <c r="AE15" s="20" t="n"/>
-      <c r="AF15" s="22" t="n"/>
-      <c r="AG15" s="20" t="n"/>
-      <c r="AH15" s="20" t="n"/>
-      <c r="AI15" s="22" t="n"/>
-      <c r="AJ15" s="20" t="n"/>
-      <c r="AK15" s="20" t="n"/>
-      <c r="AL15" s="23" t="n"/>
-      <c r="AM15" s="20" t="n"/>
-      <c r="AN15" s="20" t="n"/>
-      <c r="AO15" s="24" t="n"/>
-      <c r="AP15" s="22" t="n"/>
-      <c r="AQ15" s="20" t="n"/>
+      <c r="Y15" s="21" t="n"/>
+      <c r="Z15" s="23" t="n"/>
+      <c r="AA15" s="21" t="n"/>
+      <c r="AB15" s="21" t="n"/>
+      <c r="AC15" s="23" t="n"/>
+      <c r="AD15" s="21" t="n"/>
+      <c r="AE15" s="21" t="n"/>
+      <c r="AF15" s="23" t="n"/>
+      <c r="AG15" s="21" t="n"/>
+      <c r="AH15" s="21" t="n"/>
+      <c r="AI15" s="23" t="n"/>
+      <c r="AJ15" s="21" t="n"/>
+      <c r="AK15" s="21" t="n"/>
+      <c r="AL15" s="24" t="n"/>
+      <c r="AM15" s="21" t="n"/>
+      <c r="AN15" s="21" t="n"/>
+      <c r="AO15" s="25" t="n"/>
+      <c r="AP15" s="23" t="n"/>
+      <c r="AQ15" s="21" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="11" t="n">
@@ -2918,9 +2918,9 @@
         <v>46274</v>
       </c>
       <c r="S16" s="18" t="n">
-        <v>-35</v>
-      </c>
-      <c r="T16" s="25" t="inlineStr">
+        <v>-44</v>
+      </c>
+      <c r="T16" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
@@ -2933,31 +2933,31 @@
       <c r="V16" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="W16" s="20" t="n"/>
-      <c r="X16" s="21" t="inlineStr">
+      <c r="W16" s="21" t="n"/>
+      <c r="X16" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y16" s="20" t="n"/>
-      <c r="Z16" s="22" t="n"/>
-      <c r="AA16" s="20" t="n"/>
-      <c r="AB16" s="20" t="n"/>
-      <c r="AC16" s="22" t="n"/>
-      <c r="AD16" s="20" t="n"/>
-      <c r="AE16" s="20" t="n"/>
-      <c r="AF16" s="22" t="n"/>
-      <c r="AG16" s="20" t="n"/>
-      <c r="AH16" s="20" t="n"/>
-      <c r="AI16" s="22" t="n"/>
-      <c r="AJ16" s="20" t="n"/>
-      <c r="AK16" s="20" t="n"/>
-      <c r="AL16" s="23" t="n"/>
-      <c r="AM16" s="20" t="n"/>
-      <c r="AN16" s="20" t="n"/>
-      <c r="AO16" s="24" t="n"/>
-      <c r="AP16" s="22" t="n"/>
-      <c r="AQ16" s="20" t="n"/>
+      <c r="Y16" s="21" t="n"/>
+      <c r="Z16" s="23" t="n"/>
+      <c r="AA16" s="21" t="n"/>
+      <c r="AB16" s="21" t="n"/>
+      <c r="AC16" s="23" t="n"/>
+      <c r="AD16" s="21" t="n"/>
+      <c r="AE16" s="21" t="n"/>
+      <c r="AF16" s="23" t="n"/>
+      <c r="AG16" s="21" t="n"/>
+      <c r="AH16" s="21" t="n"/>
+      <c r="AI16" s="23" t="n"/>
+      <c r="AJ16" s="21" t="n"/>
+      <c r="AK16" s="21" t="n"/>
+      <c r="AL16" s="24" t="n"/>
+      <c r="AM16" s="21" t="n"/>
+      <c r="AN16" s="21" t="n"/>
+      <c r="AO16" s="25" t="n"/>
+      <c r="AP16" s="23" t="n"/>
+      <c r="AQ16" s="21" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="11" t="n">
@@ -3041,9 +3041,9 @@
         <v>46248</v>
       </c>
       <c r="S17" s="18" t="n">
-        <v>-61</v>
-      </c>
-      <c r="T17" s="25" t="inlineStr">
+        <v>-70</v>
+      </c>
+      <c r="T17" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
@@ -3056,31 +3056,31 @@
       <c r="V17" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="W17" s="20" t="n"/>
-      <c r="X17" s="21" t="inlineStr">
+      <c r="W17" s="21" t="n"/>
+      <c r="X17" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y17" s="20" t="n"/>
-      <c r="Z17" s="22" t="n"/>
-      <c r="AA17" s="20" t="n"/>
-      <c r="AB17" s="20" t="n"/>
-      <c r="AC17" s="22" t="n"/>
-      <c r="AD17" s="20" t="n"/>
-      <c r="AE17" s="20" t="n"/>
-      <c r="AF17" s="22" t="n"/>
-      <c r="AG17" s="20" t="n"/>
-      <c r="AH17" s="20" t="n"/>
-      <c r="AI17" s="22" t="n"/>
-      <c r="AJ17" s="20" t="n"/>
-      <c r="AK17" s="20" t="n"/>
-      <c r="AL17" s="23" t="n"/>
-      <c r="AM17" s="20" t="n"/>
-      <c r="AN17" s="20" t="n"/>
-      <c r="AO17" s="24" t="n"/>
-      <c r="AP17" s="22" t="n"/>
-      <c r="AQ17" s="20" t="n"/>
+      <c r="Y17" s="21" t="n"/>
+      <c r="Z17" s="23" t="n"/>
+      <c r="AA17" s="21" t="n"/>
+      <c r="AB17" s="21" t="n"/>
+      <c r="AC17" s="23" t="n"/>
+      <c r="AD17" s="21" t="n"/>
+      <c r="AE17" s="21" t="n"/>
+      <c r="AF17" s="23" t="n"/>
+      <c r="AG17" s="21" t="n"/>
+      <c r="AH17" s="21" t="n"/>
+      <c r="AI17" s="23" t="n"/>
+      <c r="AJ17" s="21" t="n"/>
+      <c r="AK17" s="21" t="n"/>
+      <c r="AL17" s="24" t="n"/>
+      <c r="AM17" s="21" t="n"/>
+      <c r="AN17" s="21" t="n"/>
+      <c r="AO17" s="25" t="n"/>
+      <c r="AP17" s="23" t="n"/>
+      <c r="AQ17" s="21" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="11" t="n">
@@ -3164,9 +3164,9 @@
         <v>46293</v>
       </c>
       <c r="S18" s="18" t="n">
-        <v>-16</v>
-      </c>
-      <c r="T18" s="25" t="inlineStr">
+        <v>-25</v>
+      </c>
+      <c r="T18" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
@@ -3179,31 +3179,31 @@
       <c r="V18" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="W18" s="20" t="n"/>
-      <c r="X18" s="21" t="inlineStr">
+      <c r="W18" s="21" t="n"/>
+      <c r="X18" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y18" s="20" t="n"/>
-      <c r="Z18" s="22" t="n"/>
-      <c r="AA18" s="20" t="n"/>
-      <c r="AB18" s="20" t="n"/>
-      <c r="AC18" s="22" t="n"/>
-      <c r="AD18" s="20" t="n"/>
-      <c r="AE18" s="20" t="n"/>
-      <c r="AF18" s="22" t="n"/>
-      <c r="AG18" s="20" t="n"/>
-      <c r="AH18" s="20" t="n"/>
-      <c r="AI18" s="22" t="n"/>
-      <c r="AJ18" s="20" t="n"/>
-      <c r="AK18" s="20" t="n"/>
-      <c r="AL18" s="23" t="n"/>
-      <c r="AM18" s="20" t="n"/>
-      <c r="AN18" s="20" t="n"/>
-      <c r="AO18" s="24" t="n"/>
-      <c r="AP18" s="22" t="n"/>
-      <c r="AQ18" s="20" t="n"/>
+      <c r="Y18" s="21" t="n"/>
+      <c r="Z18" s="23" t="n"/>
+      <c r="AA18" s="21" t="n"/>
+      <c r="AB18" s="21" t="n"/>
+      <c r="AC18" s="23" t="n"/>
+      <c r="AD18" s="21" t="n"/>
+      <c r="AE18" s="21" t="n"/>
+      <c r="AF18" s="23" t="n"/>
+      <c r="AG18" s="21" t="n"/>
+      <c r="AH18" s="21" t="n"/>
+      <c r="AI18" s="23" t="n"/>
+      <c r="AJ18" s="21" t="n"/>
+      <c r="AK18" s="21" t="n"/>
+      <c r="AL18" s="24" t="n"/>
+      <c r="AM18" s="21" t="n"/>
+      <c r="AN18" s="21" t="n"/>
+      <c r="AO18" s="25" t="n"/>
+      <c r="AP18" s="23" t="n"/>
+      <c r="AQ18" s="21" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="11" t="n">
@@ -3287,14 +3287,14 @@
         <v>46305</v>
       </c>
       <c r="S19" s="18" t="n">
-        <v>-4</v>
-      </c>
-      <c r="T19" s="25" t="inlineStr">
+        <v>-13</v>
+      </c>
+      <c r="T19" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
       </c>
-      <c r="U19" s="19" t="inlineStr">
+      <c r="U19" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3302,31 +3302,31 @@
       <c r="V19" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="W19" s="20" t="n"/>
-      <c r="X19" s="21" t="inlineStr">
+      <c r="W19" s="21" t="n"/>
+      <c r="X19" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y19" s="20" t="n"/>
-      <c r="Z19" s="22" t="n"/>
-      <c r="AA19" s="20" t="n"/>
-      <c r="AB19" s="20" t="n"/>
-      <c r="AC19" s="22" t="n"/>
-      <c r="AD19" s="20" t="n"/>
-      <c r="AE19" s="20" t="n"/>
-      <c r="AF19" s="22" t="n"/>
-      <c r="AG19" s="20" t="n"/>
-      <c r="AH19" s="20" t="n"/>
-      <c r="AI19" s="22" t="n"/>
-      <c r="AJ19" s="20" t="n"/>
-      <c r="AK19" s="20" t="n"/>
-      <c r="AL19" s="23" t="n"/>
-      <c r="AM19" s="20" t="n"/>
-      <c r="AN19" s="20" t="n"/>
-      <c r="AO19" s="24" t="n"/>
-      <c r="AP19" s="22" t="n"/>
-      <c r="AQ19" s="20" t="n"/>
+      <c r="Y19" s="21" t="n"/>
+      <c r="Z19" s="23" t="n"/>
+      <c r="AA19" s="21" t="n"/>
+      <c r="AB19" s="21" t="n"/>
+      <c r="AC19" s="23" t="n"/>
+      <c r="AD19" s="21" t="n"/>
+      <c r="AE19" s="21" t="n"/>
+      <c r="AF19" s="23" t="n"/>
+      <c r="AG19" s="21" t="n"/>
+      <c r="AH19" s="21" t="n"/>
+      <c r="AI19" s="23" t="n"/>
+      <c r="AJ19" s="21" t="n"/>
+      <c r="AK19" s="21" t="n"/>
+      <c r="AL19" s="24" t="n"/>
+      <c r="AM19" s="21" t="n"/>
+      <c r="AN19" s="21" t="n"/>
+      <c r="AO19" s="25" t="n"/>
+      <c r="AP19" s="23" t="n"/>
+      <c r="AQ19" s="21" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="11" t="n">
@@ -3410,14 +3410,14 @@
         <v>46241</v>
       </c>
       <c r="S20" s="18" t="n">
-        <v>-68</v>
-      </c>
-      <c r="T20" s="25" t="inlineStr">
+        <v>-77</v>
+      </c>
+      <c r="T20" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
       </c>
-      <c r="U20" s="19" t="inlineStr">
+      <c r="U20" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3425,31 +3425,31 @@
       <c r="V20" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="W20" s="20" t="n"/>
-      <c r="X20" s="21" t="inlineStr">
+      <c r="W20" s="21" t="n"/>
+      <c r="X20" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y20" s="20" t="n"/>
-      <c r="Z20" s="22" t="n"/>
-      <c r="AA20" s="20" t="n"/>
-      <c r="AB20" s="20" t="n"/>
-      <c r="AC20" s="22" t="n"/>
-      <c r="AD20" s="20" t="n"/>
-      <c r="AE20" s="20" t="n"/>
-      <c r="AF20" s="22" t="n"/>
-      <c r="AG20" s="20" t="n"/>
-      <c r="AH20" s="20" t="n"/>
-      <c r="AI20" s="22" t="n"/>
-      <c r="AJ20" s="20" t="n"/>
-      <c r="AK20" s="20" t="n"/>
-      <c r="AL20" s="23" t="n"/>
-      <c r="AM20" s="20" t="n"/>
-      <c r="AN20" s="20" t="n"/>
-      <c r="AO20" s="24" t="n"/>
-      <c r="AP20" s="22" t="n"/>
-      <c r="AQ20" s="20" t="n"/>
+      <c r="Y20" s="21" t="n"/>
+      <c r="Z20" s="23" t="n"/>
+      <c r="AA20" s="21" t="n"/>
+      <c r="AB20" s="21" t="n"/>
+      <c r="AC20" s="23" t="n"/>
+      <c r="AD20" s="21" t="n"/>
+      <c r="AE20" s="21" t="n"/>
+      <c r="AF20" s="23" t="n"/>
+      <c r="AG20" s="21" t="n"/>
+      <c r="AH20" s="21" t="n"/>
+      <c r="AI20" s="23" t="n"/>
+      <c r="AJ20" s="21" t="n"/>
+      <c r="AK20" s="21" t="n"/>
+      <c r="AL20" s="24" t="n"/>
+      <c r="AM20" s="21" t="n"/>
+      <c r="AN20" s="21" t="n"/>
+      <c r="AO20" s="25" t="n"/>
+      <c r="AP20" s="23" t="n"/>
+      <c r="AQ20" s="21" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="11" t="n">
@@ -3533,9 +3533,9 @@
         <v>46280</v>
       </c>
       <c r="S21" s="18" t="n">
-        <v>-29</v>
-      </c>
-      <c r="T21" s="25" t="inlineStr">
+        <v>-38</v>
+      </c>
+      <c r="T21" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
@@ -3548,31 +3548,31 @@
       <c r="V21" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="W21" s="20" t="n"/>
-      <c r="X21" s="21" t="inlineStr">
+      <c r="W21" s="21" t="n"/>
+      <c r="X21" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y21" s="20" t="n"/>
-      <c r="Z21" s="22" t="n"/>
-      <c r="AA21" s="20" t="n"/>
-      <c r="AB21" s="20" t="n"/>
-      <c r="AC21" s="22" t="n"/>
-      <c r="AD21" s="20" t="n"/>
-      <c r="AE21" s="20" t="n"/>
-      <c r="AF21" s="22" t="n"/>
-      <c r="AG21" s="20" t="n"/>
-      <c r="AH21" s="20" t="n"/>
-      <c r="AI21" s="22" t="n"/>
-      <c r="AJ21" s="20" t="n"/>
-      <c r="AK21" s="20" t="n"/>
-      <c r="AL21" s="23" t="n"/>
-      <c r="AM21" s="20" t="n"/>
-      <c r="AN21" s="20" t="n"/>
-      <c r="AO21" s="24" t="n"/>
-      <c r="AP21" s="22" t="n"/>
-      <c r="AQ21" s="20" t="n"/>
+      <c r="Y21" s="21" t="n"/>
+      <c r="Z21" s="23" t="n"/>
+      <c r="AA21" s="21" t="n"/>
+      <c r="AB21" s="21" t="n"/>
+      <c r="AC21" s="23" t="n"/>
+      <c r="AD21" s="21" t="n"/>
+      <c r="AE21" s="21" t="n"/>
+      <c r="AF21" s="23" t="n"/>
+      <c r="AG21" s="21" t="n"/>
+      <c r="AH21" s="21" t="n"/>
+      <c r="AI21" s="23" t="n"/>
+      <c r="AJ21" s="21" t="n"/>
+      <c r="AK21" s="21" t="n"/>
+      <c r="AL21" s="24" t="n"/>
+      <c r="AM21" s="21" t="n"/>
+      <c r="AN21" s="21" t="n"/>
+      <c r="AO21" s="25" t="n"/>
+      <c r="AP21" s="23" t="n"/>
+      <c r="AQ21" s="21" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="11" t="n">
@@ -3656,14 +3656,14 @@
         <v>46240</v>
       </c>
       <c r="S22" s="18" t="n">
-        <v>-69</v>
-      </c>
-      <c r="T22" s="25" t="inlineStr">
+        <v>-78</v>
+      </c>
+      <c r="T22" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
       </c>
-      <c r="U22" s="19" t="inlineStr">
+      <c r="U22" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3671,31 +3671,31 @@
       <c r="V22" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="W22" s="20" t="n"/>
-      <c r="X22" s="21" t="inlineStr">
+      <c r="W22" s="21" t="n"/>
+      <c r="X22" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y22" s="20" t="n"/>
-      <c r="Z22" s="22" t="n"/>
-      <c r="AA22" s="20" t="n"/>
-      <c r="AB22" s="20" t="n"/>
-      <c r="AC22" s="22" t="n"/>
-      <c r="AD22" s="20" t="n"/>
-      <c r="AE22" s="20" t="n"/>
-      <c r="AF22" s="22" t="n"/>
-      <c r="AG22" s="20" t="n"/>
-      <c r="AH22" s="20" t="n"/>
-      <c r="AI22" s="22" t="n"/>
-      <c r="AJ22" s="20" t="n"/>
-      <c r="AK22" s="20" t="n"/>
-      <c r="AL22" s="23" t="n"/>
-      <c r="AM22" s="20" t="n"/>
-      <c r="AN22" s="20" t="n"/>
-      <c r="AO22" s="24" t="n"/>
-      <c r="AP22" s="22" t="n"/>
-      <c r="AQ22" s="20" t="n"/>
+      <c r="Y22" s="21" t="n"/>
+      <c r="Z22" s="23" t="n"/>
+      <c r="AA22" s="21" t="n"/>
+      <c r="AB22" s="21" t="n"/>
+      <c r="AC22" s="23" t="n"/>
+      <c r="AD22" s="21" t="n"/>
+      <c r="AE22" s="21" t="n"/>
+      <c r="AF22" s="23" t="n"/>
+      <c r="AG22" s="21" t="n"/>
+      <c r="AH22" s="21" t="n"/>
+      <c r="AI22" s="23" t="n"/>
+      <c r="AJ22" s="21" t="n"/>
+      <c r="AK22" s="21" t="n"/>
+      <c r="AL22" s="24" t="n"/>
+      <c r="AM22" s="21" t="n"/>
+      <c r="AN22" s="21" t="n"/>
+      <c r="AO22" s="25" t="n"/>
+      <c r="AP22" s="23" t="n"/>
+      <c r="AQ22" s="21" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="11" t="n">
@@ -3782,7 +3782,7 @@
           <t>Notice period only</t>
         </is>
       </c>
-      <c r="U23" s="19" t="inlineStr">
+      <c r="U23" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3790,31 +3790,31 @@
       <c r="V23" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="W23" s="20" t="n"/>
-      <c r="X23" s="21" t="inlineStr">
+      <c r="W23" s="21" t="n"/>
+      <c r="X23" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y23" s="20" t="n"/>
-      <c r="Z23" s="22" t="n"/>
-      <c r="AA23" s="20" t="n"/>
-      <c r="AB23" s="20" t="n"/>
-      <c r="AC23" s="22" t="n"/>
-      <c r="AD23" s="20" t="n"/>
-      <c r="AE23" s="20" t="n"/>
-      <c r="AF23" s="22" t="n"/>
-      <c r="AG23" s="20" t="n"/>
-      <c r="AH23" s="20" t="n"/>
-      <c r="AI23" s="22" t="n"/>
-      <c r="AJ23" s="20" t="n"/>
-      <c r="AK23" s="20" t="n"/>
-      <c r="AL23" s="23" t="n"/>
-      <c r="AM23" s="20" t="n"/>
-      <c r="AN23" s="20" t="n"/>
-      <c r="AO23" s="24" t="n"/>
-      <c r="AP23" s="22" t="n"/>
-      <c r="AQ23" s="20" t="n"/>
+      <c r="Y23" s="21" t="n"/>
+      <c r="Z23" s="23" t="n"/>
+      <c r="AA23" s="21" t="n"/>
+      <c r="AB23" s="21" t="n"/>
+      <c r="AC23" s="23" t="n"/>
+      <c r="AD23" s="21" t="n"/>
+      <c r="AE23" s="21" t="n"/>
+      <c r="AF23" s="23" t="n"/>
+      <c r="AG23" s="21" t="n"/>
+      <c r="AH23" s="21" t="n"/>
+      <c r="AI23" s="23" t="n"/>
+      <c r="AJ23" s="21" t="n"/>
+      <c r="AK23" s="21" t="n"/>
+      <c r="AL23" s="24" t="n"/>
+      <c r="AM23" s="21" t="n"/>
+      <c r="AN23" s="21" t="n"/>
+      <c r="AO23" s="25" t="n"/>
+      <c r="AP23" s="23" t="n"/>
+      <c r="AQ23" s="21" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="11" t="n">
@@ -3898,14 +3898,14 @@
         <v>46178</v>
       </c>
       <c r="S24" s="18" t="n">
-        <v>-131</v>
-      </c>
-      <c r="T24" s="25" t="inlineStr">
+        <v>-140</v>
+      </c>
+      <c r="T24" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
       </c>
-      <c r="U24" s="19" t="inlineStr">
+      <c r="U24" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3913,31 +3913,31 @@
       <c r="V24" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="W24" s="20" t="n"/>
-      <c r="X24" s="21" t="inlineStr">
+      <c r="W24" s="21" t="n"/>
+      <c r="X24" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y24" s="20" t="n"/>
-      <c r="Z24" s="22" t="n"/>
-      <c r="AA24" s="20" t="n"/>
-      <c r="AB24" s="20" t="n"/>
-      <c r="AC24" s="22" t="n"/>
-      <c r="AD24" s="20" t="n"/>
-      <c r="AE24" s="20" t="n"/>
-      <c r="AF24" s="22" t="n"/>
-      <c r="AG24" s="20" t="n"/>
-      <c r="AH24" s="20" t="n"/>
-      <c r="AI24" s="22" t="n"/>
-      <c r="AJ24" s="20" t="n"/>
-      <c r="AK24" s="20" t="n"/>
-      <c r="AL24" s="23" t="n"/>
-      <c r="AM24" s="20" t="n"/>
-      <c r="AN24" s="20" t="n"/>
-      <c r="AO24" s="24" t="n"/>
-      <c r="AP24" s="22" t="n"/>
-      <c r="AQ24" s="20" t="n"/>
+      <c r="Y24" s="21" t="n"/>
+      <c r="Z24" s="23" t="n"/>
+      <c r="AA24" s="21" t="n"/>
+      <c r="AB24" s="21" t="n"/>
+      <c r="AC24" s="23" t="n"/>
+      <c r="AD24" s="21" t="n"/>
+      <c r="AE24" s="21" t="n"/>
+      <c r="AF24" s="23" t="n"/>
+      <c r="AG24" s="21" t="n"/>
+      <c r="AH24" s="21" t="n"/>
+      <c r="AI24" s="23" t="n"/>
+      <c r="AJ24" s="21" t="n"/>
+      <c r="AK24" s="21" t="n"/>
+      <c r="AL24" s="24" t="n"/>
+      <c r="AM24" s="21" t="n"/>
+      <c r="AN24" s="21" t="n"/>
+      <c r="AO24" s="25" t="n"/>
+      <c r="AP24" s="23" t="n"/>
+      <c r="AQ24" s="21" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="11" t="n">
@@ -4021,14 +4021,14 @@
         <v>46295</v>
       </c>
       <c r="S25" s="18" t="n">
-        <v>-14</v>
-      </c>
-      <c r="T25" s="25" t="inlineStr">
+        <v>-23</v>
+      </c>
+      <c r="T25" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
       </c>
-      <c r="U25" s="19" t="inlineStr">
+      <c r="U25" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4036,31 +4036,31 @@
       <c r="V25" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="W25" s="20" t="n"/>
-      <c r="X25" s="21" t="inlineStr">
+      <c r="W25" s="21" t="n"/>
+      <c r="X25" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y25" s="20" t="n"/>
-      <c r="Z25" s="22" t="n"/>
-      <c r="AA25" s="20" t="n"/>
-      <c r="AB25" s="20" t="n"/>
-      <c r="AC25" s="22" t="n"/>
-      <c r="AD25" s="20" t="n"/>
-      <c r="AE25" s="20" t="n"/>
-      <c r="AF25" s="22" t="n"/>
-      <c r="AG25" s="20" t="n"/>
-      <c r="AH25" s="20" t="n"/>
-      <c r="AI25" s="22" t="n"/>
-      <c r="AJ25" s="20" t="n"/>
-      <c r="AK25" s="20" t="n"/>
-      <c r="AL25" s="23" t="n"/>
-      <c r="AM25" s="20" t="n"/>
-      <c r="AN25" s="20" t="n"/>
-      <c r="AO25" s="24" t="n"/>
-      <c r="AP25" s="22" t="n"/>
-      <c r="AQ25" s="20" t="n"/>
+      <c r="Y25" s="21" t="n"/>
+      <c r="Z25" s="23" t="n"/>
+      <c r="AA25" s="21" t="n"/>
+      <c r="AB25" s="21" t="n"/>
+      <c r="AC25" s="23" t="n"/>
+      <c r="AD25" s="21" t="n"/>
+      <c r="AE25" s="21" t="n"/>
+      <c r="AF25" s="23" t="n"/>
+      <c r="AG25" s="21" t="n"/>
+      <c r="AH25" s="21" t="n"/>
+      <c r="AI25" s="23" t="n"/>
+      <c r="AJ25" s="21" t="n"/>
+      <c r="AK25" s="21" t="n"/>
+      <c r="AL25" s="24" t="n"/>
+      <c r="AM25" s="21" t="n"/>
+      <c r="AN25" s="21" t="n"/>
+      <c r="AO25" s="25" t="n"/>
+      <c r="AP25" s="23" t="n"/>
+      <c r="AQ25" s="21" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="11" t="n">
@@ -4144,9 +4144,9 @@
         <v>46188</v>
       </c>
       <c r="S26" s="18" t="n">
-        <v>-121</v>
-      </c>
-      <c r="T26" s="25" t="inlineStr">
+        <v>-130</v>
+      </c>
+      <c r="T26" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
@@ -4159,31 +4159,31 @@
       <c r="V26" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="W26" s="20" t="n"/>
-      <c r="X26" s="21" t="inlineStr">
+      <c r="W26" s="21" t="n"/>
+      <c r="X26" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y26" s="20" t="n"/>
-      <c r="Z26" s="22" t="n"/>
-      <c r="AA26" s="20" t="n"/>
-      <c r="AB26" s="20" t="n"/>
-      <c r="AC26" s="22" t="n"/>
-      <c r="AD26" s="20" t="n"/>
-      <c r="AE26" s="20" t="n"/>
-      <c r="AF26" s="22" t="n"/>
-      <c r="AG26" s="20" t="n"/>
-      <c r="AH26" s="20" t="n"/>
-      <c r="AI26" s="22" t="n"/>
-      <c r="AJ26" s="20" t="n"/>
-      <c r="AK26" s="20" t="n"/>
-      <c r="AL26" s="23" t="n"/>
-      <c r="AM26" s="20" t="n"/>
-      <c r="AN26" s="20" t="n"/>
-      <c r="AO26" s="24" t="n"/>
-      <c r="AP26" s="22" t="n"/>
-      <c r="AQ26" s="20" t="n"/>
+      <c r="Y26" s="21" t="n"/>
+      <c r="Z26" s="23" t="n"/>
+      <c r="AA26" s="21" t="n"/>
+      <c r="AB26" s="21" t="n"/>
+      <c r="AC26" s="23" t="n"/>
+      <c r="AD26" s="21" t="n"/>
+      <c r="AE26" s="21" t="n"/>
+      <c r="AF26" s="23" t="n"/>
+      <c r="AG26" s="21" t="n"/>
+      <c r="AH26" s="21" t="n"/>
+      <c r="AI26" s="23" t="n"/>
+      <c r="AJ26" s="21" t="n"/>
+      <c r="AK26" s="21" t="n"/>
+      <c r="AL26" s="24" t="n"/>
+      <c r="AM26" s="21" t="n"/>
+      <c r="AN26" s="21" t="n"/>
+      <c r="AO26" s="25" t="n"/>
+      <c r="AP26" s="23" t="n"/>
+      <c r="AQ26" s="21" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="11" t="n">
@@ -4267,9 +4267,9 @@
         <v>46111</v>
       </c>
       <c r="S27" s="18" t="n">
-        <v>-198</v>
-      </c>
-      <c r="T27" s="25" t="inlineStr">
+        <v>-207</v>
+      </c>
+      <c r="T27" s="19" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
@@ -4282,50 +4282,296 @@
       <c r="V27" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="W27" s="20" t="n"/>
-      <c r="X27" s="21" t="inlineStr">
+      <c r="W27" s="21" t="n"/>
+      <c r="X27" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y27" s="20" t="n"/>
-      <c r="Z27" s="22" t="n"/>
-      <c r="AA27" s="20" t="n"/>
-      <c r="AB27" s="20" t="n"/>
-      <c r="AC27" s="22" t="n"/>
-      <c r="AD27" s="20" t="n"/>
-      <c r="AE27" s="20" t="n"/>
-      <c r="AF27" s="22" t="n"/>
-      <c r="AG27" s="20" t="n"/>
-      <c r="AH27" s="20" t="n"/>
-      <c r="AI27" s="22" t="n"/>
-      <c r="AJ27" s="20" t="n"/>
-      <c r="AK27" s="20" t="n"/>
-      <c r="AL27" s="23" t="n"/>
-      <c r="AM27" s="20" t="n"/>
-      <c r="AN27" s="20" t="n"/>
-      <c r="AO27" s="24" t="n"/>
-      <c r="AP27" s="22" t="n"/>
-      <c r="AQ27" s="20" t="n"/>
+      <c r="Y27" s="21" t="n"/>
+      <c r="Z27" s="23" t="n"/>
+      <c r="AA27" s="21" t="n"/>
+      <c r="AB27" s="21" t="n"/>
+      <c r="AC27" s="23" t="n"/>
+      <c r="AD27" s="21" t="n"/>
+      <c r="AE27" s="21" t="n"/>
+      <c r="AF27" s="23" t="n"/>
+      <c r="AG27" s="21" t="n"/>
+      <c r="AH27" s="21" t="n"/>
+      <c r="AI27" s="23" t="n"/>
+      <c r="AJ27" s="21" t="n"/>
+      <c r="AK27" s="21" t="n"/>
+      <c r="AL27" s="24" t="n"/>
+      <c r="AM27" s="21" t="n"/>
+      <c r="AN27" s="21" t="n"/>
+      <c r="AO27" s="25" t="n"/>
+      <c r="AP27" s="23" t="n"/>
+      <c r="AQ27" s="21" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>IKrux Engineering</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>22-Oct-2026</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Process Manager</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>Dinesh Kumar C</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>9894771567</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>kumdin321@gmail.com</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>8.4 Years</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Process Management: 6 Years | Client: 8 Years</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="L28" s="14" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>LWD : 4-Sep-26</t>
+        </is>
+      </c>
+      <c r="N28" s="15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O28" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q28" s="16" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="R28" s="17" t="n">
+        <v>46269</v>
+      </c>
+      <c r="S28" s="18" t="n">
+        <v>-49</v>
+      </c>
+      <c r="T28" s="19" t="inlineStr">
+        <is>
+          <t>Available now</t>
+        </is>
+      </c>
+      <c r="U28" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="V28" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W28" s="21" t="n"/>
+      <c r="X28" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y28" s="21" t="n"/>
+      <c r="Z28" s="23" t="n"/>
+      <c r="AA28" s="21" t="n"/>
+      <c r="AB28" s="21" t="n"/>
+      <c r="AC28" s="23" t="n"/>
+      <c r="AD28" s="21" t="n"/>
+      <c r="AE28" s="21" t="n"/>
+      <c r="AF28" s="23" t="n"/>
+      <c r="AG28" s="21" t="n"/>
+      <c r="AH28" s="21" t="n"/>
+      <c r="AI28" s="23" t="n"/>
+      <c r="AJ28" s="21" t="n"/>
+      <c r="AK28" s="21" t="n"/>
+      <c r="AL28" s="24" t="n"/>
+      <c r="AM28" s="21" t="n"/>
+      <c r="AN28" s="21" t="n"/>
+      <c r="AO28" s="25" t="n"/>
+      <c r="AP28" s="23" t="n"/>
+      <c r="AQ28" s="21" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>IKrux Engineering</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>22-Oct-2026</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Process Manager</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>Sowdhamini J</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>8086298137</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>sowdhaminij@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Atain</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>10 Years</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Process Management: 6 Years | Client: 6 Years</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="L29" s="14" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>LWD : 12-Oct-26</t>
+        </is>
+      </c>
+      <c r="N29" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="O29" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q29" s="16" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="R29" s="17" t="n">
+        <v>46307</v>
+      </c>
+      <c r="S29" s="18" t="n">
+        <v>-11</v>
+      </c>
+      <c r="T29" s="19" t="inlineStr">
+        <is>
+          <t>Available now</t>
+        </is>
+      </c>
+      <c r="U29" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="V29" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="W29" s="21" t="n"/>
+      <c r="X29" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y29" s="21" t="n"/>
+      <c r="Z29" s="23" t="n"/>
+      <c r="AA29" s="21" t="n"/>
+      <c r="AB29" s="21" t="n"/>
+      <c r="AC29" s="23" t="n"/>
+      <c r="AD29" s="21" t="n"/>
+      <c r="AE29" s="21" t="n"/>
+      <c r="AF29" s="23" t="n"/>
+      <c r="AG29" s="21" t="n"/>
+      <c r="AH29" s="21" t="n"/>
+      <c r="AI29" s="23" t="n"/>
+      <c r="AJ29" s="21" t="n"/>
+      <c r="AK29" s="21" t="n"/>
+      <c r="AL29" s="24" t="n"/>
+      <c r="AM29" s="21" t="n"/>
+      <c r="AN29" s="21" t="n"/>
+      <c r="AO29" s="25" t="n"/>
+      <c r="AP29" s="23" t="n"/>
+      <c r="AQ29" s="21" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AQ27"/>
+  <autoFilter ref="A2:AQ29"/>
   <mergeCells count="3">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="Q1:V1"/>
     <mergeCell ref="W1:AQ1"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="Y3:Y27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Y3:Y29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Shortlisted,On Hold,Rejected"</formula1>
     </dataValidation>
-    <dataValidation sqref="AB3:AB27 AE3:AE27 AH3:AH27 AK3:AK27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AB3:AB29 AE3:AE29 AH3:AH29 AK3:AK29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Scheduled,Selected,Rejected,On Hold,No Show,Rescheduled"</formula1>
     </dataValidation>
-    <dataValidation sqref="AM3:AM27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AM3:AM29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"In Process,Selected,Rejected,On Hold,Offer Declined,Joined,Dropped Out"</formula1>
     </dataValidation>
-    <dataValidation sqref="X3:X27 AN3:AN27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="X3:X29 AN3:AN29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4340,7 +4586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4356,7 +4602,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Resume validation - all 22 candidates</t>
+          <t>Resume validation - all 27 candidates</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4689,7 @@
           <t>L&amp;T Infotech appears under its post-merger name LTIMindtree, and the .Net depth is real — .NET 8 Azure Functions, Service Bus, Cosmos DB. Two things: his CV lists employment from Jul 2007, about 18 years of history, yet states 14+ years, and the difference is an unexplained gap between Cognizant (to Oct 2013) and TCS (from Dec 2014). His AI entry rests on ‘Claude prompt Eng’ in a skills list, against the 2 years recorded.</t>
         </is>
       </c>
-      <c r="H5" s="19" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4483,7 +4729,7 @@
           <t>Experience, employer, location and the .Net / React / Azure / AI split all line up with his CV. Two things to probe: 10.7 of the 15 years were at Pricol as an Application Engineer rather than services or product delivery, and his CV shows IBM as current with no notice stated while the row records an LWD of 4 Sep 2026.</t>
         </is>
       </c>
-      <c r="H6" s="19" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4523,7 +4769,7 @@
           <t>Experience, employer, location and the Aug 2026 exit all agree. Roughly Jun–Oct 2020 is unaccounted for between LAKEBA and his return to OMS, the CV carries no education section, and his AI exposure is AI-assisted coding with Claude and ChatGPT rather than AI engineering.</t>
         </is>
       </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4563,7 +4809,7 @@
           <t>Rackspace, Angular, Azure and AWS all agree, and he holds an AWS Developer Associate certification. But his CV states 9.5 years against the 10.3 recorded, and the row credits 10.3 years of .Net when his first Infosys projects — Customer Account Opening and Multi-Channel Printing for NatWest — were Java, Struts and Spring Boot. .NET is nearer 7 to 8 years.</t>
         </is>
       </c>
-      <c r="H8" s="19" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4603,7 +4849,7 @@
           <t>Fourteen years from Sep 2012, HCLTech, and the .Net / Angular / React / Azure split all agree, and he adds Python, FastAPI and Azure OpenAI work the row does not record. The flag is his own closing line: ‘Open to international opportunities (H1B Visa Holder)’ — worth weighing against a Coimbatore posting and a 36 L expectation.</t>
         </is>
       </c>
-      <c r="H9" s="19" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4643,7 +4889,7 @@
           <t>His industry software experience starts Nov 2018 at cSoft — about 8 years, which is exactly what the Java, React and AWS 8-year entries reflect. The remaining 4+ years were as an Assistant Professor of Computer Science at Nandha Engineering College (Aug 2014 – Nov 2018). His AI credentials are stronger than the 1 year recorded. His CV gives his location only as Tamil Nadu, and his employer as Bengaluru (remote).</t>
         </is>
       </c>
-      <c r="H10" s="19" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4683,7 +4929,7 @@
           <t>React at 8 years is well supported and the front-end depth is genuine. But the row credits 6 years of .Net, and his CV shows C# only at Lycatech (2017–2020) and again on the current Nagarro project from Jul 2025 — the four years between are React, Node and Next.js. .NET is nearer 3 to 4 years. His address reads Tamil Nadu 638701, which is Erode, not Coimbatore, and the Nagarro role is remote.</t>
         </is>
       </c>
-      <c r="H11" s="19" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4763,7 +5009,7 @@
           <t>Bosch, Angular and the lead experience all agree, and his GenAI work — AccentBridge, LangChain, LangGraph, Whisper, LoRA, Ollama, plus an AI hackathon win — is a real asset the row does not record at all. But Java and Spring Boot start at Datamatics in Jun 2018, about 8 years, not 10: Nov 2016 to May 2018 at MAK Controls was Android and IoT work. His CV says 9+ years against the 10.3 recorded.</t>
         </is>
       </c>
-      <c r="H13" s="19" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4843,7 +5089,7 @@
           <t>The Python, React, RAG and LangGraph depth is real and current. But Lead at 5 years does not hold: he has been Tech Lead at Wipro since Apr 2024, about 2.4 years, with Senior Software Engineer and Senior PHP Developer titles before that. He has had four employers between Apr 2021 and Apr 2024, one of them a six-month stint, with gaps before Wipro and before Equator. His earlier career was PHP and LAMP, which the row does not mention.</t>
         </is>
       </c>
-      <c r="H15" s="19" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5083,7 +5329,7 @@
           <t>Five years at LTIMindtree on the Citi BFS-AML project, split between Java development and L3 production support with Actimize, ActOne and AIS. His entire tech skills list is Java 8, Unix shell, SQL, HTML/CSS, Actimize and AIS — no framework, no cloud, no modern front end. Against an 18 L expectation for a Senior Software Engineer, probe what he has actually built.</t>
         </is>
       </c>
-      <c r="H21" s="19" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5123,7 +5369,7 @@
           <t>Sixteen years and a genuine lead record at Virtusa on British Telecom work — microservices, Kafka, Docker and Kubernetes, AWS, and real observability with Prometheus, Grafana and Loki. Three gaps between the row and the CV: the row claims AWS and Microservices at 12 years each, but his AWS work starts at Virtusa in Jan 2020, about six years; the row says Coimbatore while the CV header says Chennai; and the row gives an LWD of 7 Aug 2026 while the CV still shows Virtusa as current. His own CV puts Java at about 5 years against Node at 7 and Angular at 9, so for a Java lead the hands-on Java is shallower than 16 years implies.</t>
         </is>
       </c>
-      <c r="H22" s="19" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5203,7 +5449,7 @@
           <t>Eleven years of Java and Spring Boot microservices with React and Angular, most recently leading offshore delivery for Cisco at Tech Mahindra — monolith-to-microservices, Berkeley DB to PostgreSQL, Docker, Kubernetes, Jenkins, and Scrum Master duties. Two things to note: the Tech Mahindra engagement is listed as ending August 2026, so she has been out roughly two months, and the MCA is recorded as coursework completed rather than awarded, with a B.Sc. as the completed degree.</t>
         </is>
       </c>
-      <c r="H24" s="19" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5243,7 +5489,7 @@
           <t>Real distributed-systems substance at Zoho: a browser-to-device P2P file transfer platform at 1M+ users with 95% peer completion, WebSocket infrastructure, a JSON to Protocol Buffers migration, a Kafka event pipeline, and ownership of a 30,000-line React/TypeScript migration on a product serving 10M+ monthly actives. Also build-pipeline work across a 70-engineer organisation. The honest caveat is tenure: five years total, so architecture and multi-tenancy theory will be thinner than the engineering. No location anywhere on the CV.</t>
         </is>
       </c>
-      <c r="H25" s="19" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5283,7 +5529,7 @@
           <t>Eleven years of Java and J2EE across Wipro, HCL and smaller firms, with named enterprise clients — United HealthCare, MasterCard — on Spring Boot microservices, Kafka, Kubernetes, Docker, GCP and AWS. Submitted as a Technical Consultant. Three things to check: the row gives an LWD of 5 June 2026 while the CV says the Wipro engagement ran to 25 June 2026, so the exit date needs pinning down and either way he has been out about four months; the row says Coimbatore while his CV address is Madurai; and the degree is a BE in Electrical and Electronics rather than computer science. The CV is also list-heavy — long technology inventories with thin description of what he personally built.</t>
         </is>
       </c>
-      <c r="H26" s="19" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5323,7 +5569,7 @@
           <t>Five years at Accenture, progressing associate to senior analyst, all of it Java on a Fortune 100 healthcare account. Real substance for the level: Spring Boot and Quarkus microservices, Kafka event integration replacing a synchronous dependency between services, JBeret batch jobs, Redis caching, an on-premises to Azure migration handling 1M+ drug, pricing and insurance records, and a drug data pipeline feeding 400+ US pharmacy stores. Azure Fundamentals certified. Two caveats: one employer throughout, so no exposure to a different engineering culture, and the degree is Mechatronics rather than computer science. His 9 L current salary is the lowest in the pipeline and the 15 L expectation is a 67% ask.</t>
         </is>
       </c>
-      <c r="H27" s="19" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5404,6 +5650,86 @@
         </is>
       </c>
       <c r="H29" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="104" customHeight="1">
+      <c r="A30" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Dinesh Kumar C</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>IKrux Engineering</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Dinesh_Kumar.pdf</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>PMO | Project management and operations | Contract-to-cash</t>
+        </is>
+      </c>
+      <c r="F30" s="28" t="inlineStr">
+        <is>
+          <t>Clean PMO record, with two gaps and a question about the remit</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Four years running contract-to-cash as PMO at Cognizant — SOW processing, onboarding and allocation, timesheet and billing control, invoice and timesheet reconciliation, support to budgeting and forecasting, payment follow-up and unbilled revenue tracking — preceded by two years as an Implementation Manager at TCS on cash management solutions. That is the six years of process management the row credits, and the CV supports it. Three things to weigh. His CV carries two gaps: twenty months between State Street HCL ending May 2017 and resuming in Jan 2019, and five months between Accenture and TCS in 2020. His first four years were securities trade settlement — prematching, fails resolution, EMEA markets — a different discipline from what he does now. And the PMO work is commercial operations rather than process design or improvement: there is no PMP, Prince2, Lean or Six Sigma anywhere on the CV, and the MBA is in Finance. The LWD of 4 Sep 2026 has passed while the CV still shows Cognizant as current.</t>
+        </is>
+      </c>
+      <c r="H30" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="104" customHeight="1">
+      <c r="A31" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>Sowdhamini J</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>IKrux Engineering</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Sowdhamini_J.pdf</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Manager — Operations | BPO | Workforce, quality and client management</t>
+        </is>
+      </c>
+      <c r="F31" s="30" t="inlineStr">
+        <is>
+          <t>Real operations credentials, but five employers in four years</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>A genuine BPO operations manager: workforce planning, shrinkage and adherence, attrition tracking through early warning systems and open houses, quality monitoring banded by agent tenure, client escalation handling and business reviews — with a Lean Six Sigma Black Belt taken in July 2025, the only formal process credential across the two Process Manager submissions. Three concerns. Tenure: five employers since September 2022 — Tech Mahindra, HCL, Sutherland, Hexaware and ATAIN — and the current one is six months old. Span: the row records 10 years, but her work history begins June 2019, about seven and a half, leaving roughly three years after her January 2016 degree unaccounted for. Domain: her experience is BPO — medical billing, airlines, customer support, technical support, sales and billing — not IT project or delivery process management, which makes her a different proposition from Dinesh under the same job title. Smaller points: the LWD of 12 Oct 2026 has passed while the CV shows ATAIN as current, that employer is in Bangalore against a Coimbatore row, and the row’s e-mail address is not the one on her CV.</t>
+        </is>
+      </c>
+      <c r="H31" s="27" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5424,7 +5750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5446,7 +5772,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Raised from reading all 22 resumes against their submitted rows, plus arithmetic checks. Owner and status are yours to fill in.</t>
+          <t>Raised from reading all 27 resumes against their submitted rows, plus arithmetic checks. Owner and status are yours to fill in.</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5842,7 @@
           <t>Re-brief IKrux on the Senior Software Engineer requirement before scheduling — the whole slate for that role looks mis-targeted.</t>
         </is>
       </c>
-      <c r="G5" s="20" t="n"/>
+      <c r="G5" s="21" t="n"/>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="11" t="n">
@@ -5547,7 +5873,7 @@
           <t>Re-verify employment status for every candidate the list marks available now before approaching them.</t>
         </is>
       </c>
-      <c r="G6" s="20" t="n"/>
+      <c r="G6" s="21" t="n"/>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="11" t="n">
@@ -5576,7 +5902,7 @@
           <t>Confirm employment status, the reason for the break, and whether 30 L still holds.</t>
         </is>
       </c>
-      <c r="G7" s="20" t="n"/>
+      <c r="G7" s="21" t="n"/>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="11" t="n">
@@ -5605,7 +5931,7 @@
           <t>Confirm his relocation intent and family situation before progressing.</t>
         </is>
       </c>
-      <c r="G8" s="20" t="n"/>
+      <c r="G8" s="21" t="n"/>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="11" t="n">
@@ -5634,7 +5960,7 @@
           <t>Reconfirm the skill mapping with IKrux before allocating a panel.</t>
         </is>
       </c>
-      <c r="G9" s="20" t="n"/>
+      <c r="G9" s="21" t="n"/>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="11" t="n">
@@ -5663,7 +5989,7 @@
           <t>Confirm the opening is a build role before scheduling a development panel.</t>
         </is>
       </c>
-      <c r="G10" s="20" t="n"/>
+      <c r="G10" s="21" t="n"/>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="11" t="n">
@@ -5692,7 +6018,7 @@
           <t>Confirm whether the opening is a build or a support role before scheduling.</t>
         </is>
       </c>
-      <c r="G11" s="20" t="n"/>
+      <c r="G11" s="21" t="n"/>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="11" t="n">
@@ -5721,7 +6047,7 @@
           <t>Confirm the opening is a build role before scheduling a development panel.</t>
         </is>
       </c>
-      <c r="G12" s="20" t="n"/>
+      <c r="G12" s="21" t="n"/>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="11" t="n">
@@ -5750,7 +6076,7 @@
           <t>Challenge the skill claims with IKrux before scheduling, and test AWS directly if the role needs it.</t>
         </is>
       </c>
-      <c r="G13" s="20" t="n"/>
+      <c r="G13" s="21" t="n"/>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="11" t="n">
@@ -5779,7 +6105,7 @@
           <t>If she is wanted, compress the process and decide the number now; a normal cycle will lose her.</t>
         </is>
       </c>
-      <c r="G14" s="20" t="n"/>
+      <c r="G14" s="21" t="n"/>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="11" t="n">
@@ -5808,7 +6134,7 @@
           <t>Probe the reason for each move and what would make him stay; a permanent delivery role needs that answered.</t>
         </is>
       </c>
-      <c r="G15" s="20" t="n"/>
+      <c r="G15" s="21" t="n"/>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="11" t="n">
@@ -5837,7 +6163,7 @@
           <t>Ask her to account for it.</t>
         </is>
       </c>
-      <c r="G16" s="20" t="n"/>
+      <c r="G16" s="21" t="n"/>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="11" t="n">
@@ -5866,7 +6192,7 @@
           <t>Confirm current status and what she has been doing since.</t>
         </is>
       </c>
-      <c r="G17" s="20" t="n"/>
+      <c r="G17" s="21" t="n"/>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="11" t="n">
@@ -5895,169 +6221,165 @@
           <t>Decide whether a PM who has not worked on a modern stack can lead this team, and test it directly if she proceeds.</t>
         </is>
       </c>
-      <c r="G18" s="20" t="n"/>
+      <c r="G18" s="21" t="n"/>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B19" s="11" t="n">
+        <v>26</v>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Pipeline-wide</t>
-        </is>
-      </c>
-      <c r="D19" s="32" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Dinesh Kumar C</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>The Round 1 theory set was written for engineers and leads. The two Technical Project Manager candidates will be scored against architecture depth they are not hired for.</t>
+          <t>LWD of 4 Sep 2026 has passed, so he has been out around seven weeks, while the CV still shows Cognizant as current.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Either calibrate the expected bar for SL 24 and 25, or ask for a delivery-management question set for that role.</t>
-        </is>
-      </c>
-      <c r="G19" s="20" t="n"/>
+          <t>Confirm his current status and when he can start.</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="n"/>
     </row>
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="11" t="n">
+        <v>26</v>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Pipeline-wide</t>
-        </is>
-      </c>
-      <c r="D20" s="32" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Dinesh Kumar C</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Offers field blank for SL 8, 10, 13, 14 and 15.</t>
+          <t>Two gaps on the CV: twenty months between State Street HCL ending May 2017 and resuming Jan 2019, and five months between Accenture and TCS in 2020.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Collect a yes-with-value or a no before any offer discussion.</t>
-        </is>
-      </c>
-      <c r="G20" s="20" t="n"/>
+          <t>Ask him to account for both.</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="n"/>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="11" t="n">
+        <v>27</v>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Pipeline-wide</t>
-        </is>
-      </c>
-      <c r="D21" s="32" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Sowdhamini J</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Hikes of 100%, 97%, 65% and 64% at Senior Software Engineer level.</t>
+          <t>Five employers since Sep 2022 — Tech Mahindra, HCL, Sutherland, Hexaware and ATAIN — and the current one is only six months old.</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Check each against the approved band before the profiles reach a panel.</t>
-        </is>
-      </c>
-      <c r="G21" s="20" t="n"/>
+          <t>Probe the reason for each move and what would make her stay.</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="n"/>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="11" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="11" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Jeganagan Murugesan</t>
-        </is>
-      </c>
-      <c r="D22" s="32" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Sowdhamini J</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>CV lists employment from Jul 2007 (about 18 years of history) but states 14+ years; a gap sits between Cognizant (to Oct 2013) and TCS (from Dec 2014).</t>
+          <t>Recorded at 10 years, but her work history starts June 2019, about seven and a half; roughly three years after her Jan 2016 degree are unaccounted for.</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Ask him to account for the gap and confirm the true total.</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="n"/>
+          <t>Ask her to account for 2016 to 2019, and restate the span on the row.</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="n"/>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="11" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="11" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Dayakar G</t>
-        </is>
-      </c>
-      <c r="D23" s="32" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Sowdhamini J</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>CV shows IBM as current with no notice; the row records LWD 4 Sep 2026.</t>
+          <t>LWD of 12 Oct 2026 has passed while the CV shows ATAIN as current.</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Establish which is current and record the real notice position.</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="n"/>
+          <t>Confirm her current status and availability.</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="n"/>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="11" t="n">
-        <v>2</v>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Dayakar G</t>
+          <t>Pipeline-wide</t>
         </is>
       </c>
       <c r="D24" s="32" t="inlineStr">
@@ -6067,26 +6389,28 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>10.7 of 15 years were in-house manufacturing IT at Pricol.</t>
+          <t>The two Process Manager submissions read the title differently: one is a PMO running contract-to-cash, the other a BPO operations manager. They are not competing for the same job as written.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Probe depth of enterprise .NET delivery in the technical round.</t>
-        </is>
-      </c>
-      <c r="G24" s="20" t="n"/>
+          <t>Write down what this role actually owns before either panel meets, and tell IKrux, or the slate will keep arriving mixed.</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="n"/>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="11" t="n">
-        <v>3</v>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Amre Binnaz. M</t>
+          <t>Pipeline-wide</t>
         </is>
       </c>
       <c r="D25" s="32" t="inlineStr">
@@ -6096,26 +6420,28 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Employment gap of roughly Jun–Oct 2020 between LAKEBA and OMS.</t>
+          <t>The Round 1 theory set was written for engineers and leads. The two Technical Project Manager candidates will be scored against architecture depth they are not hired for.</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Ask the candidate to account for the gap.</t>
-        </is>
-      </c>
-      <c r="G25" s="20" t="n"/>
+          <t>Either calibrate the expected bar for SL 24 and 25, or ask for a delivery-management question set for that role.</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="n"/>
     </row>
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="11" t="n">
-        <v>4</v>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Adarsh Swaminathan</t>
+          <t>Pipeline-wide</t>
         </is>
       </c>
       <c r="D26" s="32" t="inlineStr">
@@ -6125,26 +6451,28 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Credited with 10.3 years of .Net, but his first Infosys projects (CAO, MCP for NatWest) were Java and Struts. CV states 9.5 years total against 10.3 recorded.</t>
+          <t>Offers field blank for SL 8, 10, 13, 14 and 15.</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Restate .Net at roughly 7 to 8 years and correct the total.</t>
-        </is>
-      </c>
-      <c r="G26" s="20" t="n"/>
+          <t>Collect a yes-with-value or a no before any offer discussion.</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="n"/>
     </row>
     <row r="27" ht="44" customHeight="1">
       <c r="A27" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="11" t="n">
-        <v>4</v>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Adarsh Swaminathan</t>
+          <t>Pipeline-wide</t>
         </is>
       </c>
       <c r="D27" s="32" t="inlineStr">
@@ -6154,26 +6482,26 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Based in Chamrajnagar, and already holds a 28 L offer against a 30 L expectation.</t>
+          <t>Hikes of 100%, 97%, 65% and 64% at Senior Software Engineer level.</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Confirm relocation and the closing timeline against the competing offer.</t>
-        </is>
-      </c>
-      <c r="G27" s="20" t="n"/>
+          <t>Check each against the approved band before the profiles reach a panel.</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="n"/>
     </row>
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="11" t="n">
         <v>24</v>
       </c>
       <c r="B28" s="11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Sivakumar Varatharaj</t>
+          <t>Jeganagan Murugesan</t>
         </is>
       </c>
       <c r="D28" s="32" t="inlineStr">
@@ -6183,26 +6511,26 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>CV states ‘Open to international opportunities (H1B Visa Holder)’ — a flight risk against a Coimbatore posting at 36 L.</t>
+          <t>CV lists employment from Jul 2007 (about 18 years of history) but states 14+ years; a gap sits between Cognizant (to Oct 2013) and TCS (from Dec 2014).</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Ask directly about his US plans before an offer is built.</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="n"/>
+          <t>Ask him to account for the gap and confirm the true total.</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="n"/>
     </row>
     <row r="29" ht="44" customHeight="1">
       <c r="A29" s="11" t="n">
         <v>25</v>
       </c>
       <c r="B29" s="11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Sathya K S</t>
+          <t>Dayakar G</t>
         </is>
       </c>
       <c r="D29" s="32" t="inlineStr">
@@ -6212,26 +6540,26 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Of the 12 years recorded, 4+ were as an Assistant Professor of Computer Science, not industry software engineering.</t>
+          <t>CV shows IBM as current with no notice; the row records LWD 4 Sep 2026.</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Record industry experience as roughly 8 years and confirm the panel is comfortable with the academic period.</t>
-        </is>
-      </c>
-      <c r="G29" s="20" t="n"/>
+          <t>Establish which is current and record the real notice position.</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="n"/>
     </row>
     <row r="30" ht="44" customHeight="1">
       <c r="A30" s="11" t="n">
         <v>26</v>
       </c>
       <c r="B30" s="11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Navin Kumar</t>
+          <t>Dayakar G</t>
         </is>
       </c>
       <c r="D30" s="32" t="inlineStr">
@@ -6241,26 +6569,26 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Credited with 6 years of .Net; the CV shows C# only 2017–2020 and again from Jul 2025 — roughly 3 to 4 years.</t>
+          <t>10.7 of 15 years were in-house manufacturing IT at Pricol.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Restate the .Net span and decide whether a React/Node lead fits the role.</t>
-        </is>
-      </c>
-      <c r="G30" s="20" t="n"/>
+          <t>Probe depth of enterprise .NET delivery in the technical round.</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="n"/>
     </row>
     <row r="31" ht="44" customHeight="1">
       <c r="A31" s="11" t="n">
         <v>27</v>
       </c>
       <c r="B31" s="11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Navin Kumar</t>
+          <t>Amre Binnaz. M</t>
         </is>
       </c>
       <c r="D31" s="32" t="inlineStr">
@@ -6270,26 +6598,26 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>33 L expected against 32.8 L current — a 0.6% hike, out of line with the rest.</t>
+          <t>Employment gap of roughly Jun–Oct 2020 between LAKEBA and OMS.</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Verify both figures; one is likely mis-keyed.</t>
-        </is>
-      </c>
-      <c r="G31" s="20" t="n"/>
+          <t>Ask the candidate to account for the gap.</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="n"/>
     </row>
     <row r="32" ht="44" customHeight="1">
       <c r="A32" s="11" t="n">
         <v>28</v>
       </c>
       <c r="B32" s="11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Boopathi Molakgounder</t>
+          <t>Adarsh Swaminathan</t>
         </is>
       </c>
       <c r="D32" s="32" t="inlineStr">
@@ -6299,26 +6627,26 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Location recorded as Erode; the CV says Bangalore.</t>
+          <t>Credited with 10.3 years of .Net, but his first Infosys projects (CAO, MCP for NatWest) were Java and Struts. CV states 9.5 years total against 10.3 recorded.</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Confirm with the candidate.</t>
-        </is>
-      </c>
-      <c r="G32" s="20" t="n"/>
+          <t>Restate .Net at roughly 7 to 8 years and correct the total.</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="n"/>
     </row>
     <row r="33" ht="44" customHeight="1">
       <c r="A33" s="11" t="n">
         <v>29</v>
       </c>
       <c r="B33" s="11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Ravikumar Gopal</t>
+          <t>Adarsh Swaminathan</t>
         </is>
       </c>
       <c r="D33" s="32" t="inlineStr">
@@ -6328,26 +6656,26 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Credited with 10 years of Java; Java and Spring Boot start Jun 2018 — about 8 years. The 2016–2018 role was Android and IoT.</t>
+          <t>Based in Chamrajnagar, and already holds a 28 L offer against a 30 L expectation.</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Restate the Java span, and record the GenAI depth the row currently omits.</t>
-        </is>
-      </c>
-      <c r="G33" s="20" t="n"/>
+          <t>Confirm relocation and the closing timeline against the competing offer.</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="n"/>
     </row>
     <row r="34" ht="44" customHeight="1">
       <c r="A34" s="11" t="n">
         <v>30</v>
       </c>
       <c r="B34" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Vaisakh P</t>
+          <t>Sivakumar Varatharaj</t>
         </is>
       </c>
       <c r="D34" s="32" t="inlineStr">
@@ -6357,26 +6685,26 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Angular at 4 years appears only on a personal side project, and Lead at 6 years against a title held since Aug 2022.</t>
+          <t>CV states ‘Open to international opportunities (H1B Visa Holder)’ — a flight risk against a Coimbatore posting at 36 L.</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Verify both figures with the candidate.</t>
-        </is>
-      </c>
-      <c r="G34" s="20" t="n"/>
+          <t>Ask directly about his US plans before an offer is built.</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="n"/>
     </row>
     <row r="35" ht="44" customHeight="1">
       <c r="A35" s="11" t="n">
         <v>31</v>
       </c>
       <c r="B35" s="11" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Sandhosh Kumar</t>
+          <t>Sathya K S</t>
         </is>
       </c>
       <c r="D35" s="32" t="inlineStr">
@@ -6386,26 +6714,26 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Credited with 5 years as Lead; Tech Lead title held only since Apr 2024, about 2.4 years. Four employers between Apr 2021 and Apr 2024, one a six-month stint.</t>
+          <t>Of the 12 years recorded, 4+ were as an Assistant Professor of Computer Science, not industry software engineering.</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Restate the lead span and probe the tenure pattern for retention risk.</t>
-        </is>
-      </c>
-      <c r="G35" s="20" t="n"/>
+          <t>Record industry experience as roughly 8 years and confirm the panel is comfortable with the academic period.</t>
+        </is>
+      </c>
+      <c r="G35" s="21" t="n"/>
     </row>
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="11" t="n">
         <v>32</v>
       </c>
       <c r="B36" s="11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Karthy</t>
+          <t>Navin Kumar</t>
         </is>
       </c>
       <c r="D36" s="32" t="inlineStr">
@@ -6415,26 +6743,26 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Cloud recorded generically at 4 years; the CV shows AWS, not Azure.</t>
+          <t>Credited with 6 years of .Net; the CV shows C# only 2017–2020 and again from Jul 2025 — roughly 3 to 4 years.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Restate as AWS and confirm whether the role needs Azure.</t>
-        </is>
-      </c>
-      <c r="G36" s="20" t="n"/>
+          <t>Restate the .Net span and decide whether a React/Node lead fits the role.</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="n"/>
     </row>
     <row r="37" ht="44" customHeight="1">
       <c r="A37" s="11" t="n">
         <v>33</v>
       </c>
       <c r="B37" s="11" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Sankar Ponnusamy</t>
+          <t>Navin Kumar</t>
         </is>
       </c>
       <c r="D37" s="32" t="inlineStr">
@@ -6444,26 +6772,26 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Location recorded as Erode; the CV says Bangalore.</t>
+          <t>33 L expected against 32.8 L current — a 0.6% hike, out of line with the rest.</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Confirm with the candidate.</t>
-        </is>
-      </c>
-      <c r="G37" s="20" t="n"/>
+          <t>Verify both figures; one is likely mis-keyed.</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="n"/>
     </row>
     <row r="38" ht="44" customHeight="1">
       <c r="A38" s="11" t="n">
         <v>34</v>
       </c>
       <c r="B38" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Shanmuga raja</t>
+          <t>Boopathi Molakgounder</t>
         </is>
       </c>
       <c r="D38" s="32" t="inlineStr">
@@ -6473,26 +6801,26 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>His CV and Adhithyan C’s (SL 13) share an employer and a near-identical structure, wording and skills taxonomy, differing mainly in the client name.</t>
+          <t>Location recorded as Erode; the CV says Bangalore.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Assess the two independently; do not let one interview colour the other.</t>
-        </is>
-      </c>
-      <c r="G38" s="20" t="n"/>
+          <t>Confirm with the candidate.</t>
+        </is>
+      </c>
+      <c r="G38" s="21" t="n"/>
     </row>
     <row r="39" ht="44" customHeight="1">
       <c r="A39" s="11" t="n">
         <v>35</v>
       </c>
       <c r="B39" s="11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Srinidhi Ravi</t>
+          <t>Ravikumar Gopal</t>
         </is>
       </c>
       <c r="D39" s="32" t="inlineStr">
@@ -6502,26 +6830,26 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Entire tech skills list is Java 8, Unix shell, SQL, HTML/CSS, Actimize and AIS — no framework, no cloud, no modern front end, against an 18 L expectation.</t>
+          <t>Credited with 10 years of Java; Java and Spring Boot start Jun 2018 — about 8 years. The 2016–2018 role was Android and IoT.</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Probe what he has actually built, as distinct from supported.</t>
-        </is>
-      </c>
-      <c r="G39" s="20" t="n"/>
+          <t>Restate the Java span, and record the GenAI depth the row currently omits.</t>
+        </is>
+      </c>
+      <c r="G39" s="21" t="n"/>
     </row>
     <row r="40" ht="44" customHeight="1">
       <c r="A40" s="11" t="n">
         <v>36</v>
       </c>
       <c r="B40" s="11" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Prince Kumar P</t>
+          <t>Vaisakh P</t>
         </is>
       </c>
       <c r="D40" s="32" t="inlineStr">
@@ -6531,26 +6859,26 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Sixteen years total, but his own CV puts Java at about 5 years against Node at 7 and Angular at 9.</t>
+          <t>Angular at 4 years appears only on a personal side project, and Lead at 6 years against a title held since Aug 2022.</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Decide whether the opening needs Java depth or accepts a polyglot lead, and brief the panel accordingly.</t>
-        </is>
-      </c>
-      <c r="G40" s="20" t="n"/>
+          <t>Verify both figures with the candidate.</t>
+        </is>
+      </c>
+      <c r="G40" s="21" t="n"/>
     </row>
     <row r="41" ht="44" customHeight="1">
       <c r="A41" s="11" t="n">
         <v>37</v>
       </c>
       <c r="B41" s="11" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Prince Kumar P</t>
+          <t>Sandhosh Kumar</t>
         </is>
       </c>
       <c r="D41" s="32" t="inlineStr">
@@ -6560,26 +6888,26 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>The row claims AWS and Microservices at 12 years each; his AWS work starts at Virtusa in Jan 2020, about six years.</t>
+          <t>Credited with 5 years as Lead; Tech Lead title held only since Apr 2024, about 2.4 years. Four employers between Apr 2021 and Apr 2024, one a six-month stint.</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Restate both spans and brief the panel on the real depth.</t>
-        </is>
-      </c>
-      <c r="G41" s="20" t="n"/>
+          <t>Restate the lead span and probe the tenure pattern for retention risk.</t>
+        </is>
+      </c>
+      <c r="G41" s="21" t="n"/>
     </row>
     <row r="42" ht="44" customHeight="1">
       <c r="A42" s="11" t="n">
         <v>38</v>
       </c>
       <c r="B42" s="11" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Prince Kumar P</t>
+          <t>Karthy</t>
         </is>
       </c>
       <c r="D42" s="32" t="inlineStr">
@@ -6589,26 +6917,26 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>The row says Coimbatore and an LWD of 7 Aug 2026; the CV header says Chennai and still shows Virtusa as current.</t>
+          <t>Cloud recorded generically at 4 years; the CV shows AWS, not Azure.</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Confirm both his location and whether he has actually left.</t>
-        </is>
-      </c>
-      <c r="G42" s="20" t="n"/>
+          <t>Restate as AWS and confirm whether the role needs Azure.</t>
+        </is>
+      </c>
+      <c r="G42" s="21" t="n"/>
     </row>
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="11" t="n">
         <v>39</v>
       </c>
       <c r="B43" s="11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Gangasri Paramasivam</t>
+          <t>Sankar Ponnusamy</t>
         </is>
       </c>
       <c r="D43" s="32" t="inlineStr">
@@ -6618,26 +6946,26 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>E-mail differs between sources: the row gives gangasri.p@gmail.com, the CV says p.gangasri@gmail.com.</t>
+          <t>Location recorded as Erode; the CV says Bangalore.</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Confirm which address reaches her before sending anything.</t>
-        </is>
-      </c>
-      <c r="G43" s="20" t="n"/>
+          <t>Confirm with the candidate.</t>
+        </is>
+      </c>
+      <c r="G43" s="21" t="n"/>
     </row>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="11" t="n">
         <v>40</v>
       </c>
       <c r="B44" s="11" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Gunavadhi A S</t>
+          <t>Shanmuga raja</t>
         </is>
       </c>
       <c r="D44" s="32" t="inlineStr">
@@ -6647,26 +6975,26 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Tech Mahindra engagement is listed as ending August 2026, so she has been out around two months.</t>
+          <t>His CV and Adhithyan C’s (SL 13) share an employer and a near-identical structure, wording and skills taxonomy, differing mainly in the client name.</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Confirm current status and availability.</t>
-        </is>
-      </c>
-      <c r="G44" s="20" t="n"/>
+          <t>Assess the two independently; do not let one interview colour the other.</t>
+        </is>
+      </c>
+      <c r="G44" s="21" t="n"/>
     </row>
     <row r="45" ht="44" customHeight="1">
       <c r="A45" s="11" t="n">
         <v>41</v>
       </c>
       <c r="B45" s="11" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Dhachanamoorthy N</t>
+          <t>Srinidhi Ravi</t>
         </is>
       </c>
       <c r="D45" s="32" t="inlineStr">
@@ -6676,26 +7004,26 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Five years total experience against an architecture-heavy Round 1 — a strong engineer, but the theory set will stretch him.</t>
+          <t>Entire tech skills list is Java 8, Unix shell, SQL, HTML/CSS, Actimize and AIS — no framework, no cloud, no modern front end, against an 18 L expectation.</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Decide whether to score him against the mid-level bar or treat the gaps as expected.</t>
-        </is>
-      </c>
-      <c r="G45" s="20" t="n"/>
+          <t>Probe what he has actually built, as distinct from supported.</t>
+        </is>
+      </c>
+      <c r="G45" s="21" t="n"/>
     </row>
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="11" t="n">
         <v>42</v>
       </c>
       <c r="B46" s="11" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Krishnan K</t>
+          <t>Prince Kumar P</t>
         </is>
       </c>
       <c r="D46" s="32" t="inlineStr">
@@ -6705,26 +7033,26 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Out of employment around four months, and the dates disagree: the vendor row says LWD 5 June 2026, the CV says the Wipro engagement ran to 25 June 2026.</t>
+          <t>Sixteen years total, but his own CV puts Java at about 5 years against Node at 7 and Angular at 9.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Pin down the actual exit date and the reason for the break.</t>
-        </is>
-      </c>
-      <c r="G46" s="20" t="n"/>
+          <t>Decide whether the opening needs Java depth or accepts a polyglot lead, and brief the panel accordingly.</t>
+        </is>
+      </c>
+      <c r="G46" s="21" t="n"/>
     </row>
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="11" t="n">
         <v>43</v>
       </c>
       <c r="B47" s="11" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Krishnan K</t>
+          <t>Prince Kumar P</t>
         </is>
       </c>
       <c r="D47" s="32" t="inlineStr">
@@ -6734,26 +7062,26 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>The vendor row says Coimbatore; his CV address is Madurai.</t>
+          <t>The row claims AWS and Microservices at 12 years each; his AWS work starts at Virtusa in Jan 2020, about six years.</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Confirm where he is actually based and his willingness to be in Coimbatore.</t>
-        </is>
-      </c>
-      <c r="G47" s="20" t="n"/>
+          <t>Restate both spans and brief the panel on the real depth.</t>
+        </is>
+      </c>
+      <c r="G47" s="21" t="n"/>
     </row>
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="11" t="n">
         <v>44</v>
       </c>
       <c r="B48" s="11" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Monish Kanna Bommuraj</t>
+          <t>Prince Kumar P</t>
         </is>
       </c>
       <c r="D48" s="32" t="inlineStr">
@@ -6763,26 +7091,26 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>LWD of 30 Sep 2026 has passed, so he is already out.</t>
+          <t>The row says Coimbatore and an LWD of 7 Aug 2026; the CV header says Chennai and still shows Virtusa as current.</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Confirm current status and availability.</t>
-        </is>
-      </c>
-      <c r="G48" s="20" t="n"/>
+          <t>Confirm both his location and whether he has actually left.</t>
+        </is>
+      </c>
+      <c r="G48" s="21" t="n"/>
     </row>
     <row r="49" ht="44" customHeight="1">
       <c r="A49" s="11" t="n">
         <v>45</v>
       </c>
       <c r="B49" s="11" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Saravana Kumar B</t>
+          <t>Gangasri Paramasivam</t>
         </is>
       </c>
       <c r="D49" s="32" t="inlineStr">
@@ -6792,26 +7120,26 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Out of employment around four months — InFynd ended June 2026.</t>
+          <t>E-mail differs between sources: the row gives gangasri.p@gmail.com, the CV says p.gangasri@gmail.com.</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Confirm current status and the reason for the break.</t>
-        </is>
-      </c>
-      <c r="G49" s="20" t="n"/>
+          <t>Confirm which address reaches her before sending anything.</t>
+        </is>
+      </c>
+      <c r="G49" s="21" t="n"/>
     </row>
     <row r="50" ht="44" customHeight="1">
       <c r="A50" s="11" t="n">
         <v>46</v>
       </c>
       <c r="B50" s="11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>Saravana Kumar B</t>
+          <t>Gunavadhi A S</t>
         </is>
       </c>
       <c r="D50" s="32" t="inlineStr">
@@ -6821,26 +7149,26 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>The row credits Backend Node.js at 5 years; the CV lists Node only in a skills line, and his hands-on work was Python, Java and Selenium up to 2020.</t>
+          <t>Tech Mahindra engagement is listed as ending August 2026, so she has been out around two months.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Restate the Node claim, and decide whether this role needs hands-on backend depth at all.</t>
-        </is>
-      </c>
-      <c r="G50" s="20" t="n"/>
+          <t>Confirm current status and availability.</t>
+        </is>
+      </c>
+      <c r="G50" s="21" t="n"/>
     </row>
     <row r="51" ht="44" customHeight="1">
       <c r="A51" s="11" t="n">
         <v>47</v>
       </c>
       <c r="B51" s="11" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Veena Kuppusamy</t>
+          <t>Dhachanamoorthy N</t>
         </is>
       </c>
       <c r="D51" s="32" t="inlineStr">
@@ -6850,320 +7178,318 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>The row credits 10 years as Technical Project Manager; her PM and TPM titles start Mar 2022, about four years, with the preceding eight as Technical Lead.</t>
+          <t>Five years total experience against an architecture-heavy Round 1 — a strong engineer, but the theory set will stretch him.</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Restate the management span.</t>
-        </is>
-      </c>
-      <c r="G51" s="20" t="n"/>
+          <t>Decide whether to score him against the mid-level bar or treat the gaps as expected.</t>
+        </is>
+      </c>
+      <c r="G51" s="21" t="n"/>
     </row>
     <row r="52" ht="44" customHeight="1">
       <c r="A52" s="11" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="11" t="n">
+        <v>22</v>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Pipeline-wide</t>
-        </is>
-      </c>
-      <c r="D52" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Krishnan K</t>
+        </is>
+      </c>
+      <c r="D52" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>The commercials missing for SL 18–22 have now arrived with the IKrux row of 5 Sep 2026, which also added Monish Kanna Bommuraj.</t>
+          <t>Out of employment around four months, and the dates disagree: the vendor row says LWD 5 June 2026, the CV says the Wipro engagement ran to 25 June 2026.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Closed. Note the 5 Sep batch predates the 21 Sep one, so those six were submitted first.</t>
-        </is>
-      </c>
-      <c r="G52" s="20" t="n"/>
+          <t>Pin down the actual exit date and the reason for the break.</t>
+        </is>
+      </c>
+      <c r="G52" s="21" t="n"/>
     </row>
     <row r="53" ht="44" customHeight="1">
       <c r="A53" s="11" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="11" t="n">
+        <v>22</v>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Pipeline-wide</t>
-        </is>
-      </c>
-      <c r="D53" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Krishnan K</t>
+        </is>
+      </c>
+      <c r="D53" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>All 22 resumes are on file and checked — 17 against their submitted row, and 5 that arrived as resumes only.</t>
+          <t>The vendor row says Coimbatore; his CV address is Madurai.</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Closed. Seventeen of the 22 carry a correction or an open question — see the items below.</t>
-        </is>
-      </c>
-      <c r="G53" s="20" t="n"/>
+          <t>Confirm where he is actually based and his willingness to be in Coimbatore.</t>
+        </is>
+      </c>
+      <c r="G53" s="21" t="n"/>
     </row>
     <row r="54" ht="44" customHeight="1">
       <c r="A54" s="11" t="n">
         <v>50</v>
       </c>
       <c r="B54" s="11" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Amre Binnaz. M</t>
-        </is>
-      </c>
-      <c r="D54" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Monish Kanna Bommuraj</t>
+        </is>
+      </c>
+      <c r="D54" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>‘AI : 0.6 Months’ is ambiguous and describes AI-assisted coding, not AI engineering.</t>
+          <t>LWD of 30 Sep 2026 has passed, so he is already out.</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Restate the AI entry in the units the rest of the sheet uses.</t>
-        </is>
-      </c>
-      <c r="G54" s="20" t="n"/>
+          <t>Confirm current status and availability.</t>
+        </is>
+      </c>
+      <c r="G54" s="21" t="n"/>
     </row>
     <row r="55" ht="44" customHeight="1">
       <c r="A55" s="11" t="n">
         <v>51</v>
       </c>
       <c r="B55" s="11" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Amre Binnaz. M</t>
-        </is>
-      </c>
-      <c r="D55" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Saravana Kumar B</t>
+        </is>
+      </c>
+      <c r="D55" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>The CV carries no education section.</t>
+          <t>Out of employment around four months — InFynd ended June 2026.</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Collect the qualification.</t>
-        </is>
-      </c>
-      <c r="G55" s="20" t="n"/>
+          <t>Confirm current status and the reason for the break.</t>
+        </is>
+      </c>
+      <c r="G55" s="21" t="n"/>
     </row>
     <row r="56" ht="44" customHeight="1">
       <c r="A56" s="11" t="n">
         <v>52</v>
       </c>
       <c r="B56" s="11" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>Navin Kumar</t>
-        </is>
-      </c>
-      <c r="D56" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Saravana Kumar B</t>
+        </is>
+      </c>
+      <c r="D56" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Address reads Tamil Nadu 638701, which is Erode, not Coimbatore; the Nagarro role is remote.</t>
+          <t>The row credits Backend Node.js at 5 years; the CV lists Node only in a skills line, and his hands-on work was Python, Java and Selenium up to 2020.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Confirm his base and his willingness to work onsite.</t>
-        </is>
-      </c>
-      <c r="G56" s="20" t="n"/>
+          <t>Restate the Node claim, and decide whether this role needs hands-on backend depth at all.</t>
+        </is>
+      </c>
+      <c r="G56" s="21" t="n"/>
     </row>
     <row r="57" ht="44" customHeight="1">
       <c r="A57" s="11" t="n">
         <v>53</v>
       </c>
       <c r="B57" s="11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Vaisakh P</t>
-        </is>
-      </c>
-      <c r="D57" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Veena Kuppusamy</t>
+        </is>
+      </c>
+      <c r="D57" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Two employment gaps: Mar to Aug 2017, and Dec 2019 to Jul 2020.</t>
+          <t>The row credits 10 years as Technical Project Manager; her PM and TPM titles start Mar 2022, about four years, with the preceding eight as Technical Lead.</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Ask him to account for both.</t>
-        </is>
-      </c>
-      <c r="G57" s="20" t="n"/>
+          <t>Restate the management span.</t>
+        </is>
+      </c>
+      <c r="G57" s="21" t="n"/>
     </row>
     <row r="58" ht="44" customHeight="1">
       <c r="A58" s="11" t="n">
         <v>54</v>
       </c>
       <c r="B58" s="11" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Sandhosh Kumar</t>
-        </is>
-      </c>
-      <c r="D58" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Dinesh Kumar C</t>
+        </is>
+      </c>
+      <c r="D58" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Early career was PHP and LAMP, which the recorded skill split does not mention.</t>
+          <t>His PMO work is commercial operations — contract-to-cash, timesheets, billing, receivables — rather than process design or improvement, and the first four years were securities trade settlement.</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Add it for completeness.</t>
-        </is>
-      </c>
-      <c r="G58" s="20" t="n"/>
+          <t>Confirm the remit this role actually carries before the panel meets him.</t>
+        </is>
+      </c>
+      <c r="G58" s="21" t="n"/>
     </row>
     <row r="59" ht="44" customHeight="1">
       <c r="A59" s="11" t="n">
         <v>55</v>
       </c>
       <c r="B59" s="11" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Manoj</t>
-        </is>
-      </c>
-      <c r="D59" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Dinesh Kumar C</t>
+        </is>
+      </c>
+      <c r="D59" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Location recorded as ‘Bangalore / Coimbatore’.</t>
+          <t>No process or project management certification anywhere on the CV — no PMP, Prince2, Lean or Six Sigma; the MBA is in Finance.</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Record a single current location.</t>
-        </is>
-      </c>
-      <c r="G59" s="20" t="n"/>
+          <t>Decide whether the role requires one, and say so in the brief.</t>
+        </is>
+      </c>
+      <c r="G59" s="21" t="n"/>
     </row>
     <row r="60" ht="44" customHeight="1">
       <c r="A60" s="11" t="n">
         <v>56</v>
       </c>
       <c r="B60" s="11" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Shanmuga raja</t>
-        </is>
-      </c>
-      <c r="D60" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Sowdhamini J</t>
+        </is>
+      </c>
+      <c r="D60" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>E-mail address was supplied with a leading space.</t>
+          <t>Her ten years are BPO operations — medical billing, airlines, customer support, sales and billing — not IT project or delivery process management.</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Corrected here; fix at source so mail merges do not fail.</t>
-        </is>
-      </c>
-      <c r="G60" s="20" t="n"/>
+          <t>Decide whether this opening is an operations role before scheduling a panel.</t>
+        </is>
+      </c>
+      <c r="G60" s="21" t="n"/>
     </row>
     <row r="61" ht="44" customHeight="1">
       <c r="A61" s="11" t="n">
         <v>57</v>
       </c>
       <c r="B61" s="11" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Prince Kumar P</t>
-        </is>
-      </c>
-      <c r="D61" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Sowdhamini J</t>
+        </is>
+      </c>
+      <c r="D61" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Project dates overlap: Discern runs Jan 2016 to Dec 2020 while Treselle ends Jan 2020 and Virtusa starts the same month.</t>
+          <t>The row gives sowdhaminij@yahoo.com; her CV gives sowdhaminij5908@gmail.com.</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Ask him to clarify the overlap.</t>
-        </is>
-      </c>
-      <c r="G61" s="20" t="n"/>
+          <t>Confirm which address reaches her before anything is sent.</t>
+        </is>
+      </c>
+      <c r="G61" s="21" t="n"/>
     </row>
     <row r="62" ht="44" customHeight="1">
       <c r="A62" s="11" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="11" t="n">
-        <v>20</v>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Gunavadhi A S</t>
+          <t>Pipeline-wide</t>
         </is>
       </c>
       <c r="D62" s="33" t="inlineStr">
@@ -7173,26 +7499,28 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>MCA is recorded as coursework completed rather than awarded; the completed degree is a B.Sc.</t>
+          <t>The commercials missing for SL 18–22 have now arrived with the IKrux row of 5 Sep 2026, which also added Monish Kanna Bommuraj.</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Confirm the highest qualification actually held.</t>
-        </is>
-      </c>
-      <c r="G62" s="20" t="n"/>
+          <t>Closed. Note the 5 Sep batch predates the 21 Sep one, so those six were submitted first.</t>
+        </is>
+      </c>
+      <c r="G62" s="21" t="n"/>
     </row>
     <row r="63" ht="44" customHeight="1">
       <c r="A63" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="11" t="n">
-        <v>21</v>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Dhachanamoorthy N</t>
+          <t>Pipeline-wide</t>
         </is>
       </c>
       <c r="D63" s="33" t="inlineStr">
@@ -7202,26 +7530,26 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>The CV states no location; the vendor row gives Coimbatore.</t>
+          <t>All 22 resumes are on file and checked — 17 against their submitted row, and 5 that arrived as resumes only.</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Closed by the 5 Sep row — confirm verbally at screening.</t>
-        </is>
-      </c>
-      <c r="G63" s="20" t="n"/>
+          <t>Closed. Seventeen of the 22 carry a correction or an open question — see the items below.</t>
+        </is>
+      </c>
+      <c r="G63" s="21" t="n"/>
     </row>
     <row r="64" ht="44" customHeight="1">
       <c r="A64" s="11" t="n">
         <v>60</v>
       </c>
       <c r="B64" s="11" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>Krishnan K</t>
+          <t>Amre Binnaz. M</t>
         </is>
       </c>
       <c r="D64" s="33" t="inlineStr">
@@ -7231,26 +7559,26 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Degree is BE Electrical and Electronics rather than computer science, and the CV is list-heavy with thin description of personal contribution.</t>
+          <t>‘AI : 0.6 Months’ is ambiguous and describes AI-assisted coding, not AI engineering.</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Probe for what he personally designed and built in the technical round.</t>
-        </is>
-      </c>
-      <c r="G64" s="20" t="n"/>
+          <t>Restate the AI entry in the units the rest of the sheet uses.</t>
+        </is>
+      </c>
+      <c r="G64" s="21" t="n"/>
     </row>
     <row r="65" ht="44" customHeight="1">
       <c r="A65" s="11" t="n">
         <v>61</v>
       </c>
       <c r="B65" s="11" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Monish Kanna Bommuraj</t>
+          <t>Amre Binnaz. M</t>
         </is>
       </c>
       <c r="D65" s="33" t="inlineStr">
@@ -7260,26 +7588,26 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>The row credits React: 2+ Years; the CV mentions React once, on a single pharmacy application.</t>
+          <t>The CV carries no education section.</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Verify the React depth if the role needs front-end work.</t>
-        </is>
-      </c>
-      <c r="G65" s="20" t="n"/>
+          <t>Collect the qualification.</t>
+        </is>
+      </c>
+      <c r="G65" s="21" t="n"/>
     </row>
     <row r="66" ht="44" customHeight="1">
       <c r="A66" s="11" t="n">
         <v>62</v>
       </c>
       <c r="B66" s="11" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Monish Kanna Bommuraj</t>
+          <t>Navin Kumar</t>
         </is>
       </c>
       <c r="D66" s="33" t="inlineStr">
@@ -7289,44 +7617,392 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Accenture is his only employer across all five years, and the degree is B.E. Mechatronics rather than computer science.</t>
+          <t>Address reads Tamil Nadu 638701, which is Erode, not Coimbatore; the Nagarro role is remote.</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Probe adaptability outside a single engineering culture; the CGPA of 8.97 and the Azure certification offset the degree.</t>
-        </is>
-      </c>
-      <c r="G66" s="20" t="n"/>
+          <t>Confirm his base and his willingness to work onsite.</t>
+        </is>
+      </c>
+      <c r="G66" s="21" t="n"/>
     </row>
     <row r="67" ht="44" customHeight="1">
       <c r="A67" s="11" t="n">
         <v>63</v>
       </c>
       <c r="B67" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>Vaisakh P</t>
+        </is>
+      </c>
+      <c r="D67" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Two employment gaps: Mar to Aug 2017, and Dec 2019 to Jul 2020.</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>Ask him to account for both.</t>
+        </is>
+      </c>
+      <c r="G67" s="21" t="n"/>
+    </row>
+    <row r="68" ht="44" customHeight="1">
+      <c r="A68" s="11" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>Sandhosh Kumar</t>
+        </is>
+      </c>
+      <c r="D68" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Early career was PHP and LAMP, which the recorded skill split does not mention.</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>Add it for completeness.</t>
+        </is>
+      </c>
+      <c r="G68" s="21" t="n"/>
+    </row>
+    <row r="69" ht="44" customHeight="1">
+      <c r="A69" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>Manoj</t>
+        </is>
+      </c>
+      <c r="D69" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Location recorded as ‘Bangalore / Coimbatore’.</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>Record a single current location.</t>
+        </is>
+      </c>
+      <c r="G69" s="21" t="n"/>
+    </row>
+    <row r="70" ht="44" customHeight="1">
+      <c r="A70" s="11" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>Shanmuga raja</t>
+        </is>
+      </c>
+      <c r="D70" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>E-mail address was supplied with a leading space.</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Corrected here; fix at source so mail merges do not fail.</t>
+        </is>
+      </c>
+      <c r="G70" s="21" t="n"/>
+    </row>
+    <row r="71" ht="44" customHeight="1">
+      <c r="A71" s="11" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>Prince Kumar P</t>
+        </is>
+      </c>
+      <c r="D71" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Project dates overlap: Discern runs Jan 2016 to Dec 2020 while Treselle ends Jan 2020 and Virtusa starts the same month.</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Ask him to clarify the overlap.</t>
+        </is>
+      </c>
+      <c r="G71" s="21" t="n"/>
+    </row>
+    <row r="72" ht="44" customHeight="1">
+      <c r="A72" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>Gunavadhi A S</t>
+        </is>
+      </c>
+      <c r="D72" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>MCA is recorded as coursework completed rather than awarded; the completed degree is a B.Sc.</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Confirm the highest qualification actually held.</t>
+        </is>
+      </c>
+      <c r="G72" s="21" t="n"/>
+    </row>
+    <row r="73" ht="44" customHeight="1">
+      <c r="A73" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>Dhachanamoorthy N</t>
+        </is>
+      </c>
+      <c r="D73" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>The CV states no location; the vendor row gives Coimbatore.</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Closed by the 5 Sep row — confirm verbally at screening.</t>
+        </is>
+      </c>
+      <c r="G73" s="21" t="n"/>
+    </row>
+    <row r="74" ht="44" customHeight="1">
+      <c r="A74" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>Krishnan K</t>
+        </is>
+      </c>
+      <c r="D74" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>Degree is BE Electrical and Electronics rather than computer science, and the CV is list-heavy with thin description of personal contribution.</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>Probe for what he personally designed and built in the technical round.</t>
+        </is>
+      </c>
+      <c r="G74" s="21" t="n"/>
+    </row>
+    <row r="75" ht="44" customHeight="1">
+      <c r="A75" s="11" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>Monish Kanna Bommuraj</t>
+        </is>
+      </c>
+      <c r="D75" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>The row credits React: 2+ Years; the CV mentions React once, on a single pharmacy application.</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>Verify the React depth if the role needs front-end work.</t>
+        </is>
+      </c>
+      <c r="G75" s="21" t="n"/>
+    </row>
+    <row r="76" ht="44" customHeight="1">
+      <c r="A76" s="11" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>Monish Kanna Bommuraj</t>
+        </is>
+      </c>
+      <c r="D76" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Accenture is his only employer across all five years, and the degree is B.E. Mechatronics rather than computer science.</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>Probe adaptability outside a single engineering culture; the CGPA of 8.97 and the Azure certification offset the degree.</t>
+        </is>
+      </c>
+      <c r="G76" s="21" t="n"/>
+    </row>
+    <row r="77" ht="44" customHeight="1">
+      <c r="A77" s="11" t="n">
+        <v>73</v>
+      </c>
+      <c r="B77" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="C67" s="12" t="inlineStr">
+      <c r="C77" s="12" t="inlineStr">
         <is>
           <t>Veena Kuppusamy</t>
         </is>
       </c>
-      <c r="D67" s="33" t="inlineStr">
+      <c r="D77" s="33" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>Her CV opens with personal details including religion and marital status.</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t>Brief the panel to disregard protected characteristics; assess on the professional record only.</t>
         </is>
       </c>
-      <c r="G67" s="20" t="n"/>
+      <c r="G77" s="21" t="n"/>
+    </row>
+    <row r="78" ht="44" customHeight="1">
+      <c r="A78" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>Dinesh Kumar C</t>
+        </is>
+      </c>
+      <c r="D78" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>No location appears anywhere on his CV; the row records Coimbatore.</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>Confirm he is in Coimbatore or will relocate.</t>
+        </is>
+      </c>
+      <c r="G78" s="21" t="n"/>
+    </row>
+    <row r="79" ht="44" customHeight="1">
+      <c r="A79" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>Sowdhamini J</t>
+        </is>
+      </c>
+      <c r="D79" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Her current employer ATAIN is in Bangalore, while both the row and her CV header say Coimbatore.</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>Confirm where she is based now and whether the ATAIN role was remote.</t>
+        </is>
+      </c>
+      <c r="G79" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7334,7 +8010,7 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In Progress,Closed,Not Applicable"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7348,7 +8024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7370,7 +8046,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>62 questions across the seven topics. Each candidate draws one per topic from the pool matching their competency stream and level; recycling moves to the next in that pool.</t>
+          <t>90 questions across the seven topics. Each candidate draws one per topic from the pool matching their competency stream and level; recycling moves to the next in that pool.</t>
         </is>
       </c>
     </row>
@@ -9581,8 +10257,988 @@
         </is>
       </c>
     </row>
+    <row r="67" ht="118" customHeight="1">
+      <c r="A67" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>Delivery governance</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>Any delivery</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>What does your weekly governance pack actually contain, and who reads which part of it?</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>A good answer separates the audiences. The team needs the work-level view — what is in flight, what is blocked, the defect trend. The client needs outcomes against commitments: milestones, scope changes, risks and the decisions they owe us. Internal leadership needs the commercial and resourcing picture: utilisation, margin, staffing gaps, escalations. It names a cadence — daily standup, weekly status, monthly business review — and says which decisions each forum is allowed to take. Strong candidates add that the pack is generated from the tracker rather than assembled by hand, and that every red item carries a named owner and a date.</t>
+        </is>
+      </c>
+      <c r="G67" s="35" t="inlineStr">
+        <is>
+          <t>Weak answers describe a slide template. Push on who owns each red item, and what happens between two weekly reports when something goes wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="118" customHeight="1">
+      <c r="A68" s="11" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>Delivery governance</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>Any delivery</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>A project reports green every week and then misses its date. What was wrong with the governance?</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>Watermelon reporting — green outside, red inside. The usual causes: status is self-reported by the people who would be blamed for red, progress is measured by activity rather than finished and accepted work, there is no agreed definition of done, risks are logged but never costed, and raising a problem has been punished before. The fixes are structural: measure against accepted deliverables, watch leading indicators — open defects, scope added after baseline, dependency ageing, velocity trend — rather than a RAG dot, make the first red free, and sample-audit rather than trusting the roll-up.</t>
+        </is>
+      </c>
+      <c r="G68" s="35" t="inlineStr">
+        <is>
+          <t>Listen for whether they have been on the wrong end of this themselves. Ask which leading indicator would have caught it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="118" customHeight="1">
+      <c r="A69" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>Delivery governance</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>PMO / delivery ops</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Walk me through contract-to-cash end to end, and tell me where it usually breaks.</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>Contract or SOW signed, project and rate set up, resources allocated against the code, time entered and approved, billing run, invoice issued, receipt and collections, revenue recognised — with unbilled and accruals tracked throughout. The common breaks: work starting before the SOW is signed or before a project code exists, so time is parked somewhere unbillable; timesheets missing the approval cut-off; rate amendments not loaded before the billing run; allocations left open after someone rolls off; disputed invoices with no owner; and unbilled ageing because nobody reconciles it monthly.</t>
+        </is>
+      </c>
+      <c r="G69" s="35" t="inlineStr">
+        <is>
+          <t>Ask for a specific control they put in to stop revenue leakage — and how they found the leak in the first place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="118" customHeight="1">
+      <c r="A70" s="11" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>Delivery governance</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>Service operations</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>How do you run a shift so that service levels hold on the worst day of the month?</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Plan from the volume forecast and the shrinkage you actually see rather than the budgeted figure; roster to the interval, not the day; keep a flex pool or cross-trained agents; take adherence commitments from team leads the day before rather than on the morning; watch intraday against forecast and move people at the first divergence, not at the breach. Have a documented escalation for queue depth and a pre-agreed degradation — what you stop doing first. Afterwards the exception is reviewed, not merely survived.</t>
+        </is>
+      </c>
+      <c r="G70" s="35" t="inlineStr">
+        <is>
+          <t>Ask what they stop doing when they are short. A candidate with no pre-agreed answer has been improvising.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="118" customHeight="1">
+      <c r="A71" s="11" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>Planning and estimation</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>Any delivery</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>How do you estimate a piece of work nobody in the team has done before?</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Break it down until the pieces resemble something already delivered, then combine analogy with bottom-up for the known parts. Give a range with the assumptions that would move it, and keep the estimate separate from the commitment. Allow explicitly for integration, test, environments, rework and non-project time rather than adding a flat fudge. Re-estimate once a first slice is genuinely built. Record the assumptions in the SOW so that a changed assumption becomes a change request rather than an argument.</t>
+        </is>
+      </c>
+      <c r="G71" s="35" t="inlineStr">
+        <is>
+          <t>Push on what they do when the answer is ‘too long’. A candidate who compresses the estimate rather than the scope is a risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="118" customHeight="1">
+      <c r="A72" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>Planning and estimation</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>Any delivery</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>The client wants a fixed date and a fixed scope. How do you respond?</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Something has to flex — date, scope, cost or quality — and quality is the one that flexes silently if nobody chooses. The useful answer holds the date, negotiates a prioritised scope with a defined minimum, phases the rest, and puts the trade-off in writing with the assumptions behind it. If the business truly needs both, add capacity early rather than late, buy down the riskiest item first, and agree a checkpoint at which scope is re-cut if the burn says the date is at risk.</t>
+        </is>
+      </c>
+      <c r="G72" s="35" t="inlineStr">
+        <is>
+          <t>Watch for a candidate who simply agrees. Ask what they have personally refused, and what happened next.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="118" customHeight="1">
+      <c r="A73" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>Planning and estimation</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>PMO / delivery ops</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>How do you build a forecast for a project that is already running?</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Actuals to date from time and billing, committed allocations for the remaining months, rate card by grade and location, and the known changes — roll-offs, rate amendments, planned ramps, leave and holiday calendars. Reconcile the bottom-up resource forecast against contract value and the revenue already recognised, and show unbilled and collections separately. Strong answers re-forecast monthly, explain variance against the last forecast rather than the original plan, and flag the month in which the project runs out of contract value.</t>
+        </is>
+      </c>
+      <c r="G73" s="35" t="inlineStr">
+        <is>
+          <t>Ask how they treat someone allocated but not billable, and what they do when the forecast and the contract value diverge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="118" customHeight="1">
+      <c r="A74" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>Planning and estimation</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>Service operations</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>How do you size a team for a process you are taking over?</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>From volume and handle time: forecast volume per interval, average handle time and its spread, occupancy target, shrinkage covering leave, training, breaks and attrition, and the service level required. A capacity or Erlang model gives required heads; then add ramp, trainer time and a nesting period before new hires carry full load, and allow for the learning curve raising handle time in the early weeks. Reconcile against the client’s budget and say plainly where the model and the budget disagree.</t>
+        </is>
+      </c>
+      <c r="G74" s="35" t="inlineStr">
+        <is>
+          <t>Ask for their shrinkage assumption and where the number came from. A figure with no source is a guess.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="118" customHeight="1">
+      <c r="A75" s="11" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>Risk and escalation</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>Any delivery</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>What makes a risk log useful rather than theatre?</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>Every risk has an owner, an observable trigger, an impact in money or days rather than high/medium/low alone, a mitigation someone is actually doing, and a review date. Risks are retired or realised rather than carried forever, and the log drives the governance conversation instead of being read out at it. Strong answers separate risk from issue from dependency, and can point to contingency that was genuinely budgeted rather than hoped for.</t>
+        </is>
+      </c>
+      <c r="G75" s="35" t="inlineStr">
+        <is>
+          <t>Ask for a risk they logged that then happened, and whether the mitigation actually worked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="118" customHeight="1">
+      <c r="A76" s="11" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>Risk and escalation</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>Any delivery</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>When do you escalate, and how do you escalate without burning the relationship?</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>Escalate when the issue is outside your authority, when the agreed mitigation has failed, or when a commitment is going to move — and before the impact lands, not after. Good escalation is pre-warned, so the counterpart hears it from you first and never in a report; specific about what you need and by when; carries options rather than a complaint; and travels up your line and the client’s in step. It stays about the problem and the decision rather than the person.</t>
+        </is>
+      </c>
+      <c r="G76" s="35" t="inlineStr">
+        <is>
+          <t>Ask about an escalation they regret, or one they left too late.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="118" customHeight="1">
+      <c r="A77" s="11" t="n">
+        <v>73</v>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>Risk and escalation</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>PMO / delivery ops</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>You discover that four months of work has been delivered against an SOW that was never signed. What do you do?</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>Stop the bleeding first: establish the exact exposure in hours, cost, people and dates, get the work covered going forward through a letter of intent, an interim PO or an instruction to pause, and tell your own leadership immediately — this is a revenue and audit problem, not paperwork. Then assemble evidence of the work and of the client’s acceptance, negotiate retrospective cover, and book the unbilled position honestly rather than hiding it. Afterwards, put in the control that would have caught it: no project code and no allocation without a signed SOW.</t>
+        </is>
+      </c>
+      <c r="G77" s="35" t="inlineStr">
+        <is>
+          <t>Listen for whether they tell anyone. A candidate who quietly fixes it is the real risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="118" customHeight="1">
+      <c r="A78" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>Risk and escalation</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>Service operations</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>An attrition spike takes 15% of your tenured agents in a month. Walk me through the first two weeks.</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>Stabilise service first: re-roster, pull in the flex pool, pause non-critical work, protect the hardest queues with the most tenured people, and tell the client before the numbers do. In parallel find the cause rather than assuming it — exit conversations, stay conversations with those most likely to go next, and the data by shift, team lead and tenure band. Then act on what the data says; the honest answers are usually pay, roster or one specific supervisor. Start hiring and nesting knowing it will not help for weeks, and say so rather than promising a recovery you cannot deliver.</t>
+        </is>
+      </c>
+      <c r="G78" s="35" t="inlineStr">
+        <is>
+          <t>Ask what the real cause turned out to be last time, and whether they could fix it or only report it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="118" customHeight="1">
+      <c r="A79" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>Stakeholder management</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>Any delivery</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>How do you handle a stakeholder who keeps changing what they want?</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>Separate the pattern from the person: churn usually means the requirement was never really agreed, or two stakeholders disagree and you are the channel between them. Fix it structurally — one accountable decision-maker per area, decisions recorded with dates, a change process that prices and schedules each change rather than refusing it, and a backlog they prioritise themselves so the trade-off is theirs. Then show the cost of churn in their own currency: a change log with the days and the money it has already taken.</t>
+        </is>
+      </c>
+      <c r="G79" s="35" t="inlineStr">
+        <is>
+          <t>Ask how they get two senior stakeholders who disagree into the same room, rather than relaying between them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="118" customHeight="1">
+      <c r="A80" s="11" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>Stakeholder management</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>Any delivery</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>How do you deliver bad news to a client?</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>Early, directly, on a call rather than in a report: the facts, the impact, the options, your recommendation and the ask. Own your part without over-apologising or blaming the team, bring the recovery plan and the date of the next update, then meet that date. Strong candidates pre-brief their own management and any sponsor who should not be surprised in front of their peers.</t>
+        </is>
+      </c>
+      <c r="G80" s="35" t="inlineStr">
+        <is>
+          <t>Ask for the last time they did it and how the client reacted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="118" customHeight="1">
+      <c r="A81" s="11" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>Stakeholder management</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>PMO / delivery ops</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>The client disputes an invoice. Take me through what you do.</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>Acknowledge quickly and commit to a date for the answer. Pull the backing — approved timesheets, allocation records, the rate card version in force, the SOW clause and any amendment — and establish whether the dispute is factual, a process failure on our side, or a negotiation. Get the undisputed portion paid now and ring-fence the rest. Fix the root cause, whether that is a wrong rate loaded, unapproved time billed, or a resource billed after roll-off. Keep the ageing visible so it does not drift into a write-off by neglect.</t>
+        </is>
+      </c>
+      <c r="G81" s="35" t="inlineStr">
+        <is>
+          <t>Ask about a dispute they lost, and what the real cause was.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="118" customHeight="1">
+      <c r="A82" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>Stakeholder management</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>Service operations</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>What does a good monthly business review with the client look like?</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>Performance against the agreed metrics with the misses explained and owned, the trend rather than a single month, what changed as a result of last month’s actions, what you need from the client — forecast accuracy, system access, decisions — and one or two improvements proposed with the benefit quantified. It is a working session, not a read-out. Strong candidates never put a number in front of the client that the client’s own team has not already seen.</t>
+        </is>
+      </c>
+      <c r="G82" s="35" t="inlineStr">
+        <is>
+          <t>Ask what they do when the client’s own volume forecast is what caused the miss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="118" customHeight="1">
+      <c r="A83" s="11" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>Metrics and improvement</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>Any delivery</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Which handful of metrics tell you whether delivery is actually healthy?</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>A small set, each with a reason: throughput or velocity as a trend rather than an absolute, milestone or schedule variance, defect escape rate and rework, scope added after baseline, dependency ageing, and on the people side utilisation against attrition. A good answer insists on counterweighted pairs so no single number can be gamed — speed against quality, utilisation against attrition — and acts when the trend turns rather than when a threshold breaks.</t>
+        </is>
+      </c>
+      <c r="G83" s="35" t="inlineStr">
+        <is>
+          <t>Ask which metric they have seen gamed, and how they noticed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="118" customHeight="1">
+      <c r="A84" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>Metrics and improvement</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>Any delivery</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>Describe an improvement you made where you can state the before and the after number.</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>Looking for a concrete case: the baseline and how it was measured, the cause established from evidence rather than assumed, the change made, the result, and whether it still held six months later. Strong answers name the thing that did not work first, and say what stopped the improvement decaying — a control chart, a checklist, an automated check, or a named owner.</t>
+        </is>
+      </c>
+      <c r="G84" s="35" t="inlineStr">
+        <is>
+          <t>If the number is suspiciously round, ask how it was measured before the change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="118" customHeight="1">
+      <c r="A85" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>Metrics and improvement</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>PMO / delivery ops</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>How would you measure whether the PMO is worth what it costs?</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>In outcomes the business already cares about: days sales outstanding and collections, unbilled ageing, leakage found and prevented, billing accuracy and credit notes issued, forecast accuracy against actuals, elapsed time from SOW signature to project start, and utilisation against target. A PMO that only reports is a cost; one that shortens the cash cycle and prevents leakage pays for itself, and a good candidate can say roughly by how much.</t>
+        </is>
+      </c>
+      <c r="G85" s="35" t="inlineStr">
+        <is>
+          <t>Ask what they would stop doing if the PMO had to be cut by a third.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="118" customHeight="1">
+      <c r="A86" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>Metrics and improvement</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>Service operations</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>Take me through one Lean Six Sigma project you ran, at the level of the actual data.</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>Define: the problem in the customer’s terms with a baseline. Measure: how the data was collected and whether the measurement system itself was trustworthy. Analyse: the cause established from data rather than opinion, with the tool named — Pareto, a fishbone whose branches were actually verified, a hypothesis genuinely tested. Improve: the change and its pilot. Control: the chart, the limits and the owner that keep it. Strong candidates are honest about the step they usually have to redo, and can name a project where the data overturned their first hypothesis.</t>
+        </is>
+      </c>
+      <c r="G86" s="35" t="inlineStr">
+        <is>
+          <t>A Black Belt who cannot describe the measurement system analysis, or who has no example of the data proving them wrong, has done the training rather than the work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="118" customHeight="1">
+      <c r="A87" s="11" t="n">
+        <v>83</v>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>People and team management</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>Any delivery</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>How do you deal with someone who is not performing?</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>Establish the facts before the conversation: what the expectation was, whether it was ever made explicit, and whether the cause is capability, clarity, workload or something outside work. Then a direct, private, specific conversation — what is happening, what is expected, what support, by when, and what follows if it does not change — documented, and followed up on the date promised. Strong answers include cases where the cause turned out to be theirs, through unclear expectations or badly matched work, and cases they did have to exit, handled without humiliating the person.</t>
+        </is>
+      </c>
+      <c r="G87" s="35" t="inlineStr">
+        <is>
+          <t>Ask for one they turned around and one they could not. Someone who has only ever succeeded has not had the conversation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="118" customHeight="1">
+      <c r="A88" s="11" t="n">
+        <v>84</v>
+      </c>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>People and team management</t>
+        </is>
+      </c>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>Any delivery</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>How do you keep a team motivated through a long, unglamorous piece of work?</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>Honesty about why it matters and how long it will last; visible progress against something finite; rotation so nobody carries the worst of it for months; removing the friction that makes dull work worse; specific rather than generic recognition; and protecting time off instead of praising heroics. A good answer admits motivation is mostly the absence of avoidable annoyance, and handles money and promotion honestly rather than hinting.</t>
+        </is>
+      </c>
+      <c r="G88" s="35" t="inlineStr">
+        <is>
+          <t>Ask what they personally did about the dullest part, not what they told the team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="118" customHeight="1">
+      <c r="A89" s="11" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>People and team management</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>PMO / delivery ops</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>You depend on people who do not report to you — project managers, finance, account managers. How do you get them to do what the process needs?</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>Make the right thing easy and the wrong thing visible: hang the deadline off one they already have, such as the billing cut-off; put the gap in a report their own manager reads; send a pre-filled form rather than a request; and give the reason in their currency — the PM cares about margin, finance about the close, the account manager about the client. Build the relationship before you need it, escalate rarely and predictably, and never let someone first see their own name on a red item in front of their boss.</t>
+        </is>
+      </c>
+      <c r="G89" s="35" t="inlineStr">
+        <is>
+          <t>Ask about someone who simply would not comply, and what finally worked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="118" customHeight="1">
+      <c r="A90" s="11" t="n">
+        <v>86</v>
+      </c>
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>People and team management</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>Service operations</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>Your team leads give you adherence commitments they do not keep. What do you do?</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>First check whether the commitment was realistic — a roster built on budgeted shrinkage rather than actual sets people up to fail. Then make the gap visible daily rather than monthly, hold each lead to their own number in front of their peers without humiliating them, and find which constraint is real: transport, split shifts, a leave policy, one chronically short team. Fix the constraint where you can and hold the line where you cannot. Strong answers make the data self-serve so leads see their own gap before you do.</t>
+        </is>
+      </c>
+      <c r="G90" s="35" t="inlineStr">
+        <is>
+          <t>Ask what they did about the one lead who never improved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="118" customHeight="1">
+      <c r="A91" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>Commercials and resourcing</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>Any delivery</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>What drives margin on a services engagement, and what can you actually control?</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>Price is largely set at sale. Delivery controls the grade pyramid, the location mix, utilisation of the billed team, non-billable effort, rework, and scope absorbed without a change request — plus leakage through unapproved time, late billing, unbilled ageing and discounts given to settle disputes. A good answer names the lever with the biggest effect in their own experience, usually grade mix or absorbed scope, and says what they changed.</t>
+        </is>
+      </c>
+      <c r="G91" s="35" t="inlineStr">
+        <is>
+          <t>Ask what they gave away last year without raising a change request, and why.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="118" customHeight="1">
+      <c r="A92" s="11" t="n">
+        <v>88</v>
+      </c>
+      <c r="B92" s="12" t="inlineStr">
+        <is>
+          <t>Commercials and resourcing</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>Any delivery</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>A key person is leaving mid-project. What do you do, in order?</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>Assess exposure first: what only they know, what is in flight, what the client-facing impact is. Secure the knowledge while they are still there — documented handover, pairing, recorded walkthroughs, and the unglamorous items such as access, credentials and the undocumented runbook. Rebalance the plan honestly rather than assuming a replacement is immediately equivalent, tell the client if a commitment moves, and start the backfill knowing the ramp. Afterwards, remove the single point of failure instead of recreating it.</t>
+        </is>
+      </c>
+      <c r="G92" s="35" t="inlineStr">
+        <is>
+          <t>Ask what they have done to stop one person becoming indispensable in the first place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="118" customHeight="1">
+      <c r="A93" s="11" t="n">
+        <v>89</v>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>Commercials and resourcing</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>PMO / delivery ops</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>How do you manage allocations and utilisation across several projects at once?</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>One source of truth for who is allocated where and at what percentage, kept current, with allocations closed on roll-off rather than left running. Watch bench and partial allocations, which hide inside an average, and reconcile allocation against timesheets, because the two diverge quietly. Forecast the roll-off calendar forward so bench is seen before it arrives, and work the pipeline with account managers rather than reacting. Report utilisation against billable capacity rather than head count, and be explicit about trainees, leave and non-billable commitments.</t>
+        </is>
+      </c>
+      <c r="G93" s="35" t="inlineStr">
+        <is>
+          <t>Ask how they catch someone allocated to two projects at 100% each.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="118" customHeight="1">
+      <c r="A94" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>Commercials and resourcing</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="inlineStr">
+        <is>
+          <t>Service operations</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>How do you hold a cost line when the client wants more without paying more?</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>Quantify the ask in heads and rupees and put it in front of them, and distinguish a genuine volume change — which the contract should already price — from scope creep dressed up as one more report. Offer the trade: we can do this if we stop that, or if the volume forecast holds. Get the decision in writing. Where the relationship matters, give something small and visible and hold the line on the expensive thing, and keep a running log of absorbed asks so the next commercial conversation has evidence.</t>
+        </is>
+      </c>
+      <c r="G94" s="35" t="inlineStr">
+        <is>
+          <t>Ask what they absorbed anyway, and what it cost.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G66"/>
+  <autoFilter ref="A4:G94"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -9597,7 +11253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H179"/>
+  <dimension ref="A1:H193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -9620,7 +11276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The default draw for each of the 22 candidates: one question per topic, with the expected answer. Recycling in the portal moves to the next question in that topic's pool.</t>
+          <t>The default draw for each of the 27 candidates: one question per topic, with the expected answer. Recycling in the portal moves to the next question in that topic's pool. Engineers draw the theory topics; the project and process managers draw the delivery set.</t>
         </is>
       </c>
     </row>
@@ -13866,8 +15522,344 @@
       </c>
       <c r="H179" s="39" t="n"/>
     </row>
+    <row r="180" ht="108" customHeight="1">
+      <c r="A180" s="36" t="n">
+        <v>26</v>
+      </c>
+      <c r="B180" s="37" t="inlineStr">
+        <is>
+          <t>Dinesh Kumar C</t>
+        </is>
+      </c>
+      <c r="C180" s="38" t="inlineStr">
+        <is>
+          <t>PMO / delivery ops</t>
+        </is>
+      </c>
+      <c r="D180" s="36" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>Delivery governance</t>
+        </is>
+      </c>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>What does your weekly governance pack actually contain, and who reads which part of it?</t>
+        </is>
+      </c>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>A good answer separates the audiences. The team needs the work-level view — what is in flight, what is blocked, the defect trend. The client needs outcomes against commitments: milestones, scope changes, risks and the decisions they owe us. Internal leadership needs the commercial and resourcing picture: utilisation, margin, staffing gaps, escalations. It names a cadence — daily standup, weekly status, monthly business review — and says which decisions each forum is allowed to take. Strong candidates add that the pack is generated from the tracker rather than assembled by hand, and that every red item carries a named owner and a date.</t>
+        </is>
+      </c>
+      <c r="H180" s="39" t="n"/>
+    </row>
+    <row r="181" ht="108" customHeight="1">
+      <c r="A181" s="40" t="n"/>
+      <c r="B181" s="40" t="n"/>
+      <c r="C181" s="40" t="n"/>
+      <c r="D181" s="40" t="n"/>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>Planning and estimation</t>
+        </is>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>How do you estimate a piece of work nobody in the team has done before?</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t>Break it down until the pieces resemble something already delivered, then combine analogy with bottom-up for the known parts. Give a range with the assumptions that would move it, and keep the estimate separate from the commitment. Allow explicitly for integration, test, environments, rework and non-project time rather than adding a flat fudge. Re-estimate once a first slice is genuinely built. Record the assumptions in the SOW so that a changed assumption becomes a change request rather than an argument.</t>
+        </is>
+      </c>
+      <c r="H181" s="39" t="n"/>
+    </row>
+    <row r="182" ht="108" customHeight="1">
+      <c r="A182" s="40" t="n"/>
+      <c r="B182" s="40" t="n"/>
+      <c r="C182" s="40" t="n"/>
+      <c r="D182" s="40" t="n"/>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>Risk and escalation</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>What makes a risk log useful rather than theatre?</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>Every risk has an owner, an observable trigger, an impact in money or days rather than high/medium/low alone, a mitigation someone is actually doing, and a review date. Risks are retired or realised rather than carried forever, and the log drives the governance conversation instead of being read out at it. Strong answers separate risk from issue from dependency, and can point to contingency that was genuinely budgeted rather than hoped for.</t>
+        </is>
+      </c>
+      <c r="H182" s="39" t="n"/>
+    </row>
+    <row r="183" ht="108" customHeight="1">
+      <c r="A183" s="40" t="n"/>
+      <c r="B183" s="40" t="n"/>
+      <c r="C183" s="40" t="n"/>
+      <c r="D183" s="40" t="n"/>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>Stakeholder management</t>
+        </is>
+      </c>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>How do you handle a stakeholder who keeps changing what they want?</t>
+        </is>
+      </c>
+      <c r="G183" s="4" t="inlineStr">
+        <is>
+          <t>Separate the pattern from the person: churn usually means the requirement was never really agreed, or two stakeholders disagree and you are the channel between them. Fix it structurally — one accountable decision-maker per area, decisions recorded with dates, a change process that prices and schedules each change rather than refusing it, and a backlog they prioritise themselves so the trade-off is theirs. Then show the cost of churn in their own currency: a change log with the days and the money it has already taken.</t>
+        </is>
+      </c>
+      <c r="H183" s="39" t="n"/>
+    </row>
+    <row r="184" ht="108" customHeight="1">
+      <c r="A184" s="40" t="n"/>
+      <c r="B184" s="40" t="n"/>
+      <c r="C184" s="40" t="n"/>
+      <c r="D184" s="40" t="n"/>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>Metrics and improvement</t>
+        </is>
+      </c>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>Which handful of metrics tell you whether delivery is actually healthy?</t>
+        </is>
+      </c>
+      <c r="G184" s="4" t="inlineStr">
+        <is>
+          <t>A small set, each with a reason: throughput or velocity as a trend rather than an absolute, milestone or schedule variance, defect escape rate and rework, scope added after baseline, dependency ageing, and on the people side utilisation against attrition. A good answer insists on counterweighted pairs so no single number can be gamed — speed against quality, utilisation against attrition — and acts when the trend turns rather than when a threshold breaks.</t>
+        </is>
+      </c>
+      <c r="H184" s="39" t="n"/>
+    </row>
+    <row r="185" ht="108" customHeight="1">
+      <c r="A185" s="40" t="n"/>
+      <c r="B185" s="40" t="n"/>
+      <c r="C185" s="40" t="n"/>
+      <c r="D185" s="40" t="n"/>
+      <c r="E185" s="4" t="inlineStr">
+        <is>
+          <t>People and team management</t>
+        </is>
+      </c>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>How do you deal with someone who is not performing?</t>
+        </is>
+      </c>
+      <c r="G185" s="4" t="inlineStr">
+        <is>
+          <t>Establish the facts before the conversation: what the expectation was, whether it was ever made explicit, and whether the cause is capability, clarity, workload or something outside work. Then a direct, private, specific conversation — what is happening, what is expected, what support, by when, and what follows if it does not change — documented, and followed up on the date promised. Strong answers include cases where the cause turned out to be theirs, through unclear expectations or badly matched work, and cases they did have to exit, handled without humiliating the person.</t>
+        </is>
+      </c>
+      <c r="H185" s="39" t="n"/>
+    </row>
+    <row r="186" ht="108" customHeight="1">
+      <c r="A186" s="41" t="n"/>
+      <c r="B186" s="41" t="n"/>
+      <c r="C186" s="41" t="n"/>
+      <c r="D186" s="41" t="n"/>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>Commercials and resourcing</t>
+        </is>
+      </c>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>What drives margin on a services engagement, and what can you actually control?</t>
+        </is>
+      </c>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>Price is largely set at sale. Delivery controls the grade pyramid, the location mix, utilisation of the billed team, non-billable effort, rework, and scope absorbed without a change request — plus leakage through unapproved time, late billing, unbilled ageing and discounts given to settle disputes. A good answer names the lever with the biggest effect in their own experience, usually grade mix or absorbed scope, and says what they changed.</t>
+        </is>
+      </c>
+      <c r="H186" s="39" t="n"/>
+    </row>
+    <row r="187" ht="108" customHeight="1">
+      <c r="A187" s="36" t="n">
+        <v>27</v>
+      </c>
+      <c r="B187" s="37" t="inlineStr">
+        <is>
+          <t>Sowdhamini J</t>
+        </is>
+      </c>
+      <c r="C187" s="38" t="inlineStr">
+        <is>
+          <t>Service operations</t>
+        </is>
+      </c>
+      <c r="D187" s="36" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="E187" s="4" t="inlineStr">
+        <is>
+          <t>Delivery governance</t>
+        </is>
+      </c>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>What does your weekly governance pack actually contain, and who reads which part of it?</t>
+        </is>
+      </c>
+      <c r="G187" s="4" t="inlineStr">
+        <is>
+          <t>A good answer separates the audiences. The team needs the work-level view — what is in flight, what is blocked, the defect trend. The client needs outcomes against commitments: milestones, scope changes, risks and the decisions they owe us. Internal leadership needs the commercial and resourcing picture: utilisation, margin, staffing gaps, escalations. It names a cadence — daily standup, weekly status, monthly business review — and says which decisions each forum is allowed to take. Strong candidates add that the pack is generated from the tracker rather than assembled by hand, and that every red item carries a named owner and a date.</t>
+        </is>
+      </c>
+      <c r="H187" s="39" t="n"/>
+    </row>
+    <row r="188" ht="108" customHeight="1">
+      <c r="A188" s="40" t="n"/>
+      <c r="B188" s="40" t="n"/>
+      <c r="C188" s="40" t="n"/>
+      <c r="D188" s="40" t="n"/>
+      <c r="E188" s="4" t="inlineStr">
+        <is>
+          <t>Planning and estimation</t>
+        </is>
+      </c>
+      <c r="F188" s="4" t="inlineStr">
+        <is>
+          <t>How do you estimate a piece of work nobody in the team has done before?</t>
+        </is>
+      </c>
+      <c r="G188" s="4" t="inlineStr">
+        <is>
+          <t>Break it down until the pieces resemble something already delivered, then combine analogy with bottom-up for the known parts. Give a range with the assumptions that would move it, and keep the estimate separate from the commitment. Allow explicitly for integration, test, environments, rework and non-project time rather than adding a flat fudge. Re-estimate once a first slice is genuinely built. Record the assumptions in the SOW so that a changed assumption becomes a change request rather than an argument.</t>
+        </is>
+      </c>
+      <c r="H188" s="39" t="n"/>
+    </row>
+    <row r="189" ht="108" customHeight="1">
+      <c r="A189" s="40" t="n"/>
+      <c r="B189" s="40" t="n"/>
+      <c r="C189" s="40" t="n"/>
+      <c r="D189" s="40" t="n"/>
+      <c r="E189" s="4" t="inlineStr">
+        <is>
+          <t>Risk and escalation</t>
+        </is>
+      </c>
+      <c r="F189" s="4" t="inlineStr">
+        <is>
+          <t>What makes a risk log useful rather than theatre?</t>
+        </is>
+      </c>
+      <c r="G189" s="4" t="inlineStr">
+        <is>
+          <t>Every risk has an owner, an observable trigger, an impact in money or days rather than high/medium/low alone, a mitigation someone is actually doing, and a review date. Risks are retired or realised rather than carried forever, and the log drives the governance conversation instead of being read out at it. Strong answers separate risk from issue from dependency, and can point to contingency that was genuinely budgeted rather than hoped for.</t>
+        </is>
+      </c>
+      <c r="H189" s="39" t="n"/>
+    </row>
+    <row r="190" ht="108" customHeight="1">
+      <c r="A190" s="40" t="n"/>
+      <c r="B190" s="40" t="n"/>
+      <c r="C190" s="40" t="n"/>
+      <c r="D190" s="40" t="n"/>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>Stakeholder management</t>
+        </is>
+      </c>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>How do you handle a stakeholder who keeps changing what they want?</t>
+        </is>
+      </c>
+      <c r="G190" s="4" t="inlineStr">
+        <is>
+          <t>Separate the pattern from the person: churn usually means the requirement was never really agreed, or two stakeholders disagree and you are the channel between them. Fix it structurally — one accountable decision-maker per area, decisions recorded with dates, a change process that prices and schedules each change rather than refusing it, and a backlog they prioritise themselves so the trade-off is theirs. Then show the cost of churn in their own currency: a change log with the days and the money it has already taken.</t>
+        </is>
+      </c>
+      <c r="H190" s="39" t="n"/>
+    </row>
+    <row r="191" ht="108" customHeight="1">
+      <c r="A191" s="40" t="n"/>
+      <c r="B191" s="40" t="n"/>
+      <c r="C191" s="40" t="n"/>
+      <c r="D191" s="40" t="n"/>
+      <c r="E191" s="4" t="inlineStr">
+        <is>
+          <t>Metrics and improvement</t>
+        </is>
+      </c>
+      <c r="F191" s="4" t="inlineStr">
+        <is>
+          <t>Which handful of metrics tell you whether delivery is actually healthy?</t>
+        </is>
+      </c>
+      <c r="G191" s="4" t="inlineStr">
+        <is>
+          <t>A small set, each with a reason: throughput or velocity as a trend rather than an absolute, milestone or schedule variance, defect escape rate and rework, scope added after baseline, dependency ageing, and on the people side utilisation against attrition. A good answer insists on counterweighted pairs so no single number can be gamed — speed against quality, utilisation against attrition — and acts when the trend turns rather than when a threshold breaks.</t>
+        </is>
+      </c>
+      <c r="H191" s="39" t="n"/>
+    </row>
+    <row r="192" ht="108" customHeight="1">
+      <c r="A192" s="40" t="n"/>
+      <c r="B192" s="40" t="n"/>
+      <c r="C192" s="40" t="n"/>
+      <c r="D192" s="40" t="n"/>
+      <c r="E192" s="4" t="inlineStr">
+        <is>
+          <t>People and team management</t>
+        </is>
+      </c>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>How do you deal with someone who is not performing?</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>Establish the facts before the conversation: what the expectation was, whether it was ever made explicit, and whether the cause is capability, clarity, workload or something outside work. Then a direct, private, specific conversation — what is happening, what is expected, what support, by when, and what follows if it does not change — documented, and followed up on the date promised. Strong answers include cases where the cause turned out to be theirs, through unclear expectations or badly matched work, and cases they did have to exit, handled without humiliating the person.</t>
+        </is>
+      </c>
+      <c r="H192" s="39" t="n"/>
+    </row>
+    <row r="193" ht="108" customHeight="1">
+      <c r="A193" s="41" t="n"/>
+      <c r="B193" s="41" t="n"/>
+      <c r="C193" s="41" t="n"/>
+      <c r="D193" s="41" t="n"/>
+      <c r="E193" s="4" t="inlineStr">
+        <is>
+          <t>Commercials and resourcing</t>
+        </is>
+      </c>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>What drives margin on a services engagement, and what can you actually control?</t>
+        </is>
+      </c>
+      <c r="G193" s="4" t="inlineStr">
+        <is>
+          <t>Price is largely set at sale. Delivery controls the grade pyramid, the location mix, utilisation of the billed team, non-billable effort, rework, and scope absorbed without a change request — plus leakage through unapproved time, late billing, unbilled ageing and discounts given to settle disputes. A good answer names the lever with the biggest effect in their own experience, usually grade mix or absorbed scope, and says what they changed.</t>
+        </is>
+      </c>
+      <c r="H193" s="39" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="102">
+  <mergeCells count="110">
     <mergeCell ref="A12:A18"/>
     <mergeCell ref="C12:C18"/>
     <mergeCell ref="C61:C67"/>
@@ -13887,11 +15879,15 @@
     <mergeCell ref="A54:A60"/>
     <mergeCell ref="A138:A144"/>
     <mergeCell ref="C54:C60"/>
+    <mergeCell ref="B180:B186"/>
     <mergeCell ref="A82:A88"/>
+    <mergeCell ref="A187:A193"/>
+    <mergeCell ref="C187:C193"/>
     <mergeCell ref="B117:B123"/>
     <mergeCell ref="C26:C32"/>
     <mergeCell ref="A124:A130"/>
     <mergeCell ref="C124:C130"/>
+    <mergeCell ref="C180:C186"/>
     <mergeCell ref="B166:B172"/>
     <mergeCell ref="D166:D172"/>
     <mergeCell ref="C117:C123"/>
@@ -13917,6 +15913,7 @@
     <mergeCell ref="A152:A158"/>
     <mergeCell ref="C68:C74"/>
     <mergeCell ref="D131:D137"/>
+    <mergeCell ref="D187:D193"/>
     <mergeCell ref="D124:D130"/>
     <mergeCell ref="B61:B67"/>
     <mergeCell ref="D61:D67"/>
@@ -13926,6 +15923,7 @@
     <mergeCell ref="A33:A39"/>
     <mergeCell ref="B54:B60"/>
     <mergeCell ref="D54:D60"/>
+    <mergeCell ref="A180:A186"/>
     <mergeCell ref="A19:A25"/>
     <mergeCell ref="A117:A123"/>
     <mergeCell ref="C33:C39"/>
@@ -13948,6 +15946,7 @@
     <mergeCell ref="C47:C53"/>
     <mergeCell ref="A145:A151"/>
     <mergeCell ref="B82:B88"/>
+    <mergeCell ref="B187:B193"/>
     <mergeCell ref="A89:A95"/>
     <mergeCell ref="D12:D18"/>
     <mergeCell ref="A1:H1"/>
@@ -13955,6 +15954,7 @@
     <mergeCell ref="B124:B130"/>
     <mergeCell ref="B5:B11"/>
     <mergeCell ref="A26:A32"/>
+    <mergeCell ref="D180:D186"/>
     <mergeCell ref="D5:D11"/>
     <mergeCell ref="A131:A137"/>
     <mergeCell ref="C131:C137"/>
@@ -13972,7 +15972,7 @@
     <mergeCell ref="B152:B158"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="H5:H193" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
@@ -13987,7 +15987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -14019,7 +16019,7 @@
         </is>
       </c>
       <c r="B4" s="43" t="n">
-        <v>46309</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="5">
@@ -14029,8 +16029,8 @@
         </is>
       </c>
       <c r="B5" s="11">
-        <f>COUNTA('Interview Inventory'!$A$3:$A$27)</f>
-        <v>25</v>
+        <f>COUNTA('Interview Inventory'!$A$3:$A$29)</f>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -14075,470 +16075,508 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Process Manager</t>
         </is>
       </c>
       <c r="B9" s="11">
-        <f>COUNTIF('Interview Inventory'!$D$3:$D$27,A9)</f>
-        <v>7</v>
+        <f>COUNTIF('Interview Inventory'!$D$3:$D$29,A9)</f>
+        <v>2</v>
       </c>
       <c r="C9" s="15">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A9,'Interview Inventory'!$N$3:$N$27),"")</f>
-        <v>9.8885714286</v>
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$29,A9,'Interview Inventory'!$N$3:$N$29),"")</f>
+        <v>11.25</v>
       </c>
       <c r="D9" s="15">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A9,'Interview Inventory'!$O$3:$O$27),"")</f>
-        <v>15.8571428571</v>
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$29,A9,'Interview Inventory'!$O$3:$O$29),"")</f>
+        <v>16</v>
       </c>
       <c r="E9" s="16">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A9,'Interview Inventory'!$Q$3:$Q$27),"")</f>
-        <v>0.6679520583</v>
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$29,A9,'Interview Inventory'!$Q$3:$Q$29),"")</f>
+        <v>0.4226190476</v>
       </c>
       <c r="F9" s="15">
-        <f>_xlfn.MAXIFS('Interview Inventory'!$O$3:$O$27,'Interview Inventory'!$D$3:$D$27,A9)</f>
-        <v>25</v>
+        <f>_xlfn.MAXIFS('Interview Inventory'!$O$3:$O$29,'Interview Inventory'!$D$3:$D$29,A9)</f>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>Technical Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" s="11">
-        <f>COUNTIF('Interview Inventory'!$D$3:$D$27,A10)</f>
-        <v>9</v>
+        <f>COUNTIF('Interview Inventory'!$D$3:$D$29,A10)</f>
+        <v>7</v>
       </c>
       <c r="C10" s="15">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A10,'Interview Inventory'!$N$3:$N$27),"")</f>
-        <v>22.8555555556</v>
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$29,A10,'Interview Inventory'!$N$3:$N$29),"")</f>
+        <v>9.8885714286</v>
       </c>
       <c r="D10" s="15">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A10,'Interview Inventory'!$O$3:$O$27),"")</f>
-        <v>29.4444444444</v>
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$29,A10,'Interview Inventory'!$O$3:$O$29),"")</f>
+        <v>15.8571428571</v>
       </c>
       <c r="E10" s="16">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A10,'Interview Inventory'!$Q$3:$Q$27),"")</f>
-        <v>0.3315765374</v>
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$29,A10,'Interview Inventory'!$Q$3:$Q$29),"")</f>
+        <v>0.6679520583</v>
       </c>
       <c r="F10" s="15">
-        <f>_xlfn.MAXIFS('Interview Inventory'!$O$3:$O$27,'Interview Inventory'!$D$3:$D$27,A10)</f>
-        <v>36</v>
+        <f>_xlfn.MAXIFS('Interview Inventory'!$O$3:$O$29,'Interview Inventory'!$D$3:$D$29,A10)</f>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>Technical Project Manager</t>
+          <t>Technical Consultant</t>
         </is>
       </c>
       <c r="B11" s="11">
-        <f>COUNTIF('Interview Inventory'!$D$3:$D$27,A11)</f>
-        <v>2</v>
+        <f>COUNTIF('Interview Inventory'!$D$3:$D$29,A11)</f>
+        <v>9</v>
       </c>
       <c r="C11" s="15">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A11,'Interview Inventory'!$N$3:$N$27),"")</f>
-        <v>14.25</v>
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$29,A11,'Interview Inventory'!$N$3:$N$29),"")</f>
+        <v>22.8555555556</v>
       </c>
       <c r="D11" s="15">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A11,'Interview Inventory'!$O$3:$O$27),"")</f>
-        <v>20.25</v>
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$29,A11,'Interview Inventory'!$O$3:$O$29),"")</f>
+        <v>29.4444444444</v>
       </c>
       <c r="E11" s="16">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A11,'Interview Inventory'!$Q$3:$Q$27),"")</f>
-        <v>0.4275</v>
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$29,A11,'Interview Inventory'!$Q$3:$Q$29),"")</f>
+        <v>0.3315765374</v>
       </c>
       <c r="F11" s="15">
-        <f>_xlfn.MAXIFS('Interview Inventory'!$O$3:$O$27,'Interview Inventory'!$D$3:$D$27,A11)</f>
-        <v>22</v>
+        <f>_xlfn.MAXIFS('Interview Inventory'!$O$3:$O$29,'Interview Inventory'!$D$3:$D$29,A11)</f>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
+          <t>Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="B12" s="11">
+        <f>COUNTIF('Interview Inventory'!$D$3:$D$29,A12)</f>
+        <v>2</v>
+      </c>
+      <c r="C12" s="15">
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$29,A12,'Interview Inventory'!$N$3:$N$29),"")</f>
+        <v>14.25</v>
+      </c>
+      <c r="D12" s="15">
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$29,A12,'Interview Inventory'!$O$3:$O$29),"")</f>
+        <v>20.25</v>
+      </c>
+      <c r="E12" s="16">
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$29,A12,'Interview Inventory'!$Q$3:$Q$29),"")</f>
+        <v>0.4275</v>
+      </c>
+      <c r="F12" s="15">
+        <f>_xlfn.MAXIFS('Interview Inventory'!$O$3:$O$29,'Interview Inventory'!$D$3:$D$29,A12)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
           <t>Technology Lead</t>
         </is>
       </c>
-      <c r="B12" s="11">
-        <f>COUNTIF('Interview Inventory'!$D$3:$D$27,A12)</f>
+      <c r="B13" s="11">
+        <f>COUNTIF('Interview Inventory'!$D$3:$D$29,A13)</f>
         <v>7</v>
       </c>
-      <c r="C12" s="15">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A12,'Interview Inventory'!$N$3:$N$27),"")</f>
+      <c r="C13" s="15">
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$29,A13,'Interview Inventory'!$N$3:$N$29),"")</f>
         <v>22.8428571429</v>
       </c>
-      <c r="D12" s="15">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A12,'Interview Inventory'!$O$3:$O$27),"")</f>
+      <c r="D13" s="15">
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$29,A13,'Interview Inventory'!$O$3:$O$29),"")</f>
         <v>31.4285714286</v>
       </c>
-      <c r="E12" s="16">
-        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$27,A12,'Interview Inventory'!$Q$3:$Q$27),"")</f>
+      <c r="E13" s="16">
+        <f>IFERROR(AVERAGEIF('Interview Inventory'!$D$3:$D$29,A13,'Interview Inventory'!$Q$3:$Q$29),"")</f>
         <v>0.3802691395</v>
       </c>
-      <c r="F12" s="15">
-        <f>_xlfn.MAXIFS('Interview Inventory'!$O$3:$O$27,'Interview Inventory'!$D$3:$D$27,A12)</f>
+      <c r="F13" s="15">
+        <f>_xlfn.MAXIFS('Interview Inventory'!$O$3:$O$29,'Interview Inventory'!$D$3:$D$29,A13)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="42" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>All roles</t>
         </is>
       </c>
-      <c r="B13" s="33">
-        <f>COUNTA('Interview Inventory'!$A$3:$A$27)</f>
-        <v>25</v>
-      </c>
-      <c r="C13" s="46">
-        <f>AVERAGE('Interview Inventory'!$N$3:$N$27)</f>
-        <v>18.5328</v>
-      </c>
-      <c r="D13" s="46">
-        <f>AVERAGE('Interview Inventory'!$O$3:$O$27)</f>
-        <v>25.46</v>
-      </c>
-      <c r="E13" s="47">
-        <f>AVERAGE('Interview Inventory'!$Q$3:$Q$27)</f>
-        <v>0.4470694889</v>
-      </c>
-      <c r="F13" s="46">
-        <f>MAX('Interview Inventory'!$O$3:$O$27)</f>
+      <c r="B14" s="33">
+        <f>COUNTA('Interview Inventory'!$A$3:$A$29)</f>
+        <v>27</v>
+      </c>
+      <c r="C14" s="46">
+        <f>AVERAGE('Interview Inventory'!$N$3:$N$29)</f>
+        <v>17.9933333333</v>
+      </c>
+      <c r="D14" s="46">
+        <f>AVERAGE('Interview Inventory'!$O$3:$O$29)</f>
+        <v>24.7592592593</v>
+      </c>
+      <c r="E14" s="47">
+        <f>AVERAGE('Interview Inventory'!$Q$3:$Q$29)</f>
+        <v>0.4452583451</v>
+      </c>
+      <c r="F14" s="46">
+        <f>MAX('Interview Inventory'!$O$3:$O$29)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="45" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="45" t="inlineStr">
         <is>
           <t>Availability against the as-on date</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Candidates</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>% of pipeline</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>Last working day already passed</t>
-        </is>
-      </c>
-      <c r="B17" s="11">
-        <f>COUNTIF('Interview Inventory'!$T$3:$T$27,"Available now")</f>
-        <v>22</v>
-      </c>
-      <c r="C17" s="16">
-        <f>IFERROR(B17/$B$5,"")</f>
-        <v>0.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>Within 30 days</t>
+          <t>Last working day already passed</t>
         </is>
       </c>
       <c r="B18" s="11">
-        <f>COUNTIF('Interview Inventory'!$T$3:$T$27,"Within 30 days")</f>
-        <v>2</v>
+        <f>COUNTIF('Interview Inventory'!$T$3:$T$29,"Available now")</f>
+        <v>25</v>
       </c>
       <c r="C18" s="16">
         <f>IFERROR(B18/$B$5,"")</f>
-        <v>0.08</v>
+        <v>0.9259259259</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>Beyond 30 days</t>
+          <t>Within 30 days</t>
         </is>
       </c>
       <c r="B19" s="11">
-        <f>COUNTIF('Interview Inventory'!$T$3:$T$27,"Beyond 30 days")</f>
-        <v>0</v>
+        <f>COUNTIF('Interview Inventory'!$T$3:$T$29,"Within 30 days")</f>
+        <v>1</v>
       </c>
       <c r="C19" s="16">
         <f>IFERROR(B19/$B$5,"")</f>
-        <v>0.0</v>
+        <v>0.037037037</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Notice period stated, no exit date</t>
+          <t>Beyond 30 days</t>
         </is>
       </c>
       <c r="B20" s="11">
-        <f>COUNTIF('Interview Inventory'!$T$3:$T$27,"Notice period only")</f>
-        <v>1</v>
+        <f>COUNTIF('Interview Inventory'!$T$3:$T$29,"Beyond 30 days")</f>
+        <v>0</v>
       </c>
       <c r="C20" s="16">
         <f>IFERROR(B20/$B$5,"")</f>
-        <v>0.04</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>Notice not captured</t>
+          <t>Notice period stated, no exit date</t>
         </is>
       </c>
       <c r="B21" s="11">
-        <f>COUNTIF('Interview Inventory'!$T$3:$T$27,"Not captured")</f>
-        <v>0</v>
+        <f>COUNTIF('Interview Inventory'!$T$3:$T$29,"Notice period only")</f>
+        <v>1</v>
       </c>
       <c r="C21" s="16">
         <f>IFERROR(B21/$B$5,"")</f>
+        <v>0.037037037</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Notice not captured</t>
+        </is>
+      </c>
+      <c r="B22" s="11">
+        <f>COUNTIF('Interview Inventory'!$T$3:$T$29,"Not captured")</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="16">
+        <f>IFERROR(B22/$B$5,"")</f>
         <v>0.0</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="45" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="45" t="inlineStr">
         <is>
           <t>Batch, commercials, offers and flags</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Measure</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>Submitted 5 Sep 2026</t>
-        </is>
-      </c>
-      <c r="B25" s="11">
-        <f>COUNTIF('Interview Inventory'!$C$3:$C$27,"5-Sep-2026")</f>
-        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>Submitted 21 Sep 2026</t>
+          <t>Submitted 5 Sep 2026</t>
         </is>
       </c>
       <c r="B26" s="11">
-        <f>COUNTIF('Interview Inventory'!$C$3:$C$27,"21-Sep-2026")</f>
-        <v>17</v>
+        <f>COUNTIF('Interview Inventory'!$C$3:$C$29,"5-Sep-2026")</f>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>Submitted 8 Oct 2026</t>
+          <t>Submitted 21 Sep 2026</t>
         </is>
       </c>
       <c r="B27" s="11">
-        <f>COUNTIF('Interview Inventory'!$C$3:$C$27,"8-Oct-2026")</f>
-        <v>2</v>
+        <f>COUNTIF('Interview Inventory'!$C$3:$C$29,"21-Sep-2026")</f>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>CTC and ECTC captured</t>
+          <t>Submitted 8 Oct 2026</t>
         </is>
       </c>
       <c r="B28" s="11">
-        <f>COUNT('Interview Inventory'!$N$3:$N$27)</f>
-        <v>25</v>
+        <f>COUNTIF('Interview Inventory'!$C$3:$C$29,"8-Oct-2026")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>Commercials not yet captured</t>
+          <t>Submitted 22 Oct 2026</t>
         </is>
       </c>
       <c r="B29" s="11">
-        <f>$B$5-COUNT('Interview Inventory'!$N$3:$N$27)</f>
-        <v>0</v>
+        <f>COUNTIF('Interview Inventory'!$C$3:$C$29,"22-Oct-2026")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Holding a competing offer</t>
+          <t>CTC and ECTC captured</t>
         </is>
       </c>
       <c r="B30" s="11">
-        <f>$B$5-COUNTIF('Interview Inventory'!$P$3:$P$27,"No")-COUNTIF('Interview Inventory'!$P$3:$P$27,"Not captured")</f>
-        <v>4</v>
+        <f>COUNT('Interview Inventory'!$N$3:$N$29)</f>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Already in Coimbatore</t>
+          <t>Commercials not yet captured</t>
         </is>
       </c>
       <c r="B31" s="11">
-        <f>COUNTIF('Interview Inventory'!$K$3:$K$27,"Coimbatore")</f>
-        <v>17</v>
+        <f>$B$5-COUNT('Interview Inventory'!$N$3:$N$29)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>Carrying a High flag</t>
+          <t>Holding a competing offer</t>
         </is>
       </c>
       <c r="B32" s="11">
-        <f>COUNTIF('Interview Inventory'!$U$3:$U$27,"High")</f>
-        <v>9</v>
+        <f>$B$5-COUNTIF('Interview Inventory'!$P$3:$P$29,"No")-COUNTIF('Interview Inventory'!$P$3:$P$29,"Not captured")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>Carrying a Medium flag</t>
+          <t>Already in Coimbatore</t>
         </is>
       </c>
       <c r="B33" s="11">
-        <f>COUNTIF('Interview Inventory'!$U$3:$U$27,"Medium")</f>
-        <v>15</v>
+        <f>COUNTIF('Interview Inventory'!$K$3:$K$29,"Coimbatore")</f>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
+          <t>Carrying a High flag</t>
+        </is>
+      </c>
+      <c r="B34" s="11">
+        <f>COUNTIF('Interview Inventory'!$U$3:$U$29,"High")</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>Carrying a Medium flag</t>
+        </is>
+      </c>
+      <c r="B35" s="11">
+        <f>COUNTIF('Interview Inventory'!$U$3:$U$29,"Medium")</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
           <t>No flags raised</t>
         </is>
       </c>
-      <c r="B34" s="11">
-        <f>COUNTIF('Interview Inventory'!$U$3:$U$27,"None")</f>
+      <c r="B36" s="11">
+        <f>COUNTIF('Interview Inventory'!$U$3:$U$29,"None")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="45" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="45" t="inlineStr">
         <is>
           <t>Interview funnel (fills as the tracking columns are used)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr">
-        <is>
-          <t>Shortlisted at screening</t>
-        </is>
-      </c>
-      <c r="B38" s="11">
-        <f>COUNTIF('Interview Inventory'!$Y$3:$Y$27,"Shortlisted")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="14" t="inlineStr">
-        <is>
-          <t>Round 1 selected</t>
-        </is>
-      </c>
-      <c r="B39" s="11">
-        <f>COUNTIF('Interview Inventory'!$AB$3:$AB$27,"Selected")</f>
-        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Round 2 selected</t>
+          <t>Shortlisted at screening</t>
         </is>
       </c>
       <c r="B40" s="11">
-        <f>COUNTIF('Interview Inventory'!$AE$3:$AE$27,"Selected")</f>
+        <f>COUNTIF('Interview Inventory'!$Y$3:$Y$29,"Shortlisted")</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Round 3 selected</t>
+          <t>Round 1 selected</t>
         </is>
       </c>
       <c r="B41" s="11">
-        <f>COUNTIF('Interview Inventory'!$AH$3:$AH$27,"Selected")</f>
+        <f>COUNTIF('Interview Inventory'!$AB$3:$AB$29,"Selected")</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>Final round selected</t>
+          <t>Round 2 selected</t>
         </is>
       </c>
       <c r="B42" s="11">
-        <f>COUNTIF('Interview Inventory'!$AK$3:$AK$27,"Selected")</f>
+        <f>COUNTIF('Interview Inventory'!$AE$3:$AE$29,"Selected")</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>Offer released</t>
+          <t>Round 3 selected</t>
         </is>
       </c>
       <c r="B43" s="11">
-        <f>COUNTIF('Interview Inventory'!$AN$3:$AN$27,"Yes")</f>
+        <f>COUNTIF('Interview Inventory'!$AH$3:$AH$29,"Selected")</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>Joined</t>
+          <t>Final round selected</t>
         </is>
       </c>
       <c r="B44" s="11">
-        <f>COUNTIF('Interview Inventory'!$AM$3:$AM$27,"Joined")</f>
+        <f>COUNTIF('Interview Inventory'!$AK$3:$AK$29,"Selected")</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
+          <t>Offer released</t>
+        </is>
+      </c>
+      <c r="B45" s="11">
+        <f>COUNTIF('Interview Inventory'!$AN$3:$AN$29,"Yes")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>Joined</t>
+        </is>
+      </c>
+      <c r="B46" s="11">
+        <f>COUNTIF('Interview Inventory'!$AM$3:$AM$29,"Joined")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
           <t>Rejected at any round</t>
         </is>
       </c>
-      <c r="B45" s="11">
-        <f>COUNTIF('Interview Inventory'!$Y$3:$Y$27,"Rejected")+COUNTIF('Interview Inventory'!$AB$3:$AB$27,"Rejected")+COUNTIF('Interview Inventory'!$AE$3:$AE$27,"Rejected")+COUNTIF('Interview Inventory'!$AH$3:$AH$27,"Rejected")+COUNTIF('Interview Inventory'!$AK$3:$AK$27,"Rejected")</f>
+      <c r="B47" s="11">
+        <f>COUNTIF('Interview Inventory'!$Y$3:$Y$29,"Rejected")+COUNTIF('Interview Inventory'!$AB$3:$AB$29,"Rejected")+COUNTIF('Interview Inventory'!$AE$3:$AE$29,"Rejected")+COUNTIF('Interview Inventory'!$AH$3:$AH$29,"Rejected")+COUNTIF('Interview Inventory'!$AK$3:$AK$29,"Rejected")</f>
         <v>0</v>
       </c>
     </row>
